--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication marine results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication marine results.xlsx
@@ -589,19 +589,19 @@
         <v>0.001864157737064602</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001754113421556967</v>
+        <v>0.001754113421556968</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001829942376750429</v>
+        <v>0.001829942376750431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002872673017420662</v>
+        <v>0.002872673017420658</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001803679743120383</v>
+        <v>0.001803679743120384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001943722429435665</v>
+        <v>0.001943722429435666</v>
       </c>
       <c r="H2" t="n">
         <v>0.001864157737064602</v>
@@ -646,7 +646,7 @@
         <v>0.001864157737064602</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001796001026684731</v>
+        <v>0.001796001026684733</v>
       </c>
       <c r="W2" t="n">
         <v>0.001864157737064602</v>
@@ -658,7 +658,7 @@
         <v>0.001864157737064602</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001800508874961835</v>
+        <v>0.001800508874961836</v>
       </c>
       <c r="AA2" t="n">
         <v>0.001864157737064602</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002879850906566444</v>
+        <v>0.002879850906566443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001763328783796273</v>
+        <v>0.001763328783796274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001776245881037472</v>
+        <v>0.001776245881037473</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001768365280962512</v>
+        <v>0.001768365280962511</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03525147899299396</v>
+        <v>0.03525147899299397</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007963894675772862</v>
+        <v>0.007963894675772867</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03111000349592578</v>
+        <v>0.03111000349592579</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01461666424202286</v>
+        <v>0.01461666424202283</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02359369252301798</v>
+        <v>0.02359369252301793</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05999111011245782</v>
+        <v>0.05999111011245774</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02797156959309736</v>
+        <v>0.02797156959309738</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03511889628077471</v>
+        <v>0.03511889628077464</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03882952017870061</v>
+        <v>0.03882952017870062</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05265290118517389</v>
+        <v>0.0526529011851739</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05055152664452104</v>
+        <v>0.05055152664452112</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06961039704281181</v>
+        <v>0.06961039704281173</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04597571833663535</v>
+        <v>0.04597571833663527</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03144318302704475</v>
+        <v>0.03144318302704469</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03802887962947453</v>
+        <v>0.03802887962947449</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02077426463386631</v>
+        <v>0.02077426463386626</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02204564099472861</v>
+        <v>0.02204564099472864</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03189731623496573</v>
+        <v>0.03189731623496569</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03580184744576241</v>
+        <v>0.0358018474457624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04597571833663536</v>
+        <v>0.04597571833663525</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01668706507849802</v>
+        <v>0.01668706507849797</v>
       </c>
       <c r="W4" t="n">
         <v>0.02296743526931158</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03296942234099751</v>
+        <v>0.0329694223409975</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03604422636519726</v>
+        <v>0.03604422636519711</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02028228888907483</v>
+        <v>0.02028228888907478</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03638824174135249</v>
+        <v>0.03638824174135245</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.07433982528597365</v>
+        <v>0.07433982528597356</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="J5" t="n">
         <v>0.001067722337445204</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001034567162272617</v>
+        <v>0.001034567162272618</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00105519446619477</v>
+        <v>0.001055194466194769</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001034567162272617</v>
+        <v>0.001034567162272618</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001070045067587398</v>
+        <v>0.0010700450675874</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001070045067587399</v>
+        <v>0.0010700450675874</v>
       </c>
     </row>
     <row r="6">
@@ -938,58 +938,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001966619837033752</v>
+        <v>0.002914491115200135</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.002914491115200135</v>
       </c>
       <c r="D6" t="n">
         <v>0.001966619837033752</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.001966619837033752</v>
       </c>
       <c r="F6" t="n">
+        <v>0.002914491115200135</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.002914491115200135</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.002914491115200135</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.001966619837033752</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.001966619837033752</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.002914491115200134</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.002914491115200134</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.001964297106891547</v>
+        <v>0.002912168385057936</v>
       </c>
       <c r="K6" t="n">
         <v>0.001966619837033752</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.001966619837033752</v>
       </c>
       <c r="M6" t="n">
         <v>0.001966619837033752</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001971101844371763</v>
+        <v>0.00197110184437176</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002919315696664486</v>
+        <v>0.002919315696664487</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002919316905572724</v>
+        <v>0.002919316905572727</v>
       </c>
       <c r="Q6" t="n">
         <v>0.001966619837033752</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.001966619837033752</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.002914491115200135</v>
       </c>
       <c r="T6" t="n">
         <v>0.001966619837033752</v>
@@ -998,25 +998,25 @@
         <v>0.001966619837033752</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002899640513807505</v>
+        <v>0.002899640513807502</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002031382970734991</v>
+        <v>0.002919316249625546</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.002914491115200135</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002020043481806898</v>
+        <v>0.002020043481806926</v>
       </c>
       <c r="Z6" t="n">
         <v>0.001966619837033752</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002914491115200134</v>
+        <v>0.001966619837033752</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001983952789715743</v>
+        <v>0.001983952789715742</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001743668291898179</v>
+        <v>0.001743668291898175</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001745930932915293</v>
+        <v>0.001745930932915289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001745930932915293</v>
+        <v>0.001745930932915289</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001745105141209783</v>
+        <v>0.001745105141209779</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001731140420647745</v>
+        <v>0.00173114042064774</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001745991022040372</v>
+        <v>0.001745991022040369</v>
       </c>
     </row>
     <row r="8">
@@ -1114,67 +1114,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002318012700317719</v>
+        <v>0.00231801270031772</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.002794336973861685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002476731572983576</v>
+        <v>0.002476731572983575</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.00354808099944091</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="J8" t="n">
         <v>0.003334501136942856</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085046</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002547074769404925</v>
+        <v>0.002547074769404924</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002764104678644946</v>
+        <v>0.002764104678644947</v>
       </c>
       <c r="P8" t="n">
         <v>0.002710905403720685</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002117793052858829</v>
+        <v>0.002117793052858827</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002709299601508719</v>
+        <v>0.002838915766113746</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003321973265692425</v>
+        <v>0.003042810945605557</v>
       </c>
       <c r="W8" t="n">
         <v>0.003337024092516661</v>
@@ -1186,10 +1186,10 @@
         <v>0.004348709820953377</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.00229908775984898</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003336823867085058</v>
+        <v>0.003336823867085055</v>
       </c>
       <c r="AB8" t="n">
         <v>0.004401057322234732</v>
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003800312683439678</v>
+        <v>0.003800312683439675</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004456735114243822</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.002686420479335433</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691453507528</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004651368562131275</v>
+        <v>0.004651368562131274</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004936500060507006</v>
+        <v>0.004936500060507001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004998006080348213</v>
+        <v>0.004998006080348207</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00465369145350753</v>
+        <v>0.004653691453507528</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004638840690880845</v>
+        <v>0.005623620563837596</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.00413917994055779</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004653691292273477</v>
+        <v>0.004653691292273474</v>
       </c>
     </row>
     <row r="10">
@@ -1296,49 +1296,49 @@
         <v>0.001634103855261371</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001190089506507838</v>
+        <v>0.001190089506507839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002598550994747303</v>
+        <v>0.002598550994747297</v>
       </c>
       <c r="F10" t="n">
         <v>0.00134599775628775</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005048391753902349</v>
+        <v>0.0005048391753902352</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001273755317122926</v>
+        <v>0.001273755317122928</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00112120365912173</v>
+        <v>0.001121203659121731</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0009763438735835739</v>
+        <v>0.0009763438735835749</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007664193753231228</v>
+        <v>0.0007664193753231219</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0007550939846021194</v>
+        <v>0.0007550939846021208</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0004665474106656564</v>
+        <v>0.000466547410665656</v>
       </c>
       <c r="N10" t="n">
         <v>0.001033441369487843</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001081364570679369</v>
+        <v>0.001081364570679371</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0009659132191464209</v>
+        <v>0.000965913219146418</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001380212564519661</v>
+        <v>0.001380212564519662</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001375399846670473</v>
+        <v>0.001375399846670474</v>
       </c>
       <c r="S10" t="n">
         <v>0.001110047517225441</v>
@@ -1347,13 +1347,13 @@
         <v>0.001102664372104498</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0008297273305254545</v>
+        <v>0.000829727330525455</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001436039756393179</v>
+        <v>0.001436039756393181</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001324019037507214</v>
+        <v>0.001324019037507213</v>
       </c>
       <c r="X10" t="n">
         <v>0.001145432216580323</v>
@@ -1362,13 +1362,13 @@
         <v>0.001059493063026285</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001356595592857503</v>
+        <v>0.001356595592857504</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001056963681589349</v>
+        <v>0.001056963681589348</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004224414286842002</v>
+        <v>0.0004224414286842017</v>
       </c>
     </row>
     <row r="11">
@@ -1381,16 +1381,16 @@
         <v>0.001520757093097281</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001693024044997169</v>
+        <v>0.00169302404499717</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001566825056518005</v>
+        <v>0.001566825056518006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002744680661093326</v>
+        <v>0.002744680661093324</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001611501173387927</v>
+        <v>0.001611501173387928</v>
       </c>
       <c r="G11" t="n">
         <v>0.001368814024781495</v>
@@ -1405,31 +1405,31 @@
         <v>0.00150104117295597</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001408269156986533</v>
+        <v>0.001408269156986535</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001403116068116598</v>
+        <v>0.0014031160681166</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001361981477998797</v>
+        <v>0.0013619814779988</v>
       </c>
       <c r="N11" t="n">
         <v>0.001521763700177543</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001551570224544412</v>
+        <v>0.001551570224544413</v>
       </c>
       <c r="P11" t="n">
         <v>0.001499039491675293</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001687547014113795</v>
+        <v>0.001687547014113796</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001685357212155191</v>
+        <v>0.001685357212155192</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001564621056630003</v>
+        <v>0.001564621056630004</v>
       </c>
       <c r="T11" t="n">
         <v>0.001561261702071287</v>
@@ -1438,16 +1438,16 @@
         <v>0.001437074478354079</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001641206155798988</v>
+        <v>0.001641206155798989</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001661978780244984</v>
+        <v>0.001661978780244985</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001580721207600819</v>
+        <v>0.00158072120760082</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0015416186188619</v>
+        <v>0.001541618618861901</v>
       </c>
       <c r="Z11" t="n">
         <v>0.001613152354641922</v>
@@ -1456,7 +1456,7 @@
         <v>0.001540467742247434</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.00125175809507315</v>
+        <v>0.001251758095073152</v>
       </c>
     </row>
   </sheetData>
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001511721600753784</v>
+        <v>0.001511721600753783</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001524767091814097</v>
+        <v>0.001524767091814098</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001518293437811516</v>
+        <v>0.001518293437811517</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002737540497992269</v>
+        <v>0.00273754049799227</v>
       </c>
       <c r="F2" t="n">
         <v>0.001526827647979833</v>
@@ -1640,10 +1640,10 @@
         <v>0.001464548143936709</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001519635892978318</v>
+        <v>0.001519635892978319</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001519423493847929</v>
+        <v>0.001519423493847928</v>
       </c>
       <c r="J2" t="n">
         <v>0.001525163332006053</v>
@@ -1670,25 +1670,25 @@
         <v>0.001516966680331782</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001518008520484394</v>
+        <v>0.001518008520484395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001528396897864043</v>
+        <v>0.001528396897864044</v>
       </c>
       <c r="T2" t="n">
         <v>0.001521628470829072</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001529099781890029</v>
+        <v>0.001529099781890031</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001468700276424418</v>
+        <v>0.001468700276424417</v>
       </c>
       <c r="W2" t="n">
         <v>0.001539939916382564</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001571796430504118</v>
+        <v>0.001571796430504119</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001557522330772123</v>
@@ -1697,10 +1697,10 @@
         <v>0.001524539239073619</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001551898013671019</v>
+        <v>0.001551898013671018</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00145584637598524</v>
+        <v>0.001455846375985239</v>
       </c>
     </row>
     <row r="3">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001549635433805084</v>
+        <v>0.001549635433805085</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002783013998942291</v>
+        <v>0.00278301399894229</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0015465518720947</v>
+        <v>0.001546551872094701</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001475200475825989</v>
+        <v>0.00147520047582599</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001540360556644255</v>
+        <v>0.001540360556644256</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001543852082862741</v>
+        <v>0.001543852082862742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001524085547267262</v>
+        <v>0.001524085547267263</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="V3" t="n">
         <v>0.001481045731866806</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="X3" t="n">
         <v>0.001516808237021113</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001541522367227299</v>
+        <v>0.0015415223672273</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00154090623454039</v>
+        <v>0.001540906234540391</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001476823498975864</v>
+        <v>0.001476823498975865</v>
       </c>
     </row>
     <row r="4">
@@ -1798,37 +1798,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002016059532946635</v>
+        <v>0.002016059532946637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003398647980571769</v>
+        <v>0.003398647980571773</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003801562488129838</v>
+        <v>0.003801562488129844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002692453183958728</v>
+        <v>0.002692453183958736</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004706799360419379</v>
+        <v>0.004706799360419373</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004904452663301747</v>
+        <v>0.004904452663301718</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004368576579511767</v>
+        <v>0.004368576579511764</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00417775748611479</v>
+        <v>0.004177757486114785</v>
       </c>
       <c r="J4" t="n">
         <v>0.005380233465317245</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005512516784598425</v>
+        <v>0.005512516784598427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006797275801751675</v>
+        <v>0.006797275801751663</v>
       </c>
       <c r="M4" t="n">
         <v>0.004113123115439384</v>
@@ -1837,46 +1837,46 @@
         <v>0.005109619634379356</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007208357758245408</v>
+        <v>0.007208357758245403</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005453329943362465</v>
+        <v>0.005453329943362463</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003357824395748637</v>
+        <v>0.00335782439574864</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007984491652641066</v>
+        <v>0.007984491652641063</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005780028912733123</v>
+        <v>0.005780028912733116</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004766034838654265</v>
+        <v>0.004766034838654271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005953128198573938</v>
+        <v>0.005953128198573928</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005632625600327614</v>
+        <v>0.005632625600327621</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009190106190752214</v>
+        <v>0.009190106190752207</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02214442829211435</v>
+        <v>0.02214442829211429</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01384879800839739</v>
+        <v>0.01384879800839738</v>
       </c>
       <c r="Z4" t="n">
         <v>0.004636579194651794</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01235396893951928</v>
+        <v>0.01235396893951929</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002974924287597982</v>
+        <v>0.002974924287597993</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006309820495527577</v>
+        <v>0.0006309820495527587</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0006309820495527578</v>
+        <v>0.0006309820495527588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0006293749092632983</v>
+        <v>0.0006293749092632984</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="N5" t="n">
         <v>0.005109619634379356</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006309820495527578</v>
+        <v>0.0006309820495527588</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0006309820495527578</v>
+        <v>0.0006309820495527588</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0006309820495527578</v>
+        <v>0.0006309820495527588</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0006086842370133011</v>
+        <v>0.0006086842370133005</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006205983215136368</v>
+        <v>0.000620598321513637</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000630982049552758</v>
+        <v>0.0006309820495527597</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0006309820495527578</v>
+        <v>0.0006309820495527588</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006086842370133011</v>
+        <v>0.0006086842370133005</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0006309820495527581</v>
+        <v>0.0006309820495527596</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0006309820495527578</v>
+        <v>0.0006309820495527588</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001384327921540868</v>
+        <v>0.001983288832231882</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="N6" t="n">
         <v>0.005109619634379356</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002015111324665354</v>
+        <v>0.002015111324665357</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00134277753025351</v>
+        <v>0.001997835651778088</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001984895972521344</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001375551333791208</v>
+        <v>0.00197451224448222</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00144122127393762</v>
+        <v>0.001441221273937622</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001442993132988569</v>
+        <v>0.001442993132988576</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001984895972521338</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00138593506183033</v>
+        <v>0.001385935061830333</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001385895007177327</v>
+        <v>0.001385895007177331</v>
       </c>
     </row>
     <row r="7">
@@ -2086,7 +2086,7 @@
         <v>0.001068837487775741</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001067230347486281</v>
+        <v>0.00106723034748628</v>
       </c>
       <c r="K7" t="n">
         <v>0.001068837487775741</v>
@@ -2101,10 +2101,10 @@
         <v>0.005109619634379356</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001068787012470951</v>
+        <v>0.001068787012470952</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001068787012470951</v>
+        <v>0.001068787012470952</v>
       </c>
       <c r="Q7" t="n">
         <v>0.001068837487775741</v>
@@ -2119,10 +2119,10 @@
         <v>0.001068837487775741</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001068250954283859</v>
+        <v>0.001068250954283861</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001058453759736618</v>
+        <v>0.00105845375973662</v>
       </c>
       <c r="W7" t="n">
         <v>0.001068837487775741</v>
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001440185347233334</v>
+        <v>0.001440185347233338</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.001753557393465237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00154460592931731</v>
+        <v>0.001544605929317314</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002249442908343165</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002108850451693405</v>
+        <v>0.002108850451693414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.00211045759198282</v>
       </c>
       <c r="N8" t="n">
         <v>0.005109619634379356</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001733667673931582</v>
+        <v>0.001733667673931586</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001698668060079367</v>
+        <v>0.00169866806007937</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001308461552945237</v>
+        <v>0.001308461552945241</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001697616867703969</v>
+        <v>0.001782891223356566</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002100073863943741</v>
+        <v>0.001916420143653589</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00211058931959765</v>
+        <v>0.002110589319597654</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001369893335974976</v>
+        <v>0.00136989333597498</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002776183345358089</v>
+        <v>0.002776183345358098</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.001427734696175457</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002110457591982862</v>
+        <v>0.002110457591982872</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00281061299879768</v>
+        <v>0.002810612998797688</v>
       </c>
     </row>
     <row r="9">
@@ -2238,85 +2238,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001589147202893987</v>
+        <v>0.001589147202893989</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001845241806216858</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001154576766588167</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081739176099</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001920474343878283</v>
+        <v>0.00192047434387828</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="N9" t="n">
         <v>0.005109619634379356</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002032415808562173</v>
+        <v>0.002032415808562176</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002056411575637487</v>
+        <v>0.002056411575637491</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001922081739176098</v>
+        <v>0.001922081739176099</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001911697756128621</v>
+        <v>0.00229589702213577</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001721351819492181</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001922081484167741</v>
+        <v>0.001922081484167745</v>
       </c>
     </row>
     <row r="10">
@@ -2326,58 +2326,58 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00150699314122466</v>
+        <v>0.001506993141224661</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001486489376896218</v>
+        <v>0.001486489376896217</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001469028169091365</v>
+        <v>0.001469028169091366</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002729568929879083</v>
+        <v>0.002729568929879081</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001455353802540286</v>
+        <v>0.001455353802540288</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00136478250049364</v>
+        <v>0.001364782500493641</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001461705839551934</v>
+        <v>0.001461705839551936</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001462556665555301</v>
+        <v>0.001462556665555303</v>
       </c>
       <c r="J10" t="n">
         <v>0.00142403661149364</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001424203810548391</v>
+        <v>0.001424203810548392</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001384780495754537</v>
+        <v>0.001384780495754538</v>
       </c>
       <c r="M10" t="n">
         <v>0.001463449437956523</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001439470959531585</v>
+        <v>0.001439470959531586</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001367975196107303</v>
+        <v>0.001367975196107304</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001415784277938851</v>
+        <v>0.001415784277938852</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001476634527373297</v>
+        <v>0.001476634527373298</v>
       </c>
       <c r="R10" t="n">
         <v>0.001364472629643229</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001408201376407656</v>
+        <v>0.001408201376407657</v>
       </c>
       <c r="T10" t="n">
         <v>0.001449551465088391</v>
@@ -2389,22 +2389,22 @@
         <v>0.001352085957761707</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001340722157935726</v>
+        <v>0.001340722157935727</v>
       </c>
       <c r="X10" t="n">
         <v>0.001002048659950442</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001237442795983</v>
+        <v>0.001237442795983001</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001434823398735448</v>
+        <v>0.00143482339873545</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001270366273697382</v>
+        <v>0.001270366273697384</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001427722629813164</v>
+        <v>0.001427722629813165</v>
       </c>
     </row>
     <row r="11">
@@ -2417,31 +2417,31 @@
         <v>0.001496291035220512</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001496035434686019</v>
+        <v>0.001496035434686018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001485588688970407</v>
+        <v>0.001485588688970408</v>
       </c>
       <c r="E11" t="n">
         <v>0.002713222821249175</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001485332235701575</v>
+        <v>0.001485332235701574</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001414307613279281</v>
+        <v>0.001414307613279282</v>
       </c>
       <c r="H11" t="n">
         <v>0.001483599460861887</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00148377419027445</v>
+        <v>0.001483774190274449</v>
       </c>
       <c r="J11" t="n">
         <v>0.001472235566260105</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001474671411806689</v>
+        <v>0.001474671411806688</v>
       </c>
       <c r="L11" t="n">
         <v>0.001461392923873536</v>
@@ -2450,7 +2450,7 @@
         <v>0.001484053435182594</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00147711278824925</v>
+        <v>0.001477112788249251</v>
       </c>
       <c r="O11" t="n">
         <v>0.001456373324647116</v>
@@ -2459,7 +2459,7 @@
         <v>0.001470080380703297</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.00148772284874898</v>
+        <v>0.001487722848748981</v>
       </c>
       <c r="R11" t="n">
         <v>0.001445384134309271</v>
@@ -2471,22 +2471,22 @@
         <v>0.001480061759598037</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00146695956030319</v>
+        <v>0.001466959560303192</v>
       </c>
       <c r="V11" t="n">
         <v>0.001410023168236181</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001448855523578642</v>
+        <v>0.001448855523578641</v>
       </c>
       <c r="X11" t="n">
         <v>0.001337579182495524</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001419445499147911</v>
+        <v>0.001419445499147912</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001475990868380386</v>
+        <v>0.001475990868380388</v>
       </c>
       <c r="AA11" t="n">
         <v>0.001428801469327752</v>
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001703780183457467</v>
+        <v>0.001703780183457466</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001762359050578118</v>
+        <v>0.001762359050578119</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002840411893108084</v>
+        <v>0.002840411893108089</v>
       </c>
       <c r="F2" t="n">
         <v>0.001724722566569558</v>
@@ -2676,67 +2676,67 @@
         <v>0.001802424818753545</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001779037717944442</v>
+        <v>0.001779037717944441</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001784804426640119</v>
+        <v>0.001784804426640118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001828249760314593</v>
+        <v>0.001828249760314594</v>
       </c>
       <c r="N2" t="n">
         <v>0.001758765185067061</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001783601438380858</v>
+        <v>0.001783601438380857</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="V2" t="n">
         <v>0.001691871047185987</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="X2" t="n">
         <v>0.001779299763034164</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="Z2" t="n">
         <v>0.00172767537622912</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00178332397375459</v>
+        <v>0.001783323973754589</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001724763551843038</v>
+        <v>0.001724763551843037</v>
       </c>
     </row>
     <row r="3">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001718064315970998</v>
+        <v>0.001718064315970997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002855836399669177</v>
+        <v>0.002855836399669179</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001712733888557236</v>
+        <v>0.001712733888557235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001677497171659669</v>
+        <v>0.001677497171659668</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00170543307281636</v>
+        <v>0.001705433072816359</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001711339863163013</v>
+        <v>0.001711339863163012</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001710023434575891</v>
+        <v>0.00171002343457589</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001693385180427689</v>
+        <v>0.00169338518042769</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001705316113825281</v>
+        <v>0.00170531611382528</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001710092223341568</v>
+        <v>0.001710092223341566</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001709719817538709</v>
+        <v>0.001709719817538708</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001645637081974183</v>
+        <v>0.001645637081974182</v>
       </c>
     </row>
     <row r="4">
@@ -2834,43 +2834,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02675459903441579</v>
+        <v>0.02675459903441574</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007329468926866402</v>
+        <v>0.007329468926866394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02634580471957962</v>
+        <v>0.02634580471957956</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01135754874900303</v>
+        <v>0.01135754874900302</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01486037680444169</v>
+        <v>0.01486037680444171</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04172760573759069</v>
+        <v>0.04172760573759066</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01214201560548079</v>
+        <v>0.01214201560548082</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01942470371813001</v>
+        <v>0.01942470371813002</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03007246573193938</v>
+        <v>0.03007246573193937</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0391517589018066</v>
+        <v>0.03915175890180663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04473150270659512</v>
+        <v>0.04473150270659518</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04530384419774117</v>
+        <v>0.04530384419774124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03833146960272554</v>
+        <v>0.03833146960272549</v>
       </c>
       <c r="O4" t="n">
         <v>0.02399392614986987</v>
@@ -2879,40 +2879,40 @@
         <v>0.04210900062231681</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.015428172813907</v>
+        <v>0.01542817281390702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01195582202780087</v>
+        <v>0.01195582202780088</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02880881026552682</v>
+        <v>0.02880881026552692</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02401625718854281</v>
+        <v>0.02401625718854279</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03833146960272554</v>
+        <v>0.03833146960272549</v>
       </c>
       <c r="V4" t="n">
-        <v>0.009669971795911602</v>
+        <v>0.009669971795911595</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02555944807371583</v>
+        <v>0.02555944807371582</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03264135306540716</v>
+        <v>0.0326413530654072</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02897336708541362</v>
+        <v>0.02897336708541364</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01490556559903043</v>
+        <v>0.0149055655990304</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02697769367381156</v>
+        <v>0.02697769367381159</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06770055252464763</v>
+        <v>0.06770055252464753</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009413428800867374</v>
+        <v>0.000941342880086737</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009183265581844606</v>
+        <v>0.0009183265581844587</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0009282021152845325</v>
+        <v>0.0009282021152845288</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487897</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0009183265581844606</v>
+        <v>0.0009183265581844587</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0009437621665487898</v>
+        <v>0.00094376216654879</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009437621665487903</v>
+        <v>0.0009437621665487896</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002594177804327566</v>
+        <v>0.002594177804327564</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00178369635453326</v>
+        <v>0.001783696354533272</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002597999515764571</v>
+        <v>0.002597999515764574</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002598001799612175</v>
+        <v>0.00259800179961218</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002581037039525361</v>
+        <v>0.002581037039525355</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002597992573853414</v>
+        <v>0.002597992573853417</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="Y6" t="n">
         <v>0.001829177458795036</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001780937803551554</v>
+        <v>0.00259659709078962</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002596597090789619</v>
+        <v>0.001780937803551552</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001797348428948443</v>
+        <v>0.001797348428948444</v>
       </c>
     </row>
     <row r="7">
@@ -3098,85 +3098,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="J7" t="n">
         <v>0.00152393515641149</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001526298819812269</v>
+        <v>0.001526298819812267</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001526298819812269</v>
+        <v>0.001526298819812267</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001525589789387884</v>
+        <v>0.001525589789387885</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001510794391609284</v>
+        <v>0.001510794391609281</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001526354442873541</v>
+        <v>0.00152635444287354</v>
       </c>
     </row>
     <row r="8">
@@ -3186,85 +3186,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002020071041489751</v>
+        <v>0.00202007104148975</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002431921217281498</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002157306112721676</v>
+        <v>0.002157306112721675</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.00308364028070206</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002898559114652979</v>
+        <v>0.00289855911465298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401114979</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002218127824780905</v>
+        <v>0.002218127824780904</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002405781092184391</v>
+        <v>0.002405781092184389</v>
       </c>
       <c r="P8" t="n">
         <v>0.002359782742012072</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001846952639627757</v>
+        <v>0.001846952639627759</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002358397924186795</v>
+        <v>0.002470469794970594</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002885418349850774</v>
+        <v>0.002644047024261472</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002901151524523412</v>
+        <v>0.00290115152452341</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001927689549448493</v>
+        <v>0.001927689549448495</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003775904535589816</v>
+        <v>0.003775904535589814</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002003707735036179</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002900978401115035</v>
+        <v>0.002900978401115038</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003821159798400824</v>
+        <v>0.003821159798400821</v>
       </c>
     </row>
     <row r="9">
@@ -3277,82 +3277,82 @@
         <v>0.002953754388322241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003447301056412686</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.002116248294457564</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387319832884</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003592967822672283</v>
+        <v>0.00359296782267228</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003808023633191837</v>
+        <v>0.003808023633191833</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003854268383120186</v>
+        <v>0.003854268383120185</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003595387319832889</v>
+        <v>0.003595387319832884</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003579827057870075</v>
+        <v>0.004320257030741853</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003208539718358521</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003595387109134333</v>
+        <v>0.003595387109134329</v>
       </c>
     </row>
     <row r="10">
@@ -3362,73 +3362,73 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001097023509411305</v>
+        <v>0.001097023509411304</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001583307099327614</v>
+        <v>0.001583307099327615</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001187325530212419</v>
+        <v>0.001187325530212418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00262368555574619</v>
+        <v>0.002623685555746193</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001428327519855377</v>
+        <v>0.001428327519855376</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0007339097391583667</v>
+        <v>0.0007339097391583656</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001489461282157848</v>
+        <v>0.001489461282157846</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001334540736190999</v>
+        <v>0.001334540736190998</v>
       </c>
       <c r="J10" t="n">
         <v>0.001053580422068545</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0008607587721439634</v>
+        <v>0.000860758772143963</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0007516512551931881</v>
+        <v>0.0007516512551931869</v>
       </c>
       <c r="M10" t="n">
-        <v>0.000804817857152563</v>
+        <v>0.000804817857152561</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001206253362385387</v>
+        <v>0.001206253362385386</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001147863269749226</v>
+        <v>0.001147863269749224</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0007520976067029248</v>
+        <v>0.0007520976067029228</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001403405125070215</v>
+        <v>0.001403405125070214</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001489781717338903</v>
+        <v>0.001489781717338902</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001067598134938815</v>
+        <v>0.001067598134938812</v>
       </c>
       <c r="T10" t="n">
         <v>0.001234789633060042</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0008727748949798799</v>
+        <v>0.000872774894979879</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001485347062823744</v>
+        <v>0.001485347062823745</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001176118970297208</v>
+        <v>0.001176118970297207</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001040548012138975</v>
+        <v>0.001040548012138974</v>
       </c>
       <c r="Y10" t="n">
         <v>0.001096206228740585</v>
@@ -3440,7 +3440,7 @@
         <v>0.00114483383295966</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0003363421851151228</v>
+        <v>0.0003363421851151232</v>
       </c>
     </row>
     <row r="11">
@@ -3450,22 +3450,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001504545201009337</v>
+        <v>0.001504545201009336</v>
       </c>
       <c r="C11" t="n">
         <v>0.00164246522043896</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001524667985072844</v>
+        <v>0.001524667985072842</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002734782519302284</v>
+        <v>0.002734782519302285</v>
       </c>
       <c r="F11" t="n">
         <v>0.001595316762460894</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001373089529930724</v>
+        <v>0.001373089529930721</v>
       </c>
       <c r="H11" t="n">
         <v>0.001683105638233992</v>
@@ -3474,7 +3474,7 @@
         <v>0.00161261629611659</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001482442684523046</v>
+        <v>0.001482442684523045</v>
       </c>
       <c r="K11" t="n">
         <v>0.001397787319585346</v>
@@ -3486,25 +3486,25 @@
         <v>0.001416516484587454</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001529686343519906</v>
+        <v>0.001529686343519905</v>
       </c>
       <c r="O11" t="n">
         <v>0.001527677453979795</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001347602816063394</v>
+        <v>0.001347602816063393</v>
       </c>
       <c r="Q11" t="n">
         <v>0.001643949812514417</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00168339075516932</v>
+        <v>0.001683390755169318</v>
       </c>
       <c r="S11" t="n">
-        <v>0.00149115656185125</v>
+        <v>0.001491156561851249</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001567229226304099</v>
+        <v>0.001567229226304098</v>
       </c>
       <c r="U11" t="n">
         <v>0.001402511366805108</v>
@@ -3513,22 +3513,22 @@
         <v>0.001597213040698049</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001540533887774702</v>
+        <v>0.001540533887774701</v>
       </c>
       <c r="X11" t="n">
         <v>0.001476828158276652</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001504173335699641</v>
+        <v>0.00150417333569964</v>
       </c>
       <c r="Z11" t="n">
         <v>0.001581230552412603</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001526299050586302</v>
+        <v>0.001526299050586301</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001129030201296897</v>
+        <v>0.001129030201296896</v>
       </c>
     </row>
   </sheetData>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001696399739722295</v>
+        <v>0.001696399739722296</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001774153073995049</v>
+        <v>0.00177415307399505</v>
       </c>
       <c r="E2" t="n">
         <v>0.002837081263469096</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001721485232570078</v>
+        <v>0.001721485232570079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001781036900430969</v>
+        <v>0.00178103690043097</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="J2" t="n">
         <v>0.001764034644797247</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00176971602687051</v>
+        <v>0.001769716026870511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001768063085931507</v>
+        <v>0.001768063085931508</v>
       </c>
       <c r="N2" t="n">
         <v>0.001727544665121317</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001759642208757579</v>
+        <v>0.001759642208757581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="V2" t="n">
         <v>0.001694765540172456</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0017195817192918</v>
+        <v>0.001719581719291802</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001721142584143968</v>
+        <v>0.001721142584143969</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00176761611280941</v>
+        <v>0.001767616112809412</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001709055690897858</v>
+        <v>0.00170905569089786</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>0.001704599215617908</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0028514896339033</v>
+        <v>0.002851489633903302</v>
       </c>
       <c r="F3" t="n">
         <v>0.001708853046770436</v>
@@ -3830,7 +3830,7 @@
         <v>0.001704599215617908</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001695873344841875</v>
+        <v>0.001695873344841876</v>
       </c>
       <c r="S3" t="n">
         <v>0.001704599215617908</v>
@@ -3842,7 +3842,7 @@
         <v>0.001704599215617908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001686633043164052</v>
+        <v>0.001686633043164053</v>
       </c>
       <c r="W3" t="n">
         <v>0.001704599215617908</v>
@@ -3854,7 +3854,7 @@
         <v>0.001704599215617908</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001705225401699141</v>
+        <v>0.001705225401699142</v>
       </c>
       <c r="AA3" t="n">
         <v>0.001704599215617908</v>
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02004075581694948</v>
+        <v>0.02004075581694949</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006062778864213476</v>
+        <v>0.006062778864213482</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02876474176672335</v>
+        <v>0.02876474176672346</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01087020730316279</v>
+        <v>0.01087020730316282</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01385505374327216</v>
+        <v>0.01385505374327214</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03573557871398746</v>
+        <v>0.03573557871398751</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007627256494801909</v>
+        <v>0.007627256494801907</v>
       </c>
       <c r="I4" t="n">
         <v>0.02345112756759488</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02512296595691596</v>
+        <v>0.02512296595691598</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02565796046750531</v>
+        <v>0.02565796046750532</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0352300943180095</v>
+        <v>0.03523009431800953</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02760114858485467</v>
+        <v>0.02760114858485468</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03451078422768304</v>
+        <v>0.03451078422768323</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01811937901436666</v>
+        <v>0.0181193790143667</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03822954239767124</v>
+        <v>0.03822954239767146</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01212917768297534</v>
+        <v>0.01212917768297537</v>
       </c>
       <c r="R4" t="n">
         <v>0.007141663161469363</v>
       </c>
       <c r="S4" t="n">
-        <v>0.024693331619916</v>
+        <v>0.02469333161991603</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01905012441102713</v>
+        <v>0.0190501244110272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03451078422768305</v>
+        <v>0.03451078422768323</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01104831890860981</v>
+        <v>0.01104831890860985</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02335468584758478</v>
+        <v>0.02335468584758473</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03505427055417741</v>
+        <v>0.03505427055417755</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04334508678389833</v>
+        <v>0.04334508678389837</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01278437401152445</v>
+        <v>0.01278437401152444</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02598851720047078</v>
+        <v>0.0259885172004708</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05939868715405535</v>
+        <v>0.05939868715405536</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787027</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787028</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0008879381295429461</v>
+        <v>0.0008879381295429446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0008901262771787027</v>
+        <v>0.0008901262771787028</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787028</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787028</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787028</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0008688608597463315</v>
+        <v>0.0008688608597463327</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008760558851572437</v>
+        <v>0.0008760558851572434</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787031</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787028</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0008688608597463315</v>
+        <v>0.0008688608597463327</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0008901262771787025</v>
+        <v>0.000890126277178703</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0008901262771787026</v>
+        <v>0.0008901262771787028</v>
       </c>
     </row>
     <row r="6">
@@ -4046,82 +4046,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002419689121108508</v>
+        <v>0.00241968912110851</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="N6" t="n">
         <v>0.001678716414270264</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002423692177592768</v>
+        <v>0.001678716414270264</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00242369131837778</v>
+        <v>0.002423691318377781</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="V6" t="n">
         <v>0.002407806876722809</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002423686850698026</v>
+        <v>0.001733018196378363</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001721794599575941</v>
+        <v>0.001721794599575939</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002421877268744265</v>
+        <v>0.001675873651961765</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001675873651961763</v>
+        <v>0.002421877268744268</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001689910087460393</v>
@@ -4191,10 +4191,10 @@
         <v>0.001420652620232181</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001419958791028724</v>
+        <v>0.001419958791028723</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001406582228210724</v>
+        <v>0.001406582228210722</v>
       </c>
       <c r="W7" t="n">
         <v>0.001420652620232181</v>
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001870137399933534</v>
+        <v>0.001870137399933535</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002245886232662279</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001995342925767511</v>
+        <v>0.001995342925767512</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002840477886960117</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002671639359955672</v>
+        <v>0.002671639359955673</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591376</v>
       </c>
       <c r="N8" t="n">
         <v>0.002050833219699706</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002222037459320913</v>
+        <v>0.002222037459320917</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002180071163321708</v>
+        <v>0.002180071163321711</v>
       </c>
       <c r="Q8" t="n">
         <v>0.001712193950478572</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002178811433520467</v>
+        <v>0.002281059717278001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002659757115569967</v>
+        <v>0.00243954790035824</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002673985455607614</v>
+        <v>0.002673985455607617</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001785853745729623</v>
+        <v>0.001785853745729624</v>
       </c>
       <c r="Y8" t="n">
         <v>0.003472067423788327</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.001855208443578144</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002673827507591425</v>
+        <v>0.002673827507591426</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003513349028404666</v>
+        <v>0.003513349028404669</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002576780641944826</v>
+        <v>0.00257678064194483</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.002996177438925456</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.001865100478896192</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015396246871</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003119826900154455</v>
+        <v>0.003119826900154457</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00330270547990134</v>
+        <v>0.003302705479901342</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003342002472974127</v>
+        <v>0.003342002472974125</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003122015396246869</v>
+        <v>0.003122015396246871</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003107944655768757</v>
+        <v>0.003737133462547451</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.00279328732356891</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003122015047790217</v>
+        <v>0.003122015047790213</v>
       </c>
     </row>
     <row r="10">
@@ -4398,40 +4398,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001225194934866964</v>
+        <v>0.001225194934866965</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00159438346096788</v>
+        <v>0.001594383460967881</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001083407081486401</v>
+        <v>0.0010834070814864</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002613559128693975</v>
+        <v>0.002613559128693972</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001420351709357998</v>
+        <v>0.001420351709357999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000786712720459566</v>
+        <v>0.0007867127204595674</v>
       </c>
       <c r="H10" t="n">
         <v>0.001563352095096698</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001211007454650075</v>
+        <v>0.001211007454650074</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001112132373324341</v>
+        <v>0.001112132373324339</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001088456319696307</v>
+        <v>0.001088456319696305</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008940727469921768</v>
+        <v>0.0008940727469921784</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001121303464975922</v>
+        <v>0.001121303464975923</v>
       </c>
       <c r="N10" t="n">
         <v>0.001354941961243159</v>
@@ -4440,7 +4440,7 @@
         <v>0.001250149778619776</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0007603981305613717</v>
+        <v>0.0007603981305613686</v>
       </c>
       <c r="Q10" t="n">
         <v>0.001444495510733884</v>
@@ -4449,25 +4449,25 @@
         <v>0.001561813278041227</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001110702721235901</v>
+        <v>0.001110702721235898</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001304379387663694</v>
+        <v>0.001304379387663693</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0008869272463233486</v>
+        <v>0.000886927246323346</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001421875451571747</v>
+        <v>0.001421875451571748</v>
       </c>
       <c r="W10" t="n">
         <v>0.00118217656997744</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0008790958291238988</v>
+        <v>0.0008790958291238954</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0007091319878500819</v>
+        <v>0.0007091319878500801</v>
       </c>
       <c r="Z10" t="n">
         <v>0.001393425353866109</v>
@@ -4476,7 +4476,7 @@
         <v>0.001121691213555391</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004136983817983364</v>
+        <v>0.0004136983817983359</v>
       </c>
     </row>
     <row r="11">
@@ -4486,16 +4486,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00154948563729694</v>
+        <v>0.001549485637296941</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001642263818897443</v>
+        <v>0.001642263818897445</v>
       </c>
       <c r="D11" t="n">
         <v>0.001491508673343341</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002728822125359323</v>
+        <v>0.00272882212535932</v>
       </c>
       <c r="F11" t="n">
         <v>0.001590216204648211</v>
@@ -4504,7 +4504,7 @@
         <v>0.001380821223016213</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001703348222844397</v>
+        <v>0.001703348222844399</v>
       </c>
       <c r="I11" t="n">
         <v>0.00154303028858544</v>
@@ -4522,46 +4522,46 @@
         <v>0.001502661660536139</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001568449500089253</v>
+        <v>0.001568449500089254</v>
       </c>
       <c r="O11" t="n">
         <v>0.001560840170730836</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001338001610118365</v>
+        <v>0.001338001610118364</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001649268098185856</v>
+        <v>0.001649268098185857</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001698644451139201</v>
+        <v>0.001698644451139203</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001497391315229767</v>
+        <v>0.001497391315229768</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001585514815665328</v>
+        <v>0.001585514815665329</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001395572761014433</v>
+        <v>0.001395572761014432</v>
       </c>
       <c r="V11" t="n">
         <v>0.001574299992265575</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001529912144180809</v>
+        <v>0.001529912144180811</v>
       </c>
       <c r="X11" t="n">
         <v>0.001367891877531739</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001314675351809227</v>
+        <v>0.001314675351809226</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001579272568732143</v>
+        <v>0.001579272568732144</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001502391114253386</v>
+        <v>0.001502391114253387</v>
       </c>
       <c r="AB11" t="n">
         <v>0.00115084954655451</v>
@@ -4736,10 +4736,10 @@
         <v>0.001704776935640387</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001750912976649311</v>
+        <v>0.00175091297664931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002865578173828791</v>
+        <v>0.002865578173828789</v>
       </c>
       <c r="F2" t="n">
         <v>0.001742917953883308</v>
@@ -4754,10 +4754,10 @@
         <v>0.001769105585941319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001767239665039558</v>
+        <v>0.001767239665039559</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001771797586056955</v>
+        <v>0.001771797586056954</v>
       </c>
       <c r="L2" t="n">
         <v>0.001769105585941319</v>
@@ -4766,7 +4766,7 @@
         <v>0.001765185203530768</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001717707988815462</v>
+        <v>0.001717707988815461</v>
       </c>
       <c r="O2" t="n">
         <v>0.001769105585941319</v>
@@ -4778,7 +4778,7 @@
         <v>0.001769105585941319</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001753734421516224</v>
+        <v>0.001753734421516223</v>
       </c>
       <c r="S2" t="n">
         <v>0.001769105585941319</v>
@@ -4796,19 +4796,19 @@
         <v>0.001769105585941319</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001747084237026679</v>
+        <v>0.001747084237026678</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001769105585941319</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00172602269560087</v>
+        <v>0.001726022695600869</v>
       </c>
       <c r="AA2" t="n">
         <v>0.001769105585941319</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001710545164029768</v>
+        <v>0.001710545164029767</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001723301072164791</v>
+        <v>0.00172330107216479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002892214974886522</v>
+        <v>0.00289221497488652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001720217510454407</v>
+        <v>0.001720217510454406</v>
       </c>
       <c r="G3" t="n">
         <v>0.001648866114185695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001712705740229312</v>
+        <v>0.001712705740229314</v>
       </c>
       <c r="K3" t="n">
         <v>0.001717517721222447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001697751185626969</v>
+        <v>0.001697751185626968</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="V3" t="n">
         <v>0.001658265371670327</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001690473875380819</v>
+        <v>0.001690473875380818</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001715188005587005</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001714571872900097</v>
+        <v>0.001714571872900096</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001650489137335571</v>
+        <v>0.00165048913733557</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0169989042661527</v>
+        <v>0.01699890426615273</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005542461565283807</v>
+        <v>0.005542461565283812</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01918657598040253</v>
+        <v>0.01918657598040254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007473607065337569</v>
+        <v>0.007473607065337576</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01625381355772937</v>
+        <v>0.01625381355772935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03068352317806649</v>
+        <v>0.03068352317806653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007601968294799262</v>
+        <v>0.007601968294799273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02232572552217075</v>
+        <v>0.02232572552217077</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02244838903101331</v>
+        <v>0.02244838903101334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03008635532636147</v>
+        <v>0.03008635532636154</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02899080970251283</v>
+        <v>0.02899080970251286</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02312344475676053</v>
+        <v>0.02312344475676055</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03643046999490655</v>
+        <v>0.03643046999490653</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01525853715995475</v>
+        <v>0.01525853715995474</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03317602446813658</v>
+        <v>0.03317602446813663</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01241623583260651</v>
+        <v>0.01241623583260652</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01079209383597833</v>
+        <v>0.01079209383597835</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02291513983470045</v>
+        <v>0.0229151398347005</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01999552334174861</v>
+        <v>0.0199955233417486</v>
       </c>
       <c r="U4" t="n">
         <v>0.03643046999490653</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01706984852211593</v>
+        <v>0.01706984852211592</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01763422717952481</v>
+        <v>0.0176342271795248</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03571741102816006</v>
+        <v>0.03571741102816021</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07155403852300894</v>
+        <v>0.07155403852300893</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01101996984770751</v>
+        <v>0.01101996984770752</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02837800466552973</v>
+        <v>0.02837800466552979</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05352942985538776</v>
+        <v>0.05352942985538778</v>
       </c>
     </row>
     <row r="5">
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="C5" t="n">
         <v>0.0009442475758692308</v>
@@ -5006,7 +5006,7 @@
         <v>0.0009442475758692308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="G5" t="n">
         <v>0.0009442475758692308</v>
@@ -5018,7 +5018,7 @@
         <v>0.0009442475758692308</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009423652145681034</v>
+        <v>0.0009423652145681035</v>
       </c>
       <c r="K5" t="n">
         <v>0.0009442475758692308</v>
@@ -5030,16 +5030,16 @@
         <v>0.0009442475758692308</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="R5" t="n">
         <v>0.0009442475758692308</v>
@@ -5051,19 +5051,19 @@
         <v>0.0009442475758692308</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009282730313594334</v>
+        <v>0.0009282730313594339</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0009321199006693337</v>
+        <v>0.0009321199006693342</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0009282730313594334</v>
+        <v>0.0009282730313594339</v>
       </c>
       <c r="Z5" t="n">
         <v>0.0009442475758692308</v>
@@ -5072,7 +5072,7 @@
         <v>0.0009442475758692308</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000944247575869231</v>
+        <v>0.0009442475758692306</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001836884933230915</v>
+        <v>0.002620876272440283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001844318184561097</v>
+        <v>0.001844318184561084</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001844318184561096</v>
+        <v>0.002630108781073821</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00263010784812744</v>
+        <v>0.001774446361506654</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002610630958541513</v>
+        <v>0.001826639619332143</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002630105888197181</v>
+        <v>0.002630105888197178</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001838767294532042</v>
+        <v>0.001838767294532041</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001896144160489117</v>
+        <v>0.001896144160489107</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002622758633741408</v>
+        <v>0.002622758633741409</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00185230706183365</v>
+        <v>0.001852307061833649</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001436667458101493</v>
+        <v>0.001436667458101491</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001438496821546397</v>
+        <v>0.001438496821546396</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001438496821546397</v>
+        <v>0.001438496821546396</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001438073563176857</v>
+        <v>0.001438073563176856</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001426422144202724</v>
+        <v>0.001426422144202722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001438549819402622</v>
+        <v>0.001438549819402621</v>
       </c>
     </row>
     <row r="8">
@@ -5261,82 +5261,82 @@
         <v>0.001932763060055364</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.002327350430359275</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002064245888165898</v>
+        <v>0.002064245888165896</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.002951752522500958</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002774864601027756</v>
+        <v>0.002774864601027754</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.002776746962328855</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002122518242603874</v>
+        <v>0.002122518242603872</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002302305975296194</v>
+        <v>0.002302305975296193</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002258235657739055</v>
+        <v>0.002258235657739052</v>
       </c>
       <c r="Q8" t="n">
         <v>0.001766900960296674</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00225709521219671</v>
+        <v>0.002364481669237983</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002764619287128985</v>
+        <v>0.002533583970054602</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002776912829228183</v>
+        <v>0.002776912829228178</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001844253761888413</v>
+        <v>0.001844253761888412</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003615339808045587</v>
+        <v>0.003615339808045582</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.001917085625777224</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002776746962328882</v>
+        <v>0.00277674696232888</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003658358720930392</v>
+        <v>0.003658358720930388</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002467780644647567</v>
+        <v>0.00246778064464756</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002864158294658978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.001795161987042377</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089469537797</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002981206780581682</v>
+        <v>0.002981206780581681</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003153862139369858</v>
+        <v>0.003153862139369859</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003191002265090432</v>
+        <v>0.003191002265090433</v>
       </c>
       <c r="Q9" t="n">
         <v>0.002983089469537797</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002970961466682908</v>
+        <v>0.003565616504774393</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002672404071177688</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002983089141882808</v>
+        <v>0.002983089141882803</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001298815879288726</v>
+        <v>0.001298815879288725</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001616329910326742</v>
+        <v>0.001616329910326741</v>
       </c>
       <c r="D10" t="n">
         <v>0.001290756609443406</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002726554461667607</v>
+        <v>0.002726554461667608</v>
       </c>
       <c r="F10" t="n">
         <v>0.001375148044606296</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0008709171131759876</v>
+        <v>0.0008709171131759854</v>
       </c>
       <c r="H10" t="n">
         <v>0.001574246301039151</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001237404689015241</v>
+        <v>0.001237404689015239</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001177325492579187</v>
+        <v>0.001177325492579186</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0009881447569550397</v>
+        <v>0.0009881447569550386</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001024819811200634</v>
+        <v>0.001024819811200632</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001209084313100525</v>
+        <v>0.001209084313100524</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001484283371797705</v>
+        <v>0.001484283371797704</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001337115706305927</v>
+        <v>0.001337115706305925</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0008687331598208199</v>
+        <v>0.0008687331598208169</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001441362651380002</v>
+        <v>0.001441362651379999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001485323086629484</v>
+        <v>0.001485323086629482</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001157655522643828</v>
+        <v>0.001157655522643827</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00129408470888114</v>
+        <v>0.001294084708881136</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0008177995982873106</v>
+        <v>0.0008177995982873091</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001229171462163318</v>
+        <v>0.001229171462163319</v>
       </c>
       <c r="W10" t="n">
         <v>0.001325925531581567</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0008770199018272925</v>
+        <v>0.0008770199018272881</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.112629827861499e-05</v>
+        <v>9.112629827861273e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001436469298496882</v>
+        <v>0.001436469298496881</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001079843940345707</v>
+        <v>0.001079843940345704</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0005302888334141985</v>
+        <v>0.000530288833414198</v>
       </c>
     </row>
     <row r="11">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001579935283912409</v>
+        <v>0.001579935283912408</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00165610471610721</v>
+        <v>0.001656104716107209</v>
       </c>
       <c r="D11" t="n">
         <v>0.001558075681157409</v>
@@ -5537,19 +5537,19 @@
         <v>0.001585910247251278</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001395383443136924</v>
+        <v>0.001395383443136923</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001705257003553525</v>
+        <v>0.001705257003553524</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001551992996632122</v>
+        <v>0.00155199299663212</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001523639946203134</v>
+        <v>0.001523639946203133</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001439930562941562</v>
+        <v>0.001439930562941561</v>
       </c>
       <c r="L11" t="n">
         <v>0.001455266199758664</v>
@@ -5561,37 +5561,37 @@
         <v>0.001612925986927967</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001597361827259543</v>
+        <v>0.001597361827259542</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001384246275962207</v>
+        <v>0.001384246275962206</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001644794519483547</v>
+        <v>0.001644794519483546</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001657078959504184</v>
+        <v>0.001657078959504183</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001515706871787613</v>
+        <v>0.001515706871787611</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001577782586299612</v>
+        <v>0.001577782586299611</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00136107134314883</v>
+        <v>0.001361071343148829</v>
       </c>
       <c r="V11" t="n">
         <v>0.001499965648060504</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001592270262098987</v>
+        <v>0.001592270262098986</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001376960086735823</v>
+        <v>0.001376960086735821</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001030432675874471</v>
+        <v>0.00103043267587447</v>
       </c>
       <c r="Z11" t="n">
         <v>0.001599204795651044</v>
@@ -5769,7 +5769,7 @@
         <v>0.001637404259752312</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001610833623211542</v>
+        <v>0.001610833623211543</v>
       </c>
       <c r="D2" t="n">
         <v>0.001643380964634409</v>
@@ -5790,10 +5790,10 @@
         <v>0.001637404259752312</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001635759021988619</v>
+        <v>0.00163575902198862</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001638884712637841</v>
+        <v>0.001638884712637842</v>
       </c>
       <c r="L2" t="n">
         <v>0.001637404259752312</v>
@@ -5826,13 +5826,13 @@
         <v>0.001637404259752312</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001607588017739471</v>
+        <v>0.001607588017739469</v>
       </c>
       <c r="W2" t="n">
         <v>0.001637404259752312</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001633380049031886</v>
+        <v>0.001633380049031887</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001637404259752312</v>
@@ -5854,85 +5854,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001641624753643082</v>
+        <v>0.001641624753643081</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="E3" t="n">
         <v>0.00280946162900175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00163629432622932</v>
+        <v>0.001636294326229319</v>
       </c>
       <c r="G3" t="n">
         <v>0.001601057609331753</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001631634831564877</v>
+        <v>0.001631634831564878</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001634900300835097</v>
+        <v>0.001634900300835096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001633583872247975</v>
+        <v>0.001633583872247974</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001626465417360924</v>
+        <v>0.001626465417360922</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="X3" t="n">
         <v>0.001628876551497365</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001633652661013651</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001633280255210793</v>
+        <v>0.001633280255210792</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001569197519646267</v>
+        <v>0.001569197519646266</v>
       </c>
     </row>
     <row r="4">
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005858547551684155</v>
+        <v>0.005858547551684156</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002418312538094821</v>
+        <v>0.00241831253809482</v>
       </c>
       <c r="D4" t="n">
         <v>0.01364507263000529</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006823937066617482</v>
+        <v>0.006823937066617487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00576497280814263</v>
+        <v>0.00576497280814264</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01171694881835598</v>
+        <v>0.01171694881835601</v>
       </c>
       <c r="H4" t="n">
         <v>0.01013429165063959</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01036159514259321</v>
+        <v>0.0103615951425932</v>
       </c>
       <c r="J4" t="n">
         <v>0.01077498397550685</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01753150808698892</v>
+        <v>0.01753150808698889</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01602523653470207</v>
+        <v>0.01602523653470209</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01550337599418529</v>
+        <v>0.0155033759941853</v>
       </c>
       <c r="N4" t="n">
         <v>0.01781886169517928</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006440832900263666</v>
+        <v>0.006440832900263651</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01390869441666367</v>
+        <v>0.01390869441666366</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00980532403313991</v>
+        <v>0.009805324033139912</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008991123334072008</v>
+        <v>0.008991123334071999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009094472734398888</v>
+        <v>0.009094472734398885</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007741043606748444</v>
+        <v>0.007741043606748445</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01781886169517929</v>
+        <v>0.01781886169517928</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005023819689398108</v>
+        <v>0.005023819689398096</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01689427351116992</v>
+        <v>0.01689427351116994</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01417063665486337</v>
+        <v>0.01417063665486338</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0068682354700563</v>
+        <v>0.006868235470056262</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008555820736464517</v>
+        <v>0.008555820736464506</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01485465541520411</v>
+        <v>0.01485465541520412</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01781875405535397</v>
+        <v>0.01781875405535398</v>
       </c>
     </row>
     <row r="5">
@@ -6030,85 +6030,85 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="F5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0007146262265785906</v>
+        <v>0.0007146262265785907</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007164831806461247</v>
+        <v>0.0007164831806461248</v>
       </c>
       <c r="N5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="U5" t="n">
+        <v>0.0007058043099856221</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0007045116767780917</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.0007164831806461245</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0007058043099856221</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0007058043099856218</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.0007045116767780897</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>0.0007164831806461248</v>
       </c>
-      <c r="X5" t="n">
-        <v>0.0007164831806461248</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0007058043099856218</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0007164831806461247</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0.0007164831806461248</v>
+        <v>0.0007164831806461245</v>
       </c>
     </row>
     <row r="6">
@@ -6118,82 +6118,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001526887629744535</v>
+        <v>0.001526887629744528</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00152941163097273</v>
+        <v>0.001529411630972728</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002218178579535369</v>
+        <v>0.002218178579535371</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002218178701437086</v>
+        <v>0.001467930017785864</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002214215834450853</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001516773079944037</v>
+        <v>0.002202244330582819</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001586068025643231</v>
+        <v>0.001586068025643213</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.001528744583812062</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001574952265523366</v>
+        <v>0.001574952265523381</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001528744583812064</v>
+        <v>0.002214215834450854</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001531985247960628</v>
@@ -6230,7 +6230,7 @@
         <v>0.00121667168446346</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001214814730395925</v>
+        <v>0.001214814730395926</v>
       </c>
       <c r="K7" t="n">
         <v>0.00121667168446346</v>
@@ -6245,10 +6245,10 @@
         <v>0.00121667168446346</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001216616819249454</v>
+        <v>0.001216616819249455</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001216616819249454</v>
+        <v>0.001216616819249455</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00121667168446346</v>
@@ -6263,10 +6263,10 @@
         <v>0.00121667168446346</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001216125166060051</v>
+        <v>0.00121612516606005</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001204700180595424</v>
+        <v>0.001204700180595426</v>
       </c>
       <c r="W7" t="n">
         <v>0.00121667168446346</v>
@@ -6297,82 +6297,82 @@
         <v>0.001638258238656271</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.001994403240585257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001756931454263186</v>
+        <v>0.001756931454263185</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002557973443406236</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002398160710070772</v>
+        <v>0.002398160710070773</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138235</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001809526669787784</v>
+        <v>0.001809526669787783</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001971798722133183</v>
+        <v>0.00197179872213318</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00193202192106605</v>
+        <v>0.001932021921066049</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001488555125263337</v>
+        <v>0.001488555125263336</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0019309128054911</v>
+        <v>0.002027832036438418</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002388046160270271</v>
+        <v>0.002179425570312274</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002400167371594074</v>
+        <v>0.00240016737159407</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001558371890188243</v>
+        <v>0.001558371890188244</v>
       </c>
       <c r="Y8" t="n">
         <v>0.003156765909190287</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.001624108166246896</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002400017664138307</v>
+        <v>0.002400017664138306</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003195739081252535</v>
+        <v>0.003195739081252534</v>
       </c>
     </row>
     <row r="9">
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002232523509791061</v>
+        <v>0.002232523509791062</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002613976102666221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.001585231385847064</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728429087162053</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="J9" t="n">
         <v>0.002726571883633754</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="O9" t="n">
         <v>0.002892771546172794</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002928513211363407</v>
+        <v>0.002928513211363406</v>
       </c>
       <c r="Q9" t="n">
         <v>0.002728429087162053</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002716457333833257</v>
+        <v>0.003288721479239903</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002429442121651948</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00272842883770129</v>
+        <v>0.002728428837701292</v>
       </c>
     </row>
     <row r="10">
@@ -6476,10 +6476,10 @@
         <v>0.001607426859531036</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001363809239027831</v>
+        <v>0.00136380923902783</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002672219605922046</v>
+        <v>0.002672219605922048</v>
       </c>
       <c r="F10" t="n">
         <v>0.001532322001097164</v>
@@ -6491,13 +6491,13 @@
         <v>0.001447579341432804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00143568410857119</v>
+        <v>0.001435684108571191</v>
       </c>
       <c r="J10" t="n">
         <v>0.001394889008143594</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001250372519041076</v>
+        <v>0.001250372519041075</v>
       </c>
       <c r="L10" t="n">
         <v>0.001257123045466417</v>
@@ -6506,7 +6506,7 @@
         <v>0.001302608713468922</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001321813505725329</v>
+        <v>0.00132181350572533</v>
       </c>
       <c r="O10" t="n">
         <v>0.001494561574243159</v>
@@ -6515,10 +6515,10 @@
         <v>0.001323642272667998</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001432550673645405</v>
+        <v>0.001432550673645404</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001468274282881364</v>
+        <v>0.001468274282881365</v>
       </c>
       <c r="S10" t="n">
         <v>0.001416013501576984</v>
@@ -6527,16 +6527,16 @@
         <v>0.001483519885525351</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001240695055879465</v>
+        <v>0.001240695055879466</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001525224804738145</v>
+        <v>0.001525224804738144</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001282613433266955</v>
+        <v>0.001282613433266956</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001344322097852643</v>
+        <v>0.001344322097852644</v>
       </c>
       <c r="Y10" t="n">
         <v>0.001499566657184608</v>
@@ -6545,10 +6545,10 @@
         <v>0.001442939528572079</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001326465640662044</v>
+        <v>0.001326465640662043</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00122104747403207</v>
+        <v>0.001221047474032069</v>
       </c>
     </row>
     <row r="11">
@@ -6561,31 +6561,31 @@
         <v>0.001582101844696113</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001595273472408339</v>
+        <v>0.00159527347240834</v>
       </c>
       <c r="D11" t="n">
         <v>0.001520770793517986</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002715721483280845</v>
+        <v>0.002715721483280847</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001570661041822524</v>
+        <v>0.001570661041822525</v>
       </c>
       <c r="G11" t="n">
         <v>0.001488718035280409</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001552909752189627</v>
+        <v>0.001552909752189629</v>
       </c>
       <c r="I11" t="n">
         <v>0.001547497383329735</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001528038917867763</v>
+        <v>0.001528038917867764</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001463923346504229</v>
+        <v>0.00146392334650423</v>
       </c>
       <c r="L11" t="n">
         <v>0.001466251530576719</v>
@@ -6594,13 +6594,13 @@
         <v>0.00150358791761529</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001508607751030262</v>
+        <v>0.001508607751030263</v>
       </c>
       <c r="O11" t="n">
         <v>0.001574286817841832</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001496517990937635</v>
+        <v>0.001496517990937636</v>
       </c>
       <c r="Q11" t="n">
         <v>0.001546071660452839</v>
@@ -6609,16 +6609,16 @@
         <v>0.001562465334406368</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001538547194460865</v>
+        <v>0.001538547194460866</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001569262814287454</v>
+        <v>0.001569262814287455</v>
       </c>
       <c r="U11" t="n">
         <v>0.001458776742961761</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001561523216361418</v>
+        <v>0.001561523216361416</v>
       </c>
       <c r="W11" t="n">
         <v>0.001477849738259012</v>
@@ -6630,10 +6630,10 @@
         <v>0.001576564146530442</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.00154303339443199</v>
+        <v>0.001543033394431991</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001497802632372468</v>
+        <v>0.001497802632372469</v>
       </c>
       <c r="AB11" t="n">
         <v>0.001420434457597935</v>
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="C2" t="n">
         <v>0.001607863458234383</v>
@@ -6811,19 +6811,19 @@
         <v>0.001603938037423131</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002763982640006346</v>
+        <v>0.002763982640006345</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001610685424709523</v>
+        <v>0.001610685424709522</v>
       </c>
       <c r="G2" t="n">
         <v>0.001571655994357001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="J2" t="n">
         <v>0.001607781772245174</v>
@@ -6832,52 +6832,52 @@
         <v>0.001610487967522086</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00159810681970143</v>
+        <v>0.001598106819701429</v>
       </c>
       <c r="N2" t="n">
         <v>0.001611531184655478</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="R2" t="n">
         <v>0.001600414149409155</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001601322887288069</v>
+        <v>0.001601322887288068</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="X2" t="n">
         <v>0.001560353659943377</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="Z2" t="n">
         <v>0.001614211861935446</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001608388053460987</v>
+        <v>0.001608388053460986</v>
       </c>
       <c r="AB2" t="n">
         <v>0.001549827631549435</v>
@@ -6899,7 +6899,7 @@
         <v>0.001623123921327366</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002800424835389489</v>
+        <v>0.00280042483538949</v>
       </c>
       <c r="F3" t="n">
         <v>0.001627377752479894</v>
@@ -6914,7 +6914,7 @@
         <v>0.001623123921327366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001622517573336311</v>
+        <v>0.001622517573336312</v>
       </c>
       <c r="K3" t="n">
         <v>0.001625421846499672</v>
@@ -6950,7 +6950,7 @@
         <v>0.001623123921327366</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00161526929966376</v>
+        <v>0.001615269299663759</v>
       </c>
       <c r="W3" t="n">
         <v>0.001623123921327366</v>
@@ -6978,67 +6978,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003115620705537463</v>
+        <v>0.003115620705537459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003862085210146505</v>
+        <v>0.003862085210146509</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004866814452282001</v>
+        <v>0.004866814452281993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005010448920120428</v>
+        <v>0.005010448920120433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005652955665412513</v>
+        <v>0.005652955665412524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004954216573413753</v>
+        <v>0.004954216573413751</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005789367567704453</v>
+        <v>0.005789367567704456</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005544850437045815</v>
+        <v>0.00554485043704582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00559775513449406</v>
+        <v>0.005597755134494064</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004213531994907932</v>
+        <v>0.004213531994907934</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004638811101445585</v>
+        <v>0.00463881110144559</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003418588032807542</v>
+        <v>0.003418588032807547</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002873937848517037</v>
+        <v>0.002873937848517041</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006386758037215922</v>
+        <v>0.006386758037215916</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005106274458861889</v>
+        <v>0.005106274458861886</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003238104697128603</v>
+        <v>0.003238104697128604</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008804315420259803</v>
+        <v>0.008804315420259799</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005319536518287559</v>
+        <v>0.005319536518287564</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003575358364618508</v>
+        <v>0.003575358364618502</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002873937848517034</v>
+        <v>0.002873937848517039</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005617874511918238</v>
+        <v>0.005617874511918248</v>
       </c>
       <c r="W4" t="n">
         <v>0.01059671808625667</v>
@@ -7047,16 +7047,16 @@
         <v>0.02056567065678996</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00687522935959497</v>
+        <v>0.006875229359594959</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006575956014337109</v>
+        <v>0.006575956014337117</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009404550068005583</v>
+        <v>0.009404550068005564</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002236881166883545</v>
+        <v>0.002236881166883542</v>
       </c>
     </row>
     <row r="5">
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="C5" t="n">
         <v>0.0006473219795784613</v>
@@ -7078,7 +7078,7 @@
         <v>0.0006473219795784613</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="G5" t="n">
         <v>0.0006473219795784613</v>
@@ -7090,7 +7090,7 @@
         <v>0.0006473219795784613</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0006457604858543421</v>
+        <v>0.0006457604858543416</v>
       </c>
       <c r="K5" t="n">
         <v>0.0006473219795784613</v>
@@ -7102,16 +7102,16 @@
         <v>0.0006473219795784613</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="R5" t="n">
         <v>0.0006473219795784613</v>
@@ -7123,19 +7123,19 @@
         <v>0.0006473219795784613</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0006420878297628683</v>
+        <v>0.000642087829762869</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006372493750505417</v>
+        <v>0.000637249375050544</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006420878297628683</v>
+        <v>0.0006420878297628689</v>
       </c>
       <c r="Z5" t="n">
         <v>0.0006473219795784613</v>
@@ -7144,7 +7144,7 @@
         <v>0.0006473219795784613</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0006473219795784581</v>
+        <v>0.00064732197957846</v>
       </c>
     </row>
     <row r="6">
@@ -7154,82 +7154,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002021106141419999</v>
+        <v>0.001406047742247251</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001407590725461005</v>
+        <v>0.001407590725460999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001407590725461005</v>
+        <v>0.001407590725461004</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002024745994955049</v>
+        <v>0.001350327012185156</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001397536631443453</v>
+        <v>0.0020125950306162</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001459939314012752</v>
+        <v>0.001459939314012743</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.001407609235971369</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00145093729578052</v>
+        <v>0.001450937295780517</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002022667635144116</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001407609235971372</v>
+        <v>0.002022667635144115</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001406596607138634</v>
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001091274680225218</v>
+        <v>0.001091274680225219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001092784929074493</v>
+        <v>0.001092784929074492</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001092784929074493</v>
+        <v>0.001092784929074491</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001092390095810953</v>
+        <v>0.001092390095810952</v>
       </c>
       <c r="V7" t="n">
         <v>0.00108276356942142</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00109283617394934</v>
+        <v>0.001092836173949337</v>
       </c>
     </row>
     <row r="8">
@@ -7330,40 +7330,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001468373784199449</v>
+        <v>0.001468373784199448</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.001787686906454762</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001574774027916905</v>
+        <v>0.001574774027916904</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002292973685995413</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0021497919174295</v>
+        <v>0.002149791917429502</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.00215135341115352</v>
       </c>
       <c r="N8" t="n">
         <v>0.001621929940239945</v>
@@ -7372,43 +7372,43 @@
         <v>0.00176742010691317</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001731756951530572</v>
+        <v>0.001731756951530573</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001334152699274196</v>
+        <v>0.001334152699274194</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001730795993580229</v>
+        <v>0.001817694184729001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0021412808066257</v>
+        <v>0.001954274682746602</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002151487636138827</v>
+        <v>0.002151487636138825</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001396749139136498</v>
+        <v>0.001396749139136499</v>
       </c>
       <c r="Y8" t="n">
         <v>0.002829901055422853</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.001455687086992157</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00215135341115362</v>
+        <v>0.002151353411153618</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.002864782741261354</v>
+        <v>0.002864782741261351</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001853966472308579</v>
+        <v>0.001853966472308578</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002164653328534712</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.001326757695111854</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873399922152</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002256311606393994</v>
+        <v>0.002256311606393989</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002391727626865045</v>
+        <v>0.002391727626865041</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002420838624671031</v>
+        <v>0.002420838624671028</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002257873399922156</v>
+        <v>0.002257873399922152</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002247800495590193</v>
+        <v>0.002713900377944151</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002014353439376634</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002257873100118113</v>
+        <v>0.002257873100118108</v>
       </c>
     </row>
     <row r="10">
@@ -7509,25 +7509,25 @@
         <v>0.001561752405005568</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001558303015027172</v>
+        <v>0.001558303015027173</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001525709880368745</v>
+        <v>0.001525709880368743</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002694044609710132</v>
+        <v>0.002694044609710133</v>
       </c>
       <c r="F10" t="n">
         <v>0.001513770078821999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001469790090879249</v>
+        <v>0.00146979009087925</v>
       </c>
       <c r="H10" t="n">
         <v>0.00151365473119109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001513642506732981</v>
+        <v>0.001513642506732984</v>
       </c>
       <c r="J10" t="n">
         <v>0.001497838260272704</v>
@@ -7539,7 +7539,7 @@
         <v>0.001515711472429911</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001560108377773925</v>
+        <v>0.001560108377773926</v>
       </c>
       <c r="N10" t="n">
         <v>0.001480630389300398</v>
@@ -7554,19 +7554,19 @@
         <v>0.001559711611780649</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00143470670622316</v>
+        <v>0.001434706706223159</v>
       </c>
       <c r="S10" t="n">
         <v>0.001496311642371136</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001557017052034105</v>
+        <v>0.001557017052034106</v>
       </c>
       <c r="U10" t="n">
         <v>0.001569049840529364</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001485590010891631</v>
+        <v>0.00148559001089163</v>
       </c>
       <c r="W10" t="n">
         <v>0.001378671559232285</v>
@@ -7575,10 +7575,10 @@
         <v>0.001089356718540593</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0014787644302965</v>
+        <v>0.001478764430296501</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001467261821145165</v>
+        <v>0.001467261821145166</v>
       </c>
       <c r="AA10" t="n">
         <v>0.00141918771483847</v>
@@ -7600,13 +7600,13 @@
         <v>0.001574382338073503</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001559614338346828</v>
+        <v>0.001559614338346829</v>
       </c>
       <c r="E11" t="n">
         <v>0.00271557929830858</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001558993571149003</v>
+        <v>0.001558993571149002</v>
       </c>
       <c r="G11" t="n">
         <v>0.001519314215870175</v>
@@ -7618,16 +7618,16 @@
         <v>0.001558573660923975</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001551052287471838</v>
+        <v>0.001551052287471837</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001571981238888866</v>
+        <v>0.001571981238888864</v>
       </c>
       <c r="L11" t="n">
         <v>0.001559515046909479</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001569434546565992</v>
+        <v>0.001569434546565991</v>
       </c>
       <c r="N11" t="n">
         <v>0.001546696173483263</v>
@@ -7642,7 +7642,7 @@
         <v>0.001579535250534191</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001518654015097497</v>
+        <v>0.001518654015097498</v>
       </c>
       <c r="S11" t="n">
         <v>0.001550688062409147</v>
@@ -7654,7 +7654,7 @@
         <v>0.001583784174374026</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001542318397633378</v>
+        <v>0.001542318397633377</v>
       </c>
       <c r="W11" t="n">
         <v>0.00149716144968427</v>
@@ -7666,13 +7666,13 @@
         <v>0.001542704024995541</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001543009192987007</v>
+        <v>0.001543009192987006</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.00151559642960241</v>
+        <v>0.001515596429602411</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001534749002995531</v>
+        <v>0.00153474900299553</v>
       </c>
     </row>
   </sheetData>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="C2" t="n">
         <v>0.001614138001790396</v>
@@ -7847,76 +7847,76 @@
         <v>0.001609730922058468</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00282017626064538</v>
+        <v>0.002820176260645375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00161623079855509</v>
+        <v>0.001616230798555089</v>
       </c>
       <c r="G2" t="n">
         <v>0.001546938073909625</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001611423638868526</v>
+        <v>0.001611423638868525</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001614401493757734</v>
+        <v>0.001614401493757733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001603587744902122</v>
+        <v>0.001603587744902121</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001610453437996191</v>
+        <v>0.00161045343799619</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001596338329217004</v>
+        <v>0.001596338329217002</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001563239464092534</v>
+        <v>0.001563239464092532</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001589688144727458</v>
+        <v>0.001589688144727457</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001614500961367311</v>
+        <v>0.00161450096136731</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001611709493642099</v>
+        <v>0.001611709493642098</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001553149071730547</v>
+        <v>0.001553149071730546</v>
       </c>
     </row>
     <row r="3">
@@ -7926,85 +7926,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001637185562830236</v>
+        <v>0.001637185562830237</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002850114873857533</v>
+        <v>0.00285011487385753</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001634102001119852</v>
+        <v>0.001634102001119853</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001562750604851141</v>
+        <v>0.001562750604851142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001628170478633741</v>
+        <v>0.00162817047863374</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001631402211887893</v>
+        <v>0.001631402211887894</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001611635676292414</v>
+        <v>0.001611635676292415</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001573431026765544</v>
+        <v>0.001573431026765543</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001604358366046264</v>
+        <v>0.001604358366046265</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00162907249625245</v>
+        <v>0.001629072496252452</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001628456363565542</v>
+        <v>0.001628456363565543</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001564373628001016</v>
+        <v>0.001564373628001017</v>
       </c>
     </row>
     <row r="4">
@@ -8014,82 +8014,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004377874190044305</v>
+        <v>0.004377874190044308</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004013976176933975</v>
+        <v>0.004013976176933977</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004931528283680367</v>
+        <v>0.004931528283680366</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006403654748598017</v>
+        <v>0.006403654748598014</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005380176689404058</v>
+        <v>0.005380176689404065</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003902137731642804</v>
+        <v>0.003902137731642785</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004250866715301106</v>
+        <v>0.004250866715301105</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004124459388686203</v>
+        <v>0.0041244593886862</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005143928499090092</v>
+        <v>0.005143928499090089</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003599863225536815</v>
+        <v>0.003599863225536808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005318128955361305</v>
+        <v>0.005318128955361308</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003430141322350081</v>
+        <v>0.00343014132235008</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003204312711983837</v>
+        <v>0.003204312711983835</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006920823774377474</v>
+        <v>0.006920823774377484</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006132153018479351</v>
+        <v>0.006132153018479347</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002985312064125545</v>
+        <v>0.002985312064125543</v>
       </c>
       <c r="R4" t="n">
-        <v>0.009891878355158102</v>
+        <v>0.009891878355158101</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005028252503448957</v>
+        <v>0.005028252503448954</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003393212376239021</v>
+        <v>0.003393212376239022</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003204312711983836</v>
+        <v>0.003204312711983835</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006293727786636746</v>
+        <v>0.006293727786636758</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009086044890887367</v>
+        <v>0.009086044890887369</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02488838453101434</v>
+        <v>0.02488838453101428</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006639866579954766</v>
+        <v>0.006639866579954782</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00529789677074939</v>
+        <v>0.005297896770749395</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01025413348744964</v>
+        <v>0.01025413348744963</v>
       </c>
       <c r="AB4" t="n">
         <v>0.003310711649878729</v>
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0007088051685621111</v>
+        <v>0.0007088051685621115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0007097114263590321</v>
+        <v>0.0007097114263590322</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007003238980812352</v>
+        <v>0.0007003238980812361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0007097114263590321</v>
+        <v>0.0007097114263590322</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0007103589549091742</v>
+        <v>0.0007103589549091754</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007103589549091741</v>
+        <v>0.0007103589549091754</v>
       </c>
     </row>
     <row r="6">
@@ -8202,22 +8202,22 @@
         <v>0.002232779544880808</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001570671711538778</v>
+        <v>0.002232779544880808</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001570671711538778</v>
+        <v>0.002232779544880808</v>
       </c>
       <c r="H6" t="n">
         <v>0.001570671711538778</v>
       </c>
       <c r="I6" t="n">
+        <v>0.001570671711538778</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.001569117925191715</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.002232779544880808</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.002231225758533748</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.001570671711538778</v>
       </c>
       <c r="L6" t="n">
         <v>0.002232779544880808</v>
@@ -8226,19 +8226,19 @@
         <v>0.002232779544880808</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001570170749488193</v>
+        <v>0.001570170749488188</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001570170749488182</v>
+        <v>0.002231451132717758</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002231447706597312</v>
+        <v>0.002231447706597311</v>
       </c>
       <c r="Q6" t="n">
         <v>0.002232779544880808</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002232779544880808</v>
+        <v>0.001570671711538778</v>
       </c>
       <c r="S6" t="n">
         <v>0.001570671711538778</v>
@@ -8253,19 +8253,19 @@
         <v>0.001560636654710839</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002231453976389281</v>
+        <v>0.002231453976389278</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002232779544880808</v>
+        <v>0.001570671711538778</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001620302737711238</v>
+        <v>0.001620302737711236</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002232779544880808</v>
+        <v>0.001570671711538778</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002232779544880808</v>
+        <v>0.001570671711538778</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001569413427439607</v>
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="J7" t="n">
         <v>0.00112035239035332</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001121853910487717</v>
+        <v>0.001121853910487718</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001121853910487717</v>
+        <v>0.001121853910487718</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001121468006549001</v>
+        <v>0.001121468006549</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001111871119872444</v>
+        <v>0.001111871119872442</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001121906176700383</v>
+        <v>0.001121906176700382</v>
       </c>
     </row>
     <row r="8">
@@ -8366,85 +8366,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001542124396646007</v>
+        <v>0.001542124396646005</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.001879474974989298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00165453500946645</v>
+        <v>0.001654535009466448</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.002413304546744791</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002262130596697011</v>
+        <v>0.002262130596697008</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.002263684383043959</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001704354679208392</v>
+        <v>0.00170435467920839</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001858063338362636</v>
+        <v>0.001858063338362634</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001820385631886021</v>
+        <v>0.001820385631886017</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00140032139053396</v>
+        <v>0.001400321390533958</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001819393118857905</v>
+        <v>0.001911201518111172</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002253649326216133</v>
+        <v>0.002056106240947999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00226382619017973</v>
+        <v>0.002263826190179724</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001466453797002706</v>
+        <v>0.001466453797002702</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002980603438684675</v>
+        <v>0.002980603438684668</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.001528721049453544</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002263684383044074</v>
+        <v>0.00226368438304407</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003017414124633879</v>
+        <v>0.003017414124633875</v>
       </c>
     </row>
     <row r="9">
@@ -8457,82 +8457,82 @@
         <v>0.001801869247015164</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002098701491875822</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.001298170549405379</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764554897302</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="J9" t="n">
         <v>0.002186210475334412</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002315649754645404</v>
+        <v>0.002315649754645409</v>
       </c>
       <c r="P9" t="n">
         <v>0.002343462591447782</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002187764554897299</v>
+        <v>0.002187764554897302</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002177729204853534</v>
+        <v>0.00262304405838867</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.001955103999394121</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002187764261681475</v>
+        <v>0.002187764261681477</v>
       </c>
     </row>
     <row r="10">
@@ -8548,16 +8548,16 @@
         <v>0.001560747057063045</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001531196260531155</v>
+        <v>0.001531196260531153</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00270404136905421</v>
+        <v>0.002704041369054206</v>
       </c>
       <c r="F10" t="n">
         <v>0.001529503951979809</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001480362841828036</v>
+        <v>0.001480362841828035</v>
       </c>
       <c r="H10" t="n">
         <v>0.001552302269235018</v>
@@ -8569,7 +8569,7 @@
         <v>0.001518395973077325</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001564064840663421</v>
+        <v>0.001564064840663422</v>
       </c>
       <c r="L10" t="n">
         <v>0.001507163250940491</v>
@@ -8581,16 +8581,16 @@
         <v>0.00152653257395464</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001464448250275681</v>
+        <v>0.00146444825027568</v>
       </c>
       <c r="P10" t="n">
         <v>0.001486206688353347</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001574031974959325</v>
+        <v>0.001574031974959324</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001410275538661625</v>
+        <v>0.001410275538661626</v>
       </c>
       <c r="S10" t="n">
         <v>0.001516130178029138</v>
@@ -8599,16 +8599,16 @@
         <v>0.001567894903834321</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001566149050691728</v>
+        <v>0.001566149050691727</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001428654830842643</v>
+        <v>0.001428654830842642</v>
       </c>
       <c r="W10" t="n">
         <v>0.001425460415292528</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001009325423092488</v>
+        <v>0.00100932542309249</v>
       </c>
       <c r="Y10" t="n">
         <v>0.001491372185129652</v>
@@ -8630,19 +8630,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001569088070690976</v>
+        <v>0.001569088070690974</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001579358238071261</v>
+        <v>0.00157935823807126</v>
       </c>
       <c r="D11" t="n">
         <v>0.001565477265228264</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002753712350451224</v>
+        <v>0.002753712350451222</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001568638352862166</v>
+        <v>0.001568638352862165</v>
       </c>
       <c r="G11" t="n">
         <v>0.00150945137917989</v>
@@ -8651,19 +8651,19 @@
         <v>0.001577059138033011</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001577050018346195</v>
+        <v>0.001577050018346194</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001561475889009764</v>
+        <v>0.001561475889009765</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00158376277525913</v>
+        <v>0.001583762775259129</v>
       </c>
       <c r="L11" t="n">
         <v>0.001556520740859485</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001575813546348767</v>
+        <v>0.001575813546348766</v>
       </c>
       <c r="N11" t="n">
         <v>0.001564077788911384</v>
@@ -8672,43 +8672,43 @@
         <v>0.001537085279432364</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001546985438097733</v>
+        <v>0.001546985438097732</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001586946223386035</v>
+        <v>0.001586946223386034</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001504718824898311</v>
+        <v>0.00150471882489831</v>
       </c>
       <c r="S11" t="n">
         <v>0.00156060072126072</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001584153836466473</v>
+        <v>0.001584153836466471</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001583359467722888</v>
+        <v>0.001583359467722886</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001497365833573254</v>
+        <v>0.001497365833573252</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001519345690268172</v>
+        <v>0.001519345690268171</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001318946259426015</v>
+        <v>0.001318946259426014</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001549335755592411</v>
+        <v>0.00154933575559241</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001558226069121541</v>
+        <v>0.00155822606912154</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001510434962143611</v>
+        <v>0.00151043496214361</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001527627029315406</v>
+        <v>0.001527627029315405</v>
       </c>
     </row>
   </sheetData>
@@ -8877,19 +8877,19 @@
         <v>0.001755662417147765</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001678183342910447</v>
+        <v>0.001678183342910446</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001725036854155963</v>
+        <v>0.001725036854155962</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002821017841780543</v>
+        <v>0.002821017841780544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001695253461733123</v>
+        <v>0.001695253461733122</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001779284082923319</v>
+        <v>0.001779284082923317</v>
       </c>
       <c r="H2" t="n">
         <v>0.001755662417147765</v>
@@ -8907,7 +8907,7 @@
         <v>0.001755662417147765</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001809758979210427</v>
+        <v>0.001809758979210425</v>
       </c>
       <c r="N2" t="n">
         <v>0.00176114800346602</v>
@@ -8934,13 +8934,13 @@
         <v>0.001755662417147765</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001670827955663479</v>
+        <v>0.001670827955663478</v>
       </c>
       <c r="W2" t="n">
         <v>0.001755662417147765</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00175163820642734</v>
+        <v>0.001751638206427339</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001755662417147765</v>
@@ -8952,7 +8952,7 @@
         <v>0.001755662417147765</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001697101995236214</v>
+        <v>0.001697101995236213</v>
       </c>
     </row>
     <row r="3">
@@ -8962,85 +8962,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00170175840382849</v>
+        <v>0.001701758403828489</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002844436692403065</v>
+        <v>0.002844436692403066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001696427976414728</v>
+        <v>0.001696427976414727</v>
       </c>
       <c r="G3" t="n">
         <v>0.001661191259517161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001689238504821355</v>
+        <v>0.001689238504821354</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001695033951020505</v>
+        <v>0.001695033951020504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001693717522433383</v>
+        <v>0.001693717522433382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="V3" t="n">
         <v>0.001677768311011509</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="X3" t="n">
         <v>0.001689010201682773</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00169378631119906</v>
+        <v>0.001693786311199059</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001693413905396201</v>
+        <v>0.0016934139053962</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001629331169831675</v>
+        <v>0.001629331169831674</v>
       </c>
     </row>
     <row r="4">
@@ -9050,85 +9050,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01687576626983555</v>
+        <v>0.01687576626983554</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004702523039827174</v>
+        <v>0.004702523039827155</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02027046370981508</v>
+        <v>0.02027046370981506</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00913613398955089</v>
+        <v>0.009136133989550887</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01092143488089378</v>
+        <v>0.01092143488089375</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03815189061010068</v>
+        <v>0.03815189061010066</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01166858310934033</v>
+        <v>0.01166858310934032</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01955843465242835</v>
+        <v>0.01955843465242834</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02602367976763257</v>
+        <v>0.02602367976763259</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02668531020618415</v>
+        <v>0.0266853102061841</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03837164914846875</v>
+        <v>0.0383716491484687</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04110887996775687</v>
+        <v>0.04110887996775686</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03346480798813301</v>
+        <v>0.03346480798813316</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01522503303467461</v>
+        <v>0.01522503303467463</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03237175373597036</v>
+        <v>0.03237175373597025</v>
       </c>
       <c r="Q4" t="n">
         <v>0.01295060649820405</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01327702382454149</v>
+        <v>0.01327702382454151</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01849349100253069</v>
+        <v>0.01849349100253065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0187460812277235</v>
+        <v>0.01874608122772349</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03346480798813301</v>
+        <v>0.03346480798813314</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00823956856192077</v>
+        <v>0.008239568561920761</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01708709367584622</v>
+        <v>0.0170870936758462</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03338045616495586</v>
+        <v>0.03338045616495587</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02507692111248276</v>
+        <v>0.02507692111248272</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01345861744428276</v>
+        <v>0.01345861744428274</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02409572764836456</v>
+        <v>0.02409572764836454</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0585849430175906</v>
+        <v>0.0585849430175905</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0008951062787879627</v>
+        <v>0.000895106278787957</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.000897494174439201</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0008734944930306704</v>
+        <v>0.0008734944930306502</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008821327198859806</v>
+        <v>0.00088213271988598</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0008734944930306704</v>
+        <v>0.0008734944930306502</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0008974941744392123</v>
+        <v>0.0008974941744392011</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.000897494174439212</v>
+        <v>0.0008974941744392009</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002519465729943711</v>
+        <v>0.001720447087628289</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001725303151307187</v>
+        <v>0.001725303151307168</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001725303151307184</v>
+        <v>0.001725303151307168</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002527273474626442</v>
+        <v>0.002527273474626423</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001707473528726312</v>
+        <v>0.002506492171041731</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001781442448061843</v>
+        <v>0.001781442448061828</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001770130628087823</v>
+        <v>0.001770130628087906</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001722834983279546</v>
+        <v>0.001722834983279533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002521853625594977</v>
+        <v>0.002521853625594954</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001737337774832953</v>
+        <v>0.001737337774832941</v>
       </c>
     </row>
     <row r="7">
@@ -9314,85 +9314,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001458060555456306</v>
+        <v>0.001458060555456294</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001460392985253179</v>
+        <v>0.001460392985253163</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001460392985253179</v>
+        <v>0.001460392985253163</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001459653665862792</v>
+        <v>0.001459653665862762</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001445086996554318</v>
+        <v>0.001445086996554319</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001460448451107557</v>
+        <v>0.00146044845110754</v>
       </c>
     </row>
     <row r="8">
@@ -9402,85 +9402,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001938889841340588</v>
+        <v>0.00193888984134057</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002338540984300975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002072059999557588</v>
+        <v>0.00207205999955757</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002970956080601119</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002791316763819021</v>
+        <v>0.002791316763819015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470195</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002131080167982612</v>
+        <v>0.00213108016798259</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002313175131650727</v>
+        <v>0.002313175131650703</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002268539256031335</v>
+        <v>0.00226853925603131</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001770899219415313</v>
+        <v>0.001770899219415281</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002267158132993346</v>
+        <v>0.002375908001372141</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002778343204917036</v>
+        <v>0.002544077474088772</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002793872654947795</v>
+        <v>0.00279387265494777</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001849244695962021</v>
+        <v>0.001849244695962003</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003642647418016486</v>
+        <v>0.003642647418016473</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.001923011217241068</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002793704659470284</v>
+        <v>0.002793704659470261</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003686630215342259</v>
+        <v>0.00368663021534224</v>
       </c>
     </row>
     <row r="9">
@@ -9490,85 +9490,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002842244943926751</v>
+        <v>0.002842244943926749</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003320604214830524</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.00203051055214437</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.00346413357401887</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003461745517853792</v>
+        <v>0.003461745517853784</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003670226651740684</v>
+        <v>0.003670226651740671</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003715048360180974</v>
+        <v>0.003715048360180965</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003464133574018887</v>
+        <v>0.00346413357401887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003448771958951805</v>
+        <v>0.004166417448949415</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003089190030568083</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003464133413505048</v>
+        <v>0.003464133413505032</v>
       </c>
     </row>
     <row r="10">
@@ -9584,58 +9584,58 @@
         <v>0.001622434251963333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001295070102310971</v>
+        <v>0.00129507010231097</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002660058914114242</v>
+        <v>0.002660058914114243</v>
       </c>
       <c r="F10" t="n">
         <v>0.001489691453394902</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0007592041169776795</v>
+        <v>0.0007592041169776787</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0014813110757582</v>
+        <v>0.001481311075758199</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0013103272459715</v>
+        <v>0.001310327245971501</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001105525573906815</v>
+        <v>0.001105525573906814</v>
       </c>
       <c r="K10" t="n">
         <v>0.001101060911599564</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008424568137623471</v>
+        <v>0.0008424568137623473</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0008022046281109835</v>
+        <v>0.0008022046281109841</v>
       </c>
       <c r="N10" t="n">
         <v>0.001080965468402179</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001343166730872298</v>
+        <v>0.001343166730872299</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0009604135821022907</v>
+        <v>0.0009604135821022914</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001432662790121046</v>
+        <v>0.001432662790121045</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001446098512020487</v>
+        <v>0.001446098512020486</v>
       </c>
       <c r="S10" t="n">
         <v>0.001261732007465589</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001325794488214371</v>
+        <v>0.00132579448821437</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0009594090936001975</v>
+        <v>0.0009594090936001945</v>
       </c>
       <c r="V10" t="n">
         <v>0.001502886704105234</v>
@@ -9644,19 +9644,19 @@
         <v>0.001342424954097448</v>
       </c>
       <c r="X10" t="n">
-        <v>0.00100707918635485</v>
+        <v>0.001007079186354848</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001162710557458132</v>
+        <v>0.001162710557458131</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001397569742980853</v>
+        <v>0.001397569742980852</v>
       </c>
       <c r="AA10" t="n">
         <v>0.00118944985200372</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004934433647277491</v>
+        <v>0.0004934433647277478</v>
       </c>
     </row>
     <row r="11">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001582348852471757</v>
+        <v>0.001582348852471756</v>
       </c>
       <c r="C11" t="n">
         <v>0.001642090601020729</v>
@@ -9675,34 +9675,34 @@
         <v>0.001543789154305806</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002737125365082017</v>
+        <v>0.002737125365082018</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001601187684928894</v>
+        <v>0.001601187684928893</v>
       </c>
       <c r="G11" t="n">
         <v>0.001368877058605382</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001659154953730863</v>
+        <v>0.001659154953730862</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001581356766284783</v>
+        <v>0.001581356766284782</v>
       </c>
       <c r="J11" t="n">
         <v>0.001485896248866249</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001486883244217004</v>
+        <v>0.001486883244217003</v>
       </c>
       <c r="L11" t="n">
         <v>0.001368474228615016</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001404255917930205</v>
+        <v>0.001404255917930204</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001482482012876377</v>
+        <v>0.001482482012876376</v>
       </c>
       <c r="O11" t="n">
         <v>0.001596298836567873</v>
@@ -9711,37 +9711,37 @@
         <v>0.001422144934115609</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.00163701982873307</v>
+        <v>0.001637019828733069</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001643272442921202</v>
+        <v>0.001643272442921201</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001559245777900754</v>
+        <v>0.001559245777900753</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001588394410796464</v>
+        <v>0.001588394410796463</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00142168788864604</v>
+        <v>0.001421687888646039</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001591256267206511</v>
+        <v>0.00159125626720651</v>
       </c>
       <c r="W11" t="n">
         <v>0.001595961325771413</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001441357421267934</v>
+        <v>0.001441357421267933</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001514190702584723</v>
+        <v>0.001514190702584722</v>
       </c>
       <c r="Z11" t="n">
         <v>0.001572437389123898</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001526357166816044</v>
+        <v>0.001526357166816043</v>
       </c>
       <c r="AB11" t="n">
         <v>0.001180269424054274</v>
@@ -9910,85 +9910,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001638158042291195</v>
+        <v>0.001638158042291191</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001637179651288986</v>
+        <v>0.001637179651288991</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002781705189783673</v>
+        <v>0.00278170518978367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00163646072144117</v>
+        <v>0.001636460721441172</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001707219078275907</v>
+        <v>0.001707219078275906</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001670168959863042</v>
+        <v>0.001670168959863044</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001675624838319181</v>
+        <v>0.001675624838319178</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001639039660453879</v>
+        <v>0.001639039660453876</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001643954656646778</v>
+        <v>0.001643954656646784</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00166555102020625</v>
+        <v>0.001665551020206247</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001617002330746848</v>
+        <v>0.001617002330746849</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001625490530740472</v>
+        <v>0.001625490530740469</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001638212808022229</v>
+        <v>0.001638212808022227</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001673524924258081</v>
+        <v>0.001673524924258078</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00161496450234653</v>
+        <v>0.001614964502346527</v>
       </c>
     </row>
     <row r="3">
@@ -9998,85 +9998,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001662370824671188</v>
+        <v>0.001662370824671191</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="E3" t="n">
         <v>0.002819230744832341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001657861198032864</v>
+        <v>0.001657861198032867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001615309606517107</v>
+        <v>0.00161530960651711</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001650251020592849</v>
+        <v>0.001650251020592848</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001655905292052641</v>
+        <v>0.001655905292052644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001644881496104303</v>
+        <v>0.001644881496104306</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001633681509757649</v>
+        <v>0.001633681509757648</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001601043273899921</v>
+        <v>0.001601043273899924</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00165423355296157</v>
+        <v>0.001654233552961573</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001653607366880336</v>
+        <v>0.001653607366880339</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00158952463131581</v>
+        <v>0.001589524631315813</v>
       </c>
     </row>
     <row r="4">
@@ -10086,85 +10086,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002442103909227052</v>
+        <v>0.002442103909227056</v>
       </c>
       <c r="C4" t="n">
         <v>0.00398638682427275</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005840706356555686</v>
+        <v>0.005840706356555681</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00485579289868598</v>
+        <v>0.004855792898685986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004669137777980391</v>
+        <v>0.004669137777980403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02808255830800577</v>
+        <v>0.02808255830800558</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005911811948809294</v>
+        <v>0.005911811948809274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005426044280549261</v>
+        <v>0.005426044280549265</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01352905442059288</v>
+        <v>0.01352905442059285</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007545608878419919</v>
+        <v>0.007545608878419926</v>
       </c>
       <c r="L4" t="n">
         <v>0.01552539154930921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006143461494816285</v>
+        <v>0.006143461494816292</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006872070166487459</v>
+        <v>0.006872070166487446</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005291893797459553</v>
+        <v>0.005291893797459577</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01757661130200139</v>
+        <v>0.0175766113020014</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006765198492719119</v>
+        <v>0.006765198492719114</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00938728170211396</v>
+        <v>0.009387281702113963</v>
       </c>
       <c r="S4" t="n">
         <v>0.007039150824673794</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005153893324123873</v>
+        <v>0.005153893324123869</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00687207016648746</v>
+        <v>0.006872070166487447</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005204656193669129</v>
+        <v>0.005204656193669138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01310866543523944</v>
+        <v>0.01310866543523943</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02240214696299505</v>
+        <v>0.02240214696299504</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02900534907343494</v>
+        <v>0.02900534907343492</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005324639789257855</v>
+        <v>0.005324639789257863</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008588915339544423</v>
+        <v>0.008588915339544454</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03435128798317157</v>
+        <v>0.03435128798317149</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0007506629840304001</v>
+        <v>0.0007506629840303952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000733068684369886</v>
+        <v>0.0007330686843698904</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007390931019872329</v>
+        <v>0.000739093101987231</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000733068684369886</v>
+        <v>0.0007330686843698904</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0007527918582490019</v>
+        <v>0.0007527918582490064</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0007527918582489982</v>
+        <v>0.0007527918582490067</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002203121624264925</v>
+        <v>0.001501932492410452</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001504819709125271</v>
+        <v>0.001504819709125244</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002209697187010536</v>
+        <v>0.001504819709125233</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001447002895208237</v>
+        <v>0.001447002895208211</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002191551742221748</v>
+        <v>0.002191551742221752</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001557574128770759</v>
+        <v>0.001557574128770767</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001546107592956554</v>
+        <v>0.001546107592956604</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001504061366629071</v>
+        <v>0.001504061366629063</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002205250498483535</v>
+        <v>0.002205250498483529</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001512963067310463</v>
+        <v>0.001512963067310455</v>
       </c>
     </row>
     <row r="7">
@@ -10350,85 +10350,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001231856145112445</v>
+        <v>0.001231856145112438</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001233933621318987</v>
+        <v>0.001233933621318975</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001233933621318987</v>
+        <v>0.001233933621318975</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001233202539644883</v>
+        <v>0.001233202539644885</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001220286263069246</v>
+        <v>0.001220286263069273</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00123398501933104</v>
+        <v>0.00123398501933105</v>
       </c>
     </row>
     <row r="8">
@@ -10438,85 +10438,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001644973315429321</v>
+        <v>0.001644973315429327</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.001990947547610848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001760257467746604</v>
+        <v>0.001760257467746601</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002538423342980907</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002382849582117773</v>
+        <v>0.002382849582117763</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336308</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001811350671941944</v>
+        <v>0.001811350671941935</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001968988567765174</v>
+        <v>0.001968988567765183</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00193034771043911</v>
+        <v>0.001930347710439095</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001499545415476419</v>
+        <v>0.001499545415476418</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001929085821828169</v>
+        <v>0.002023225253382494</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002371279700074603</v>
+        <v>0.002168400226558924</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002385123888442005</v>
+        <v>0.002385123888442017</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001567368356987123</v>
+        <v>0.001567368356987121</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003119779487276624</v>
+        <v>0.003119779487276621</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.001631227340026274</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002384978456336369</v>
+        <v>0.002384978456336373</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003157975704137723</v>
+        <v>0.003157975704137722</v>
       </c>
     </row>
     <row r="9">
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002242281280100856</v>
+        <v>0.002242281280100854</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002617097828311223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.001606249951144079</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559700067665</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002727430426056774</v>
+        <v>0.002727430426056784</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002891043130410761</v>
+        <v>0.00289104313041076</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002926163005918995</v>
+        <v>0.002926163005918997</v>
       </c>
       <c r="Q9" t="n">
         <v>0.002729559700067665</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002715860544013622</v>
+        <v>0.003278169272901947</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002435774143315508</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002729559300275394</v>
+        <v>0.002729559300275396</v>
       </c>
     </row>
     <row r="10">
@@ -10614,85 +10614,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001612092337363108</v>
+        <v>0.00161209233736311</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001588767575660366</v>
+        <v>0.001588767575660372</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001538912165915878</v>
+        <v>0.001538912165915879</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00271914982189933</v>
+        <v>0.002719149821899326</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001570577576575818</v>
+        <v>0.001570577576575824</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0008743416898504078</v>
+        <v>0.0008743416898504096</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00154543539190078</v>
+        <v>0.001545435391900784</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001551368703567501</v>
+        <v>0.001551368703567499</v>
       </c>
       <c r="J10" t="n">
         <v>0.001318683783458857</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00148848737975662</v>
+        <v>0.001488487379756621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001272941759279746</v>
+        <v>0.001272941759279749</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001528495689518895</v>
+        <v>0.001528495689518889</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001498572040314734</v>
+        <v>0.001498572040314737</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001535861630068493</v>
+        <v>0.001535861630068498</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001222372281324611</v>
+        <v>0.001222372281324606</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001505509668435061</v>
+        <v>0.00150550966843506</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001458769430070772</v>
+        <v>0.001458769430070776</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001488977301893192</v>
+        <v>0.001488977301893194</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001556007912362561</v>
+        <v>0.001556007912362566</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00150017183869388</v>
+        <v>0.001500171838693886</v>
       </c>
       <c r="V10" t="n">
-        <v>0.00151943347835182</v>
+        <v>0.001519433478351818</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001366211624109731</v>
+        <v>0.001366211624109733</v>
       </c>
       <c r="X10" t="n">
         <v>0.001096864125138487</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0009889467262280691</v>
+        <v>0.0009889467262280669</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001535126307136189</v>
+        <v>0.001535126307136191</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001471638162017521</v>
+        <v>0.001471638162017518</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0008624699922950797</v>
+        <v>0.0008624699922950803</v>
       </c>
     </row>
     <row r="11">
@@ -10702,85 +10702,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001654635453527195</v>
+        <v>0.001654635453527191</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001604668329431629</v>
+        <v>0.001604668329431631</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001584992969338238</v>
+        <v>0.001584992969338244</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002736168050910173</v>
+        <v>0.002736168050910167</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001596746395521819</v>
+        <v>0.00159674639552182</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00137007631486791</v>
+        <v>0.001370076314867912</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001624306330918748</v>
+        <v>0.00162430633091875</v>
       </c>
       <c r="I11" t="n">
         <v>0.001627006006635451</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001519304810324986</v>
+        <v>0.001519304810324989</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001599449154695249</v>
+        <v>0.001599449154695258</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001500320859690502</v>
+        <v>0.001500320859690498</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001582113448547153</v>
+        <v>0.001582113448547158</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001573413088991156</v>
+        <v>0.001573413088991165</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001619950238775291</v>
+        <v>0.001619950238775292</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001477311586065546</v>
+        <v>0.001477311586065545</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001606139999506117</v>
+        <v>0.001606139999506115</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001580869437057028</v>
+        <v>0.001580869437057027</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001598617720044043</v>
+        <v>0.00159861772004404</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001629116861421482</v>
+        <v>0.001629116861421484</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001603711269963228</v>
+        <v>0.001603711269963227</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001565019112370321</v>
+        <v>0.001565019112370325</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001542758945421565</v>
+        <v>0.001542758945421562</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001396087411330403</v>
+        <v>0.001396087411330402</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001371102214613511</v>
+        <v>0.001371102214613512</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.00158401863159941</v>
+        <v>0.001584018631599408</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001590728356144052</v>
+        <v>0.001590728356144048</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001284152324606439</v>
+        <v>0.001284152324606434</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication marine results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication marine results.xlsx
@@ -886,7 +886,7 @@
         <v>0.000678990406171346</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03728818433333009</v>
+        <v>0.0006789904061713473</v>
       </c>
       <c r="O5" t="n">
         <v>0.0006789904061713473</v>
@@ -974,7 +974,7 @@
         <v>0.002394741143385948</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03728818433333009</v>
+        <v>0.001581300516747063</v>
       </c>
       <c r="O6" t="n">
         <v>0.001581298720713795</v>
@@ -1062,7 +1062,7 @@
         <v>0.001282324252423674</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03728818433333009</v>
+        <v>0.001282324252423674</v>
       </c>
       <c r="O7" t="n">
         <v>0.001282264534013615</v>
@@ -1150,7 +1150,7 @@
         <v>0.002723735496724153</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03728818433333009</v>
+        <v>0.002012350890297622</v>
       </c>
       <c r="O8" t="n">
         <v>0.002207845556930182</v>
@@ -1238,7 +1238,7 @@
         <v>0.003515073442466154</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03728818433333009</v>
+        <v>0.003515073442466154</v>
       </c>
       <c r="O9" t="n">
         <v>0.003741470408951589</v>
@@ -1922,7 +1922,7 @@
         <v>0.0005504196021360925</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005137795362290412</v>
+        <v>0.0005504196021360922</v>
       </c>
       <c r="O5" t="n">
         <v>0.0005504196021360922</v>
@@ -2010,7 +2010,7 @@
         <v>0.001306096946466421</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005137795362290412</v>
+        <v>0.001310529450673748</v>
       </c>
       <c r="O6" t="n">
         <v>0.001936253233424984</v>
@@ -2098,7 +2098,7 @@
         <v>0.0009897577041064749</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005137795362290412</v>
+        <v>0.0009897577041064749</v>
       </c>
       <c r="O7" t="n">
         <v>0.0009897071875242867</v>
@@ -2186,7 +2186,7 @@
         <v>0.002032616788658229</v>
       </c>
       <c r="N8" t="n">
-        <v>0.005137795362290412</v>
+        <v>0.001512323345685606</v>
       </c>
       <c r="O8" t="n">
         <v>0.001655304501406083</v>
@@ -2274,7 +2274,7 @@
         <v>0.002009270157916003</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005137795362290412</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="O9" t="n">
         <v>0.002131624440956504</v>
@@ -2958,7 +2958,7 @@
         <v>0.0006088473825122982</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02410247601189806</v>
+        <v>0.0006088473825122975</v>
       </c>
       <c r="O5" t="n">
         <v>0.0006088473825122975</v>
@@ -3046,7 +3046,7 @@
         <v>0.00214352162942759</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02410247601189806</v>
+        <v>0.001421822243831088</v>
       </c>
       <c r="O6" t="n">
         <v>0.001420315506373729</v>
@@ -3134,7 +3134,7 @@
         <v>0.001147259889764047</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02410247601189806</v>
+        <v>0.001147259889764047</v>
       </c>
       <c r="O7" t="n">
         <v>0.001147205678665621</v>
@@ -3222,7 +3222,7 @@
         <v>0.002429929494245826</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02410247601189806</v>
+        <v>0.001795636716484895</v>
       </c>
       <c r="O8" t="n">
         <v>0.001969945879227203</v>
@@ -3310,7 +3310,7 @@
         <v>0.002858436337337646</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02410247601189806</v>
+        <v>0.002858436337337646</v>
       </c>
       <c r="O9" t="n">
         <v>0.003040406439491743</v>
@@ -3694,46 +3694,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001686383581615047</v>
+        <v>0.001686383581615044</v>
       </c>
       <c r="C2" t="n">
         <v>0.00165285761173293</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001710985032535596</v>
+        <v>0.001710985032535595</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002804883502781731</v>
+        <v>0.00280488350278173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001664720438746065</v>
+        <v>0.001664720438746064</v>
       </c>
       <c r="G2" t="n">
         <v>0.001668504811128077</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001650188139669161</v>
+        <v>0.00165018813966916</v>
       </c>
       <c r="I2" t="n">
         <v>0.001705774883219169</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001704654269026077</v>
+        <v>0.001704654269026076</v>
       </c>
       <c r="K2" t="n">
         <v>0.001725198820491483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001696145962378274</v>
+        <v>0.001696145962378272</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001848549583150057</v>
+        <v>0.001848549583150055</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001681348120207692</v>
+        <v>0.001681348120207691</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001677881202718554</v>
+        <v>0.001677881202718552</v>
       </c>
       <c r="P2" t="n">
         <v>0.001702247820118452</v>
@@ -3742,31 +3742,31 @@
         <v>0.001661917123302009</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001642593137398075</v>
+        <v>0.001642593137398074</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001700265161557847</v>
+        <v>0.001700265161557845</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001690968386749975</v>
+        <v>0.001690968386749972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001704358069812829</v>
+        <v>0.001704358069812828</v>
       </c>
       <c r="V2" t="n">
         <v>0.001647802167552591</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00170270257593354</v>
+        <v>0.001702702575933538</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001659353031721715</v>
+        <v>0.001659353031721716</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001722196628479402</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001668196964506817</v>
+        <v>0.001668196964506816</v>
       </c>
       <c r="AA2" t="n">
         <v>0.001718217297536887</v>
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001671356618966443</v>
+        <v>0.001671356618966442</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002825162958014671</v>
+        <v>0.002825162958014673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001666846992328119</v>
+        <v>0.001666846992328118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001624295400812362</v>
+        <v>0.001624295400812361</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="J3" t="n">
         <v>0.0016606773506554</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001664891086347896</v>
+        <v>0.001664891086347895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001653867290399559</v>
+        <v>0.001653867290399558</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="V3" t="n">
         <v>0.001646617178134423</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001610029068195176</v>
+        <v>0.001610029068195175</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001663219347256825</v>
+        <v>0.001663219347256824</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001662593161175591</v>
+        <v>0.00166259316117559</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001598510425611065</v>
+        <v>0.001598510425611064</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01492069002194664</v>
+        <v>0.01492069002194668</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005359767682092642</v>
+        <v>0.005359767682092634</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02290238905416561</v>
+        <v>0.02290238905416562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009152476137441997</v>
+        <v>0.009152476137441959</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009704143097035762</v>
+        <v>0.009704143097035755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01885431686957468</v>
+        <v>0.01885431686957471</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007268812861431107</v>
+        <v>0.007268812861431102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02187792850144631</v>
+        <v>0.02187792850144626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02067513882585328</v>
+        <v>0.02067513882585325</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02336243899515477</v>
+        <v>0.02336243899515478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01813778983824242</v>
+        <v>0.01813778983824209</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05994780223721732</v>
+        <v>0.05994780223721718</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01487071796321566</v>
+        <v>0.01487071796321565</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01231603995243196</v>
+        <v>0.01231603995243199</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01855540986966189</v>
+        <v>0.01855540986966188</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009681530223500502</v>
+        <v>0.009681530223500481</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007241766924217095</v>
+        <v>0.00724176692421709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01822850056615165</v>
+        <v>0.0182285005661516</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01781644619635921</v>
+        <v>0.01781644619635923</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0196549769262659</v>
+        <v>0.01965497692626611</v>
       </c>
       <c r="V4" t="n">
-        <v>0.009159726107377652</v>
+        <v>0.009159726107377692</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02002890378482523</v>
+        <v>0.02002890378482521</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02166593925136798</v>
+        <v>0.02166593925136808</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02475646599084032</v>
+        <v>0.02475646599084034</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01001631672220249</v>
+        <v>0.01001631672220246</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02397697761876394</v>
+        <v>0.02397697761876392</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03439834095353846</v>
+        <v>0.03439834095353844</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0005925984616587504</v>
+        <v>0.000592598461658748</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0005925984616587506</v>
+        <v>0.0005925984616587475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0005907548082388341</v>
+        <v>0.000590754808238831</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587469</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01487071796321566</v>
+        <v>0.0005925984616587475</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0005925984616587506</v>
+        <v>0.0005925984616587475</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005925984616587506</v>
+        <v>0.0005925984616587475</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0005925984616587506</v>
+        <v>0.0005925984616587475</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005590415015610436</v>
+        <v>0.00055904150156104</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0005807236197343874</v>
+        <v>0.0005807236197343869</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0005925984616587506</v>
+        <v>0.0005925984616587475</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005925984616587504</v>
+        <v>0.000592598461658748</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005590415015610436</v>
+        <v>0.00055904150156104</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0005925984616587514</v>
+        <v>0.0005925984616587464</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005925984616587506</v>
+        <v>0.0005925984616587475</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002043487454085416</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002041643800665497</v>
+        <v>0.002041643800665494</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002043487454085416</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01487071796321566</v>
+        <v>0.001373677605485479</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00204895822259329</v>
+        <v>0.002048958222593284</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002049749160371465</v>
+        <v>0.002049749160371459</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002031612612161053</v>
+        <v>0.002031612612161051</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002048843932343876</v>
+        <v>0.002048843932343869</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001369735339248646</v>
+        <v>0.001369735339248639</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001415638786407509</v>
+        <v>0.001415638786407521</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002043487454085415</v>
+        <v>0.002043487454085409</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001373104225854806</v>
+        <v>0.001373104225854803</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001088334417005601</v>
+        <v>0.0010883344170056</v>
       </c>
       <c r="C7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.001086490763585683</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.0010883344170056</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.001086490763585688</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0010883344170056</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.001088334417005601</v>
-      </c>
       <c r="M7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01487071796321566</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001088283496701772</v>
+        <v>0.001088283496701768</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001088283496701772</v>
+        <v>0.001088283496701768</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001087645157647276</v>
+        <v>0.001087645157647274</v>
       </c>
       <c r="V7" t="n">
         <v>0.00107645957508124</v>
       </c>
       <c r="W7" t="n">
+        <v>0.001088334417005599</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.0010883344170056</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.001088334417005601</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0010883344170056</v>
+        <v>0.001088334417005599</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001513210106414167</v>
+        <v>0.001513210106414166</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001864887021140054</v>
+        <v>0.00186488702114005</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001630394483840297</v>
+        <v>0.001630394483840294</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002421386843074298</v>
+        <v>0.002421386843074294</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002263569075699437</v>
+        <v>0.002263569075699435</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002265412729119357</v>
+        <v>0.002265412729119353</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002265412729119626</v>
+        <v>0.002265412729119623</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01487071796321566</v>
+        <v>0.001682329855736659</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001842566092110061</v>
+        <v>0.001842566092110058</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001803288318730691</v>
+        <v>0.001803288318730689</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00136538512289442</v>
+        <v>0.001365385122894418</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="U8" t="n">
         <v>0.001897777971350249</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002047403932082162</v>
+        <v>0.002047403932082163</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002265560558377812</v>
+        <v>0.00226556055837781</v>
       </c>
       <c r="X8" t="n">
         <v>0.001434325987847629</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003012464392804135</v>
+        <v>0.003012464392804134</v>
       </c>
       <c r="Z8" t="n">
         <v>0.001499237556524584</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002265412729119355</v>
+        <v>0.002265412729119352</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003051151266594489</v>
+        <v>0.003051151266594487</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002030170640785508</v>
+        <v>0.002030170640785501</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002391978800054391</v>
+        <v>0.002391978800054385</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001416213425006257</v>
+        <v>0.001416213425006252</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002500537568343616</v>
+        <v>0.002500537568343608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002498694154874137</v>
+        <v>0.002498694154874132</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294046</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01487071796321566</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002656416552246196</v>
+        <v>0.002656416552246191</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002690317556809721</v>
+        <v>0.002690317556809718</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002500537568343616</v>
+        <v>0.002500537568343608</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="V9" t="n">
         <v>0.003031455507129742</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294046</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002216948137685333</v>
+        <v>0.002216948137685327</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002500537808294052</v>
+        <v>0.002500537808294044</v>
       </c>
     </row>
     <row r="10">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001304341284120082</v>
+        <v>0.00130434128412008</v>
       </c>
       <c r="C10" t="n">
         <v>0.001561792148533785</v>
@@ -4407,55 +4407,55 @@
         <v>0.001165764250063158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002620934019283466</v>
+        <v>0.002620934019283467</v>
       </c>
       <c r="F10" t="n">
         <v>0.001464777730138264</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001164457625938844</v>
+        <v>0.001164457625938842</v>
       </c>
       <c r="H10" t="n">
         <v>0.001522836621754554</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001197156750787045</v>
+        <v>0.001197156750787044</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00118660311145054</v>
+        <v>0.001186603111450541</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001096299079651147</v>
+        <v>0.001096299079651146</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001248879210072415</v>
+        <v>0.001248879210072416</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003649209161461079</v>
+        <v>0.0003649209161461069</v>
       </c>
       <c r="N10" t="n">
         <v>0.001337993694897667</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001354587781627131</v>
+        <v>0.00135458778162713</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001209065721960534</v>
+        <v>0.001209065721960532</v>
       </c>
       <c r="Q10" t="n">
         <v>0.001452644226399676</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001511503954087319</v>
+        <v>0.001511503954087317</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001223120053453854</v>
+        <v>0.001223120053453853</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001283253737218777</v>
+        <v>0.001283253737218774</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001199868541819946</v>
+        <v>0.001199868541819945</v>
       </c>
       <c r="V10" t="n">
         <v>0.00142381954724726</v>
@@ -4464,19 +4464,19 @@
         <v>0.001210873381286028</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001133814947268204</v>
+        <v>0.001133814947268205</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001096736071343924</v>
+        <v>0.001096736071343921</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001416840937098733</v>
+        <v>0.001416840937098734</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001119747921756302</v>
+        <v>0.001119747921756301</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.000890256294324859</v>
+        <v>0.0008902562943248579</v>
       </c>
     </row>
     <row r="11">
@@ -4486,16 +4486,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001523377835873798</v>
+        <v>0.001523377835873797</v>
       </c>
       <c r="C11" t="n">
         <v>0.001603005428524821</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001484926294679644</v>
+        <v>0.001484926294679643</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002711958684820017</v>
+        <v>0.002711958684820015</v>
       </c>
       <c r="F11" t="n">
         <v>0.001572778280493151</v>
@@ -4504,67 +4504,67 @@
         <v>0.001459277158144585</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001586598468854923</v>
+        <v>0.001586598468854922</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001493999833234549</v>
+        <v>0.001493999833234548</v>
       </c>
       <c r="J11" t="n">
         <v>0.001488948979402906</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001466487645449252</v>
+        <v>0.001466487645449251</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001507904796198192</v>
+        <v>0.001507904796198193</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001258104576225568</v>
+        <v>0.001258104576225566</v>
       </c>
       <c r="N11" t="n">
         <v>0.001533654328614115</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001537737773469098</v>
+        <v>0.001537737773469099</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001495891389969408</v>
+        <v>0.001495891389969405</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001566389688911409</v>
+        <v>0.001566389688911408</v>
       </c>
       <c r="R11" t="n">
         <v>0.00157781736569097</v>
       </c>
       <c r="S11" t="n">
-        <v>0.00150030349702676</v>
+        <v>0.001500303497026759</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001518367739966607</v>
+        <v>0.001518367739966606</v>
       </c>
       <c r="U11" t="n">
         <v>0.001493816893390145</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001546428535485011</v>
+        <v>0.001546428535485012</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001497168636538264</v>
+        <v>0.001497168636538262</v>
       </c>
       <c r="X11" t="n">
         <v>0.001442674089095583</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001464729849326443</v>
+        <v>0.001464729849326442</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001556094002723478</v>
+        <v>0.001556094002723479</v>
       </c>
       <c r="AA11" t="n">
         <v>0.001471220983655978</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001366288933513005</v>
+        <v>0.001366288933513004</v>
       </c>
     </row>
   </sheetData>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00161327526823765</v>
+        <v>0.001613275268237652</v>
       </c>
       <c r="C2" t="n">
         <v>0.001586162130721838</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001617834735286394</v>
+        <v>0.001617834735286397</v>
       </c>
       <c r="E2" t="n">
         <v>0.002786871857401605</v>
@@ -4745,31 +4745,31 @@
         <v>0.001606531651434357</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001570983926971037</v>
+        <v>0.001570983926971041</v>
       </c>
       <c r="H2" t="n">
         <v>0.001584553848500333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001636744177823756</v>
+        <v>0.001636744177823759</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001635245445093707</v>
+        <v>0.001635245445093708</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001677770281643542</v>
+        <v>0.001677770281643544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001623543192046162</v>
+        <v>0.001623543192046163</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001746537763866823</v>
+        <v>0.001746537763866824</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001597931029718443</v>
+        <v>0.001597931029718446</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00161142586949497</v>
+        <v>0.001611425869494972</v>
       </c>
       <c r="P2" t="n">
         <v>0.001628883137990903</v>
@@ -4778,25 +4778,25 @@
         <v>0.00159666377966816</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00158171958079908</v>
+        <v>0.001581719580799079</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001630840406394281</v>
+        <v>0.001630840406394284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001629904176135965</v>
+        <v>0.001629904176135966</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001639884342073661</v>
+        <v>0.001639884342073664</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001560266918765931</v>
+        <v>0.001560266918765933</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001609816679771549</v>
+        <v>0.00160981667977155</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001627697081233584</v>
+        <v>0.001627697081233585</v>
       </c>
       <c r="Y2" t="n">
         <v>0.001702183186442088</v>
@@ -4805,10 +4805,10 @@
         <v>0.001597829997165619</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001660943835929394</v>
+        <v>0.001660943835929395</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001614149697685505</v>
+        <v>0.001614149697685508</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001605660372551815</v>
+        <v>0.001605660372551817</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002817801306578564</v>
+        <v>0.002817801306578569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001602576810841431</v>
+        <v>0.001602576810841433</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001531225414572719</v>
+        <v>0.001531225414572722</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001596029305245816</v>
+        <v>0.001596029305245817</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001599877021609471</v>
+        <v>0.001599877021609474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001580110486013993</v>
+        <v>0.001580110486013995</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001541644729017677</v>
+        <v>0.001541644729017672</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001572833175767843</v>
+        <v>0.001572833175767845</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001597547305974029</v>
+        <v>0.001597547305974032</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001596931173287121</v>
+        <v>0.001596931173287123</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001532848437722595</v>
+        <v>0.001532848437722597</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01253281389055624</v>
+        <v>0.01253281389055629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004826329083043751</v>
+        <v>0.00482632908304375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01484145099470537</v>
+        <v>0.01484145099470541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006162870962364889</v>
+        <v>0.006162870962364903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01095233847728475</v>
+        <v>0.01095233847728471</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01647857681149205</v>
+        <v>0.01647857681149203</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006995302304591694</v>
+        <v>0.006995302304591695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02033996331108251</v>
+        <v>0.0203399633110825</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01875075689881841</v>
+        <v>0.01875075689881836</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02723398600435748</v>
+        <v>0.02723398600435753</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01556847696915861</v>
+        <v>0.01556847696915862</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04783934054510488</v>
+        <v>0.04783934054510486</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01003449052063713</v>
+        <v>0.01003449052063712</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01191541268932168</v>
+        <v>0.01191541268932167</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01596569797349924</v>
+        <v>0.01596569797349918</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009307007996869895</v>
+        <v>0.00930700799686989</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0102596560255454</v>
+        <v>0.01025965602554541</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01686083180553689</v>
+        <v>0.0168608318055369</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01877477395862029</v>
+        <v>0.01877477395862033</v>
       </c>
       <c r="U4" t="n">
         <v>0.01902737542924606</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01255309570812237</v>
+        <v>0.01255309570812232</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01287006387770749</v>
+        <v>0.01287006387770748</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02275316875891005</v>
+        <v>0.02275316875890999</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03666858305077901</v>
+        <v>0.03666858305077902</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008334539639981996</v>
+        <v>0.008334539639982019</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02597973667164132</v>
+        <v>0.0259797366716413</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03120735441406606</v>
+        <v>0.03120735441406602</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006042712875472345</v>
+        <v>0.0006042712875472404</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0006042712875472335</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0006025799939027667</v>
+        <v>0.0006025799939027696</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006042712875472346</v>
+        <v>0.000604271287547242</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01003449052063713</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006042712875472335</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0006042712875472335</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0006042712875472335</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005800571326627535</v>
+        <v>0.0005800571326627599</v>
       </c>
       <c r="V5" t="n">
-        <v>0.000593355667525575</v>
+        <v>0.0005933556675255681</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0006042712875472335</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0006042712875472346</v>
+        <v>0.0006042712875472364</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0005800571326627535</v>
+        <v>0.0005800571326627599</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0006042712875472343</v>
+        <v>0.0006042712875472419</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0006042712875472335</v>
+        <v>0.0006042712875472364</v>
       </c>
     </row>
     <row r="6">
@@ -5088,10 +5088,10 @@
         <v>0.001390404754617898</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="F6" t="n">
         <v>0.001390404754617898</v>
@@ -5100,16 +5100,16 @@
         <v>0.001390404754617898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="I6" t="n">
         <v>0.001390404754617898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002060252673594593</v>
+        <v>0.002060252673594594</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="L6" t="n">
         <v>0.001390404754617898</v>
@@ -5118,49 +5118,49 @@
         <v>0.001390404754617898</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01003449052063713</v>
+        <v>0.001396909462197249</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001495410101341527</v>
+        <v>0.001495410101341529</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00207008499854183</v>
+        <v>0.002070084998541838</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="S6" t="n">
         <v>0.001390404754617898</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001379489134596243</v>
+        <v>0.001379489134596227</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001447966192737129</v>
+        <v>0.00144796619273713</v>
       </c>
       <c r="X6" t="n">
         <v>0.001390404754617898</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001451164734534773</v>
+        <v>0.001451164734534752</v>
       </c>
       <c r="Z6" t="n">
         <v>0.001390404754617898</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00206194396723906</v>
+        <v>0.002061943967239074</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001397640555048045</v>
+        <v>0.001397640555048052</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001097410356200611</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001095719062556142</v>
+        <v>0.001095719062556144</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001097410356200611</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01003449052063713</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001097358974879497</v>
+        <v>0.001097358974879501</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001097358974879497</v>
+        <v>0.001097358974879501</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001096808936724145</v>
+        <v>0.001096808936724144</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001086494736178954</v>
+        <v>0.001086494736178942</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001097410356200611</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00109741035620061</v>
+        <v>0.001097410356200614</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001516425636522819</v>
+        <v>0.00151642563652282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0018652081318198</v>
+        <v>0.001865208131819804</v>
       </c>
       <c r="F8" t="n">
         <v>0.001632645547063303</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002417127772829275</v>
+        <v>0.002417127772829273</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002260746084709012</v>
+        <v>0.00226074608470901</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00226243737835348</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002262437378353881</v>
+        <v>0.002262437378353884</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01003449052063713</v>
+        <v>0.001684153473360829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001843070911552972</v>
+        <v>0.001843070911552974</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00180411640747429</v>
+        <v>0.001804116407474294</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001369817302394312</v>
+        <v>0.001369817302394319</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001897892737940873</v>
+        <v>0.00189789273794087</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00204715534173284</v>
+        <v>0.002047155341732839</v>
       </c>
       <c r="W8" t="n">
         <v>0.002262583990928491</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001438190760815174</v>
+        <v>0.001438190760815179</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003003450655680497</v>
+        <v>0.003003450655680498</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001502568085423705</v>
+        <v>0.001502568085423711</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002262437378353479</v>
+        <v>0.002262437378353482</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003041709023084073</v>
+        <v>0.003041709023084074</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001924077532960492</v>
+        <v>0.001924077532960494</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00226056006201396</v>
+        <v>0.002260560062013965</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001353095725602828</v>
+        <v>0.001353095725602834</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002361519998845457</v>
+        <v>0.002361519998845455</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002359828890810561</v>
+        <v>0.002359828890810558</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455033</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01003449052063713</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002506487859260463</v>
+        <v>0.002506487859260465</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002538015881668796</v>
+        <v>0.002538015881668795</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002361519998845457</v>
+        <v>0.002361519998845455</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002855403153903625</v>
+        <v>0.002855403153903606</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455033</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002097781090818711</v>
+        <v>0.002097781090818714</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002361520184455024</v>
+        <v>0.002361520184455032</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001289566831961712</v>
+        <v>0.001289566831961716</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001508467038649926</v>
+        <v>0.001508467038649928</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001267602411812966</v>
+        <v>0.001267602411812973</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002677680855942302</v>
+        <v>0.002677680855942307</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001370815138494574</v>
+        <v>0.001370815138494578</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001118479826609254</v>
+        <v>0.001118479826609256</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001463456235609745</v>
+        <v>0.001463456235609746</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001157664556734325</v>
+        <v>0.001157664556734326</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00115688634962728</v>
+        <v>0.001156886349627284</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0009342993856018937</v>
+        <v>0.0009342993856018957</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001230796697579608</v>
+        <v>0.001230796697579611</v>
       </c>
       <c r="M10" t="n">
-        <v>0.000517833073990331</v>
+        <v>0.0005178330739903352</v>
       </c>
       <c r="N10" t="n">
-        <v>0.00138328674595963</v>
+        <v>0.001383286745959631</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001300245914763009</v>
+        <v>0.001300245914763011</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001195920144360787</v>
+        <v>0.00119592014436079</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001391085579128621</v>
+        <v>0.001391085579128622</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00137311126362613</v>
+        <v>0.001373111263626131</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001186342009211309</v>
+        <v>0.001186342009211312</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00119715961417578</v>
+        <v>0.001197159614175783</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001133727964394909</v>
+        <v>0.00113372796439491</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001225639547510621</v>
+        <v>0.001225639547510615</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001312421979345587</v>
+        <v>0.001312421979345589</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001056247558225067</v>
+        <v>0.001056247558225069</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0007686177625695628</v>
+        <v>0.0007686177625695661</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001385654749941621</v>
+        <v>0.001385654749941623</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00101114773840451</v>
+        <v>0.001011147738404512</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0008822339685991342</v>
+        <v>0.0008822339685991369</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.001473423513422549</v>
+        <v>0.001473423513422551</v>
       </c>
       <c r="C11" t="n">
         <v>0.001541938854059702</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001467989099307163</v>
+        <v>0.001467989099307166</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002723116605824723</v>
+        <v>0.002723116605824727</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001501079351935909</v>
+        <v>0.001501079351935914</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001383183369105518</v>
+        <v>0.00138318336910552</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001523822326497736</v>
+        <v>0.001523822326497737</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001436876467432585</v>
+        <v>0.001436876467432586</v>
       </c>
       <c r="J11" t="n">
         <v>0.001435434000821711</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001374930336190019</v>
+        <v>0.001374930336190022</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001456950838797904</v>
+        <v>0.001456950838797905</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001255544689805181</v>
+        <v>0.001255544689805184</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001500722134440044</v>
+        <v>0.001500722134440045</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001476433131386678</v>
+        <v>0.001476433131386679</v>
       </c>
       <c r="P11" t="n">
         <v>0.001446421841883096</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001503003378335058</v>
+        <v>0.00150300337833506</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001487534274945219</v>
+        <v>0.001487534274945221</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001444021028269761</v>
+        <v>0.001444021028269765</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001448006842743936</v>
+        <v>0.001448006842743938</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001429125405886659</v>
+        <v>0.001429125405886661</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001416483554131458</v>
+        <v>0.00141648355413146</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001480364089851143</v>
+        <v>0.001480364089851144</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001392648978990936</v>
+        <v>0.00139264897899094</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00132529794488738</v>
+        <v>0.001325297944887382</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001501418208909361</v>
+        <v>0.001501418208909363</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001394410506276762</v>
+        <v>0.001394410506276763</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001318118040849038</v>
+        <v>0.001318118040849043</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.0005684326030743619</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0147825594210376</v>
+        <v>0.0005684326030743635</v>
       </c>
       <c r="O5" t="n">
         <v>0.0005684326030743635</v>
@@ -6154,7 +6154,7 @@
         <v>0.002009440259356533</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0147825594210376</v>
+        <v>0.00135697814070947</v>
       </c>
       <c r="O6" t="n">
         <v>0.002023308247288013</v>
@@ -6242,7 +6242,7 @@
         <v>0.001051201442232897</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0147825594210376</v>
+        <v>0.001051201442232897</v>
       </c>
       <c r="O7" t="n">
         <v>0.001051147974851512</v>
@@ -6330,7 +6330,7 @@
         <v>0.002207448647737403</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0147825594210376</v>
+        <v>0.001633323609059706</v>
       </c>
       <c r="O8" t="n">
         <v>0.001791098154683575</v>
@@ -6418,7 +6418,7 @@
         <v>0.00246884357809754</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0147825594210376</v>
+        <v>0.00246884357809754</v>
       </c>
       <c r="O9" t="n">
         <v>0.002624473323283534</v>
@@ -6893,7 +6893,7 @@
         <v>0.001607563964469863</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001616327422260716</v>
+        <v>0.001616327422260715</v>
       </c>
       <c r="D3" t="n">
         <v>0.001607563964469863</v>
@@ -6917,7 +6917,7 @@
         <v>0.001606865781413451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001609861889642169</v>
+        <v>0.001609861889642168</v>
       </c>
       <c r="L3" t="n">
         <v>0.001607563964469863</v>
@@ -7102,7 +7102,7 @@
         <v>0.0005489394411289772</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006508376546270463</v>
+        <v>0.0005489394411289757</v>
       </c>
       <c r="O5" t="n">
         <v>0.0005489394411289758</v>
@@ -7190,7 +7190,7 @@
         <v>0.001902566405420067</v>
       </c>
       <c r="N6" t="n">
-        <v>0.006508376546270463</v>
+        <v>0.001303656523857926</v>
       </c>
       <c r="O6" t="n">
         <v>0.001911375665237118</v>
@@ -7242,43 +7242,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="J7" t="n">
         <v>0.0009851768950415263</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006508376546270463</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="O7" t="n">
         <v>0.000986702539230255</v>
@@ -7287,16 +7287,16 @@
         <v>0.000986702539230255</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="U7" t="n">
         <v>0.000986171133093072</v>
@@ -7305,22 +7305,22 @@
         <v>0.0009765842592869742</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0009867528403059713</v>
+        <v>0.0009867528403059715</v>
       </c>
     </row>
     <row r="8">
@@ -7366,7 +7366,7 @@
         <v>0.002027295332507304</v>
       </c>
       <c r="N8" t="n">
-        <v>0.006508376546270463</v>
+        <v>0.001508361246048056</v>
       </c>
       <c r="O8" t="n">
         <v>0.001650968838793631</v>
@@ -7454,7 +7454,7 @@
         <v>0.002133230281817233</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006508376546270463</v>
+        <v>0.002133230281817233</v>
       </c>
       <c r="O9" t="n">
         <v>0.002264542325011334</v>
@@ -7566,7 +7566,7 @@
         <v>0.001553201392556294</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001468347108325206</v>
+        <v>0.001468347108325207</v>
       </c>
       <c r="W10" t="n">
         <v>0.001365550359138438</v>
@@ -7666,7 +7666,7 @@
         <v>0.00153060471644816</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001527587018218609</v>
+        <v>0.001527587018218608</v>
       </c>
       <c r="AA11" t="n">
         <v>0.001513553756686952</v>
@@ -8050,7 +8050,7 @@
         <v>0.00317810144890685</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004789984538979582</v>
+        <v>0.004789984538979583</v>
       </c>
       <c r="O4" t="n">
         <v>0.009871864235761167</v>
@@ -8138,7 +8138,7 @@
         <v>0.0005502239942541567</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004789984538979583</v>
+        <v>0.000550223994254158</v>
       </c>
       <c r="O5" t="n">
         <v>0.000550223994254158</v>
@@ -8226,7 +8226,7 @@
         <v>0.001913061624881144</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004789984538979582</v>
+        <v>0.001311594264230609</v>
       </c>
       <c r="O6" t="n">
         <v>0.001410126391216941</v>
@@ -8314,7 +8314,7 @@
         <v>0.0009861611262227434</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004789984538979582</v>
+        <v>0.0009861611262227434</v>
       </c>
       <c r="O7" t="n">
         <v>0.0009861106161643599</v>
@@ -8402,7 +8402,7 @@
         <v>0.002020278256343109</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004789984538979582</v>
+        <v>0.001504055577476411</v>
       </c>
       <c r="O8" t="n">
         <v>0.00164591805187546</v>
@@ -8490,7 +8490,7 @@
         <v>0.002001403790357892</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004789984538979582</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="O9" t="n">
         <v>0.002123108767957263</v>
@@ -9174,7 +9174,7 @@
         <v>0.0005994145352302898</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02822703414332055</v>
+        <v>0.0005994145352302904</v>
       </c>
       <c r="O5" t="n">
         <v>0.0005994145352302904</v>
@@ -9262,7 +9262,7 @@
         <v>0.001397714010609461</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02822703414332055</v>
+        <v>0.00140071001840085</v>
       </c>
       <c r="O6" t="n">
         <v>0.002126465331452444</v>
@@ -9350,7 +9350,7 @@
         <v>0.001123573842820388</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02822703414332055</v>
+        <v>0.001123573842820388</v>
       </c>
       <c r="O7" t="n">
         <v>0.001123519876208378</v>
@@ -9438,7 +9438,7 @@
         <v>0.002376145997116102</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02822703414332055</v>
+        <v>0.001756348893146811</v>
       </c>
       <c r="O8" t="n">
         <v>0.001926674518867424</v>
@@ -9526,7 +9526,7 @@
         <v>0.002798893640290148</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02822703414332055</v>
+        <v>0.002798893640290148</v>
       </c>
       <c r="O9" t="n">
         <v>0.002976994707122588</v>
@@ -10210,7 +10210,7 @@
         <v>0.0005612331459957246</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00753339104159734</v>
+        <v>0.0005612331459957245</v>
       </c>
       <c r="O5" t="n">
         <v>0.0005612331459957245</v>
@@ -10298,7 +10298,7 @@
         <v>0.001311046444247972</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00753339104159734</v>
+        <v>0.001314039168355867</v>
       </c>
       <c r="O6" t="n">
         <v>0.001964671576008185</v>
@@ -10386,7 +10386,7 @@
         <v>0.001017078489349577</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00753339104159734</v>
+        <v>0.001017078489349577</v>
       </c>
       <c r="O7" t="n">
         <v>0.001017028024671273</v>
@@ -10474,7 +10474,7 @@
         <v>0.002107901006378457</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00753339104159734</v>
+        <v>0.001565587875161523</v>
       </c>
       <c r="O8" t="n">
         <v>0.001714620232395717</v>
@@ -10562,7 +10562,7 @@
         <v>0.002319659542326025</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00753339104159734</v>
+        <v>0.002319659542326025</v>
       </c>
       <c r="O9" t="n">
         <v>0.002464142358666801</v>

--- a/Results/Phase 2/Hydrogen/hydrogen eutrophication marine results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen eutrophication marine results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001767691511309999</v>
+        <v>0.001767691511310001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001691659421333834</v>
+        <v>0.001691659421333836</v>
       </c>
       <c r="D2" t="n">
         <v>0.001760182139873074</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002821357780863255</v>
+        <v>0.002821357780863263</v>
       </c>
       <c r="F2" t="n">
         <v>0.001734208296968121</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00175780113708271</v>
+        <v>0.001757801137082711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00175076256504651</v>
+        <v>0.001750762565046505</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001777068682812337</v>
+        <v>0.001777068682812336</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001758092969577217</v>
+        <v>0.00175809296957722</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001838541855594874</v>
+        <v>0.001838541855594876</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001767461265121611</v>
+        <v>0.001767461265121615</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001950844957904502</v>
+        <v>0.001950844957904503</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00179398231451557</v>
+        <v>0.001793982314515572</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001759369363464185</v>
+        <v>0.001759369363464186</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001743044771965301</v>
+        <v>0.001743044771965302</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001727286474303198</v>
+        <v>0.001727286474303199</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001734514486653494</v>
+        <v>0.001734514486653495</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001755019497645436</v>
+        <v>0.001755019497645437</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00177828815411983</v>
+        <v>0.001778288154119831</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001805943111781256</v>
+        <v>0.001805943111781257</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001734132970693873</v>
+        <v>0.001734132970693872</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001744931517006785</v>
+        <v>0.001744931517006786</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001725919091191968</v>
+        <v>0.001725919091191973</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001736107248999177</v>
+        <v>0.001736107248999179</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001724082803748242</v>
+        <v>0.001724082803748245</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00178904881233397</v>
+        <v>0.001789048812333972</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001807377001168556</v>
+        <v>0.001807377001168558</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002840314744914312</v>
+        <v>0.002840314744914318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001705105453890772</v>
+        <v>0.001705105453890773</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001722168621028855</v>
+        <v>0.001722168621028854</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001707018291075404</v>
+        <v>0.001707018291075409</v>
       </c>
     </row>
     <row r="4">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02694546248510364</v>
+        <v>0.02694546248510353</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007128744281736586</v>
+        <v>0.0071287442817366</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02805054136000606</v>
+        <v>0.02805054136000609</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01082685289970208</v>
+        <v>0.01082685289970206</v>
       </c>
       <c r="F4" t="n">
         <v>0.02056538235908027</v>
@@ -780,64 +780,64 @@
         <v>0.02496730347809254</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02615912515474804</v>
+        <v>0.02615912515474803</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03354307807343202</v>
+        <v>0.03354307807343201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02652068450091274</v>
+        <v>0.02652068450091275</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05150800162494436</v>
+        <v>0.05150800162494429</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02874682875974289</v>
+        <v>0.02874682875974195</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08686701606401749</v>
+        <v>0.0868670160640176</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03728818433333007</v>
+        <v>0.03728818433333013</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02416087021556771</v>
+        <v>0.02416087021556772</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02066886737453855</v>
+        <v>0.02066886737453851</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01768845408288296</v>
+        <v>0.01768845408288293</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02069900140166832</v>
+        <v>0.02069900140166831</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02423087031240765</v>
+        <v>0.02423087031240764</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03368173181259568</v>
+        <v>0.03368173181259575</v>
       </c>
       <c r="U4" t="n">
         <v>0.03910058881154101</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01406263545435425</v>
+        <v>0.01406263545435421</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02240630337106798</v>
+        <v>0.02240630337106795</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01740741464859034</v>
+        <v>0.01740741464859033</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01984395931261015</v>
+        <v>0.01984395931261019</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01561207684317633</v>
+        <v>0.01561207684317643</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03546735622230913</v>
+        <v>0.03546735622230909</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0444185490184465</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001806017979823412</v>
+        <v>0.001806017979823408</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002235077989971818</v>
+        <v>0.002235077989971807</v>
       </c>
       <c r="F5" t="n">
         <v>0.001948987643349809</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002914030202218625</v>
+        <v>0.00291403020221863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724122</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00272205611873931</v>
+        <v>0.002722056118739316</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002723735496724152</v>
+        <v>0.002723735496724169</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03728818433333007</v>
+        <v>0.002012350890297631</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002207845556930179</v>
+        <v>0.002207845556930177</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002159925090331671</v>
+        <v>0.002159925090331668</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001625665541904013</v>
+        <v>0.001625665541904024</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002275480821892709</v>
+        <v>0.00227548082189271</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002461804348888843</v>
+        <v>0.002461804348888844</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002723915854388558</v>
+        <v>0.002723915854388563</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001709776175785397</v>
+        <v>0.001709776175785396</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003635638306054874</v>
+        <v>0.003635638306054883</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001788970905799239</v>
+        <v>0.001788970905799235</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002723735496724108</v>
+        <v>0.002723735496724123</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003682368181305045</v>
+        <v>0.003682368181305049</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002831915937584563</v>
+        <v>0.002831915937584551</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003357403167150559</v>
+        <v>0.003357403167150571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001940209467936295</v>
+        <v>0.0019402094679363</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00351507303979411</v>
+        <v>0.003515073039794106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003513394064481366</v>
+        <v>0.003513394064481369</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03728818433333007</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003741470408951597</v>
+        <v>0.003741470408951598</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003790707952416012</v>
+        <v>0.003790707952416023</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00351507303979411</v>
+        <v>0.003515073039794106</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004292678701735693</v>
+        <v>0.004292678701735691</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00310319005586163</v>
+        <v>0.003103190055861633</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003515073442466165</v>
+        <v>0.003515073442466162</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001127547303343206</v>
+        <v>0.001127547303343205</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001581696607763028</v>
+        <v>0.001581696607763027</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001180468382645881</v>
+        <v>0.001180468382645884</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002629154785042255</v>
+        <v>0.002629154785042258</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001334440728986292</v>
+        <v>0.001334440728986295</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001186676615585148</v>
+        <v>0.001186676615585153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001238826474614595</v>
+        <v>0.001238826474614602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001082726766613315</v>
+        <v>0.001082726766613322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001175284809299964</v>
+        <v>0.001175284809299969</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007200758807862539</v>
+        <v>0.0007200758807862579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001132548412208533</v>
+        <v>0.001132548412208546</v>
       </c>
       <c r="M7" t="n">
-        <v>6.989344835420599e-05</v>
+        <v>6.989344835421116e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009794152199651598</v>
+        <v>0.0009794152199651628</v>
       </c>
       <c r="O7" t="n">
         <v>0.001176479502196101</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001273317680767289</v>
+        <v>0.001273317680767294</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001372300667860628</v>
+        <v>0.001372300667860632</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001332301984713999</v>
+        <v>0.001332301984714</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00120449333055073</v>
+        <v>0.001204493330550729</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001074813849419555</v>
+        <v>0.001074813849419557</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009042487600245578</v>
+        <v>0.0009042487600245604</v>
       </c>
       <c r="V7" t="n">
         <v>0.001430923055213953</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001266477816539182</v>
+        <v>0.001266477816539183</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001380851169107352</v>
+        <v>0.001380851169107356</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001319186611391475</v>
+        <v>0.001319186611391478</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001387338217386227</v>
+        <v>0.00138733821738623</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001006668803745011</v>
+        <v>0.001006668803745017</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0009042063695131404</v>
+        <v>0.0009042063695131441</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001504030365227381</v>
+        <v>0.001504030365227383</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001634637656050195</v>
+        <v>0.0016346376560502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001520600253522647</v>
+        <v>0.001520600253522653</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002725279326194602</v>
+        <v>0.002725279326194608</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001564684318883334</v>
+        <v>0.001564684318883341</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001521044016504113</v>
+        <v>0.001521044016504114</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001537733796518051</v>
+        <v>0.001537733796518055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001493014049683043</v>
+        <v>0.00149301404968304</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001517022887850186</v>
+        <v>0.001517022887850192</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001389479913714466</v>
+        <v>0.001389479913714473</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001506075639510306</v>
+        <v>0.001506075639510303</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001205947937259039</v>
+        <v>0.00120594793725904</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001462920598427002</v>
+        <v>0.001462920598427009</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0015179725237973</v>
+        <v>0.001517972523797308</v>
       </c>
       <c r="P8" t="n">
         <v>0.00154570961215327</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001574988889058701</v>
+        <v>0.001574988889058705</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001564017373109039</v>
+        <v>0.001564017373109044</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001526369039154681</v>
+        <v>0.001526369039154685</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001490633118450403</v>
+        <v>0.001490633118450402</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001440680416878417</v>
+        <v>0.001440680416878423</v>
       </c>
       <c r="V8" t="n">
         <v>0.001601615310103544</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001544484197173613</v>
+        <v>0.001544484197173614</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001577512011263561</v>
+        <v>0.00157751201126356</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00155964259879676</v>
+        <v>0.001559642598796766</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001578627351459719</v>
+        <v>0.001578627351459726</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001470387563717251</v>
+        <v>0.001470387563717255</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001442095018447933</v>
+        <v>0.001442095018447935</v>
       </c>
     </row>
   </sheetData>
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001513623869776597</v>
+        <v>0.001513623869776598</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001526567543245807</v>
+        <v>0.001526567543245806</v>
       </c>
       <c r="D2" t="n">
         <v>0.001520116074816347</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002739401012834174</v>
+        <v>0.002739401012834171</v>
       </c>
       <c r="F2" t="n">
         <v>0.001528636914053284</v>
@@ -1376,49 +1376,49 @@
         <v>0.001464630091081191</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001521502096428525</v>
+        <v>0.001521502096428524</v>
       </c>
       <c r="I2" t="n">
         <v>0.001521665011743461</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001526718127651989</v>
+        <v>0.001526718127651987</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001531365549881109</v>
+        <v>0.001531365549881108</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00153338054063238</v>
+        <v>0.001533380540632379</v>
       </c>
       <c r="M2" t="n">
         <v>0.001522953354560946</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001525447436270608</v>
+        <v>0.001525447436270607</v>
       </c>
       <c r="O2" t="n">
         <v>0.001536861940059337</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001528694662954082</v>
+        <v>0.001528694662954081</v>
       </c>
       <c r="Q2" t="n">
         <v>0.001518746916806518</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001519994250578451</v>
+        <v>0.001519994250578448</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001529560074793685</v>
+        <v>0.001529560074793686</v>
       </c>
       <c r="T2" t="n">
         <v>0.001524011831123037</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001526703339472701</v>
+        <v>0.0015267033394727</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001470653519513831</v>
+        <v>0.001470653519513824</v>
       </c>
       <c r="W2" t="n">
         <v>0.001541622902822534</v>
@@ -1427,13 +1427,13 @@
         <v>0.001572938459403971</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001559356929532326</v>
+        <v>0.001559356929532324</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00152636838994717</v>
+        <v>0.001526368389947172</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001553647946227671</v>
+        <v>0.00155364794622767</v>
       </c>
       <c r="AB2" t="n">
         <v>0.001457048438952951</v>
@@ -1446,28 +1446,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001551394946249923</v>
+        <v>0.001551394946249924</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002784939537226704</v>
+        <v>0.002784939537226703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001548311384539539</v>
+        <v>0.00154831138453954</v>
       </c>
       <c r="G3" t="n">
         <v>0.001476959988270828</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="J3" t="n">
         <v>0.001542160173686279</v>
@@ -1476,55 +1476,55 @@
         <v>0.00154561159530758</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001525845059712101</v>
+        <v>0.001525845059712102</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001483033313989027</v>
+        <v>0.001483033313989019</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="X3" t="n">
         <v>0.001518567749465952</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="Z3" t="n">
         <v>0.001543281879672138</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001542665746985229</v>
+        <v>0.00154266574698523</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001478583011420703</v>
+        <v>0.001478583011420704</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001972247352939202</v>
+        <v>0.001972247352939198</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003335178118813369</v>
+        <v>0.003335178118813366</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003742709170873976</v>
+        <v>0.003742709170873978</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002619906435847354</v>
+        <v>0.002619906435847347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004642869693336185</v>
+        <v>0.004642869693336175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004461685287040431</v>
+        <v>0.004461685287040416</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004319256164528628</v>
+        <v>0.004319256164528624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004224799024014984</v>
+        <v>0.004224799024014986</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005260859501063519</v>
+        <v>0.00526085950106351</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005557072407471583</v>
+        <v>0.005557072407471576</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006542102816340752</v>
+        <v>0.006542102816340756</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004515062275136148</v>
+        <v>0.004515062275136145</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005137795362290409</v>
+        <v>0.005137795362290414</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007145696968449369</v>
+        <v>0.007145696968449375</v>
       </c>
       <c r="P4" t="n">
         <v>0.005360637061813884</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003287033179707809</v>
+        <v>0.003287033179707808</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007965374731359763</v>
+        <v>0.007965374731359762</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005571292983900447</v>
+        <v>0.005571292983900441</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004849968297034259</v>
+        <v>0.004849968297034256</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004960307811555329</v>
+        <v>0.004960307811555303</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005553028265215849</v>
+        <v>0.00555302826521584</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00909077250495084</v>
+        <v>0.009090772504950833</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02191844051481349</v>
+        <v>0.02191844051481352</v>
       </c>
       <c r="Y4" t="n">
         <v>0.01378696742917453</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004579132118048669</v>
+        <v>0.00457913211804867</v>
       </c>
       <c r="AA4" t="n">
         <v>0.01227044135198144</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002746058642455527</v>
+        <v>0.002746058642455525</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001361415300415048</v>
+        <v>0.001361415300415046</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001675221795389863</v>
+        <v>0.001675221795389861</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001465980647775626</v>
+        <v>0.001465980647775623</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00217179478971095</v>
+        <v>0.002171794789710944</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002031017674794506</v>
+        <v>0.002031017674794499</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002032616788658234</v>
+        <v>0.002032616788658227</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005137795362290409</v>
+        <v>0.001512323345685604</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001655304501406083</v>
+        <v>0.001655304501406081</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001620256365234135</v>
+        <v>0.001620256365234131</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001229508888569598</v>
+        <v>0.001229508888569597</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001704594699300616</v>
+        <v>0.001704594699300613</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001838374081198519</v>
+        <v>0.001838374081198509</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002032748698902214</v>
+        <v>0.002032748698902207</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00129102583861585</v>
+        <v>0.001291025838615848</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002699262756498272</v>
+        <v>0.002699262756498267</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001348947388181477</v>
+        <v>0.001348947388181476</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002032616788658255</v>
+        <v>0.002032616788658248</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002733742868010449</v>
+        <v>0.002733742868010443</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00164006545396682</v>
+        <v>0.001640065453966819</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="E6" t="n">
         <v>0.001924059407459779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001158152228634307</v>
+        <v>0.001158152228634306</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002009270403958987</v>
+        <v>0.002009270403958983</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002007671044052257</v>
+        <v>0.002007671044052252</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005137795362290409</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002131624440956504</v>
+        <v>0.002131624440956502</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0021582343447594</v>
+        <v>0.002158234344759399</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002009270403958987</v>
+        <v>0.002009270403958983</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002424992087601887</v>
+        <v>0.002424992087601878</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001786672650098927</v>
+        <v>0.001786672650098926</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002009270157916006</v>
+        <v>0.002009270157916003</v>
       </c>
     </row>
     <row r="7">
@@ -1807,37 +1807,37 @@
         <v>0.001470500411385959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002731917525635383</v>
+        <v>0.002731917525635382</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001456905478892553</v>
+        <v>0.001456905478892554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001376600038123949</v>
+        <v>0.00137660003812395</v>
       </c>
       <c r="H7" t="n">
         <v>0.001462926681594825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00146158046561426</v>
+        <v>0.001461580465614261</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001427402608372397</v>
+        <v>0.001427402608372396</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001423146530584706</v>
+        <v>0.001423146530584708</v>
       </c>
       <c r="L7" t="n">
         <v>0.00139140933345535</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001454219769779283</v>
+        <v>0.001454219769779284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001438832289347679</v>
+        <v>0.00143883228934768</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001369550675253764</v>
+        <v>0.001369550675253765</v>
       </c>
       <c r="P7" t="n">
         <v>0.001418081141654094</v>
@@ -1846,7 +1846,7 @@
         <v>0.001478354983780973</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001364994519750295</v>
+        <v>0.001364994519750294</v>
       </c>
       <c r="S7" t="n">
         <v>0.001413580919969025</v>
@@ -1855,25 +1855,25 @@
         <v>0.001447741533240453</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001430771791780341</v>
+        <v>0.001430771791780342</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001354350844334261</v>
+        <v>0.001354350844334253</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001343016291078817</v>
+        <v>0.001343016291078816</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001007511124927869</v>
+        <v>0.001007511124927872</v>
       </c>
       <c r="Y7" t="n">
         <v>0.001238842728946987</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001436252489308289</v>
+        <v>0.001436252489308288</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001272265197253228</v>
+        <v>0.001272265197253227</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001432829133202073</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001497844861597849</v>
+        <v>0.001497844861597848</v>
       </c>
       <c r="C8" t="n">
         <v>0.001497764214033143</v>
@@ -1895,46 +1895,46 @@
         <v>0.001487280617141399</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002715275828589</v>
+        <v>0.002715275828588999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00148704693569057</v>
+        <v>0.001487046935690569</v>
       </c>
       <c r="G8" t="n">
         <v>0.001418965993936177</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001485220567562566</v>
+        <v>0.001485220567562565</v>
       </c>
       <c r="I8" t="n">
         <v>0.001484770950316207</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00147450306972351</v>
+        <v>0.001474503069723509</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001475643555159199</v>
+        <v>0.001475643555159198</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001464558390450697</v>
+        <v>0.001464558390450696</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001482710153071634</v>
+        <v>0.001482710153071633</v>
       </c>
       <c r="N8" t="n">
         <v>0.001478202882147925</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001458094030736521</v>
+        <v>0.001458094030736522</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001472008270500835</v>
+        <v>0.001472008270500837</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001489485314602338</v>
+        <v>0.001489485314602339</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001446806742295572</v>
+        <v>0.00144680674229557</v>
       </c>
       <c r="S8" t="n">
         <v>0.001470826067132377</v>
@@ -1946,7 +1946,7 @@
         <v>0.001475791233269597</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001412102585734213</v>
+        <v>0.001412102585734205</v>
       </c>
       <c r="W8" t="n">
         <v>0.001450781764140052</v>
@@ -1955,16 +1955,16 @@
         <v>0.001340406066598316</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001421116488098416</v>
+        <v>0.001421116488098415</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001477669676249191</v>
+        <v>0.00147766967624919</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001430614834384188</v>
+        <v>0.001430614834384187</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001436230278554518</v>
+        <v>0.001436230278554519</v>
       </c>
     </row>
   </sheetData>
@@ -2130,64 +2130,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001705107447704081</v>
+        <v>0.001705107447704083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001657346762585671</v>
+        <v>0.001657346762585672</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001699353003986752</v>
+        <v>0.001699353003986753</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002803533509039255</v>
+        <v>0.00280353350903926</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001668695059423121</v>
+        <v>0.001668695059423122</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001680469437262866</v>
+        <v>0.001680469437262867</v>
       </c>
       <c r="H2" t="n">
         <v>0.001664456423973439</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001690743665990917</v>
+        <v>0.001690743665990919</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001710218207312889</v>
+        <v>0.00171021820731289</v>
       </c>
       <c r="K2" t="n">
         <v>0.001771629503798502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001713164072499586</v>
+        <v>0.001713164072499588</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001883950583199601</v>
+        <v>0.001883950583199602</v>
       </c>
       <c r="N2" t="n">
         <v>0.001712231616415568</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001695357486736972</v>
+        <v>0.001695357486736973</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001707155684314928</v>
+        <v>0.001707155684314929</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001670880695039378</v>
+        <v>0.00167088069503938</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001666382277239887</v>
+        <v>0.001666382277239888</v>
       </c>
       <c r="S2" t="n">
         <v>0.001708697847191984</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001704229320571504</v>
+        <v>0.001704229320571505</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001739125406641978</v>
+        <v>0.001739125406641979</v>
       </c>
       <c r="V2" t="n">
         <v>0.001642671637060479</v>
@@ -2196,19 +2196,19 @@
         <v>0.001716418213813012</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001687875671150647</v>
+        <v>0.001687875671150649</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001686378406210812</v>
+        <v>0.001686378406210813</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001670286250621502</v>
+        <v>0.001670286250621505</v>
       </c>
       <c r="AA2" t="n">
         <v>0.001718755399380834</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001699766635062134</v>
+        <v>0.001699766635062135</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001672309195378302</v>
+        <v>0.001672309195378303</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002825963871717742</v>
+        <v>0.002825963871717744</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00166697876796454</v>
+        <v>0.001666978767964541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001631742051066973</v>
+        <v>0.001631742051066974</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001661558793161609</v>
+        <v>0.001661558793161612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001665584742570317</v>
+        <v>0.001665584742570318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001664268313983195</v>
+        <v>0.001664268313983196</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="V3" t="n">
         <v>0.001648492110527589</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001659560993232585</v>
+        <v>0.001659560993232586</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001664337102748871</v>
+        <v>0.001664337102748872</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001663964696946013</v>
+        <v>0.001663964696946014</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001599881961381487</v>
+        <v>0.001599881961381488</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0201036167959943</v>
+        <v>0.0201036167959944</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006807996297648206</v>
+        <v>0.006807996297648208</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0211128374585677</v>
+        <v>0.02111283745856767</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009218936328457796</v>
+        <v>0.009218936328457926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01161776185622563</v>
+        <v>0.01161776185622566</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02184224817506182</v>
+        <v>0.02184224817506184</v>
       </c>
       <c r="H4" t="n">
         <v>0.01157338232392649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01885921338499924</v>
+        <v>0.01885921338499925</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02354519059249382</v>
+        <v>0.0235451905924937</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03820367607685746</v>
+        <v>0.03820367607685748</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02379021309256917</v>
+        <v>0.02379021309256981</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07394673743103665</v>
+        <v>0.07394673743103641</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02410247601189802</v>
+        <v>0.02410247601189805</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01724799802975683</v>
+        <v>0.01724799802975682</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0210580472314568</v>
+        <v>0.02105804723145693</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01269304079490229</v>
+        <v>0.01269304079490238</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01190675949506497</v>
+        <v>0.01190675949506496</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02154907861311887</v>
+        <v>0.0215490786131189</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02246451111199743</v>
+        <v>0.02246451111199749</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03015680192119602</v>
+        <v>0.030156801921196</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008254545340873089</v>
+        <v>0.008254545340873085</v>
       </c>
       <c r="W4" t="n">
         <v>0.0248530871799658</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01866230173291462</v>
+        <v>0.01866230173291477</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01651982868843064</v>
+        <v>0.01651982868843062</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01158829941983891</v>
+        <v>0.01158829941983896</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02544379724571286</v>
+        <v>0.02544379724571298</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03972980446616699</v>
+        <v>0.03972980446616721</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001611663836351184</v>
+        <v>0.001611663836351182</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001994227168766375</v>
+        <v>0.001994227168766377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001739140062563936</v>
+        <v>0.001739140062563935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00259960220890762</v>
+        <v>0.002599602208907617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002427906656281609</v>
+        <v>0.002427906656281606</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002429929494245831</v>
+        <v>0.002429929494245832</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02410247601189802</v>
+        <v>0.001795636716484898</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001969945879227209</v>
+        <v>0.001969945879227207</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001927218491545439</v>
+        <v>0.001927218491545441</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001450855958602331</v>
+        <v>0.001450855958602328</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245714</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245714</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002030123467738216</v>
+        <v>0.002030123467738214</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002192787280786543</v>
+        <v>0.002192787280786541</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002430090306778609</v>
+        <v>0.002430090306778607</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001525851631997111</v>
+        <v>0.001525851631997107</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003242791383123109</v>
+        <v>0.003242791383123112</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001596464131666149</v>
+        <v>0.001596464131666151</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002429929494245713</v>
+        <v>0.002429929494245715</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003284676396073233</v>
+        <v>0.003284676396073237</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002309337699121982</v>
+        <v>0.002309337699121975</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002731706341234766</v>
+        <v>0.002731706341234767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001592614571407157</v>
+        <v>0.001592614571407153</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002858435986150423</v>
+        <v>0.002858435986150424</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002856413499373546</v>
+        <v>0.002856413499373539</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02410247601189802</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003040406439491748</v>
+        <v>0.00304040643949175</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003079981891003809</v>
+        <v>0.003079981891003805</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002858435986150423</v>
+        <v>0.002858435986150424</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00347904998327408</v>
+        <v>0.003479049983274078</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002527378546797179</v>
+        <v>0.002527378546797178</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00285843633733765</v>
+        <v>0.002858436337337645</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001201772263793096</v>
+        <v>0.001201772263793095</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001541518538032639</v>
+        <v>0.00154151853803264</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001242607030075199</v>
+        <v>0.001242607030075202</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002633785987920267</v>
+        <v>0.002633785987920263</v>
       </c>
       <c r="F7" t="n">
         <v>0.001442438344366156</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001141220055959668</v>
+        <v>0.001141220055959669</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001448481670841056</v>
+        <v>0.001448481670841058</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001293731847698865</v>
+        <v>0.001293731847698867</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001158822112607077</v>
+        <v>0.001158822112607078</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008283509682716858</v>
+        <v>0.000828350968271688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001157046659475791</v>
+        <v>0.001157046659475794</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001670253543534332</v>
+        <v>0.0001670253543534343</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001165066130323686</v>
+        <v>0.001165066130323688</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001259335738726219</v>
+        <v>0.001259335738726221</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001188647461645242</v>
+        <v>0.001188647461645244</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001408732121444724</v>
+        <v>0.001408732121444725</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001438557993215298</v>
+        <v>0.0014385579932153</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001181906950018558</v>
+        <v>0.001181906950018556</v>
       </c>
       <c r="T7" t="n">
         <v>0.001214329869364578</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001002907609882857</v>
+        <v>0.001002907609882859</v>
       </c>
       <c r="V7" t="n">
         <v>0.001466467839057255</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001138687459431138</v>
+        <v>0.001138687459431139</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001281496252592417</v>
+        <v>0.001281496252592418</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001316544456873146</v>
+        <v>0.001316544456873147</v>
       </c>
       <c r="Z7" t="n">
         <v>0.001411607528304069</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001125332067893136</v>
+        <v>0.001125332067893138</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0008332570257309493</v>
+        <v>0.0008332570257309485</v>
       </c>
     </row>
     <row r="8">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001494808417699615</v>
+        <v>0.001494808417699617</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0015978365966883</v>
+        <v>0.001597836596688301</v>
       </c>
       <c r="D8" t="n">
         <v>0.001507633922773321</v>
@@ -2670,49 +2670,49 @@
         <v>0.002716091959476823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001566528451117984</v>
+        <v>0.001566528451117986</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001457280366288194</v>
+        <v>0.001457280366288195</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001566410960392025</v>
+        <v>0.001566410960392026</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00152228653972138</v>
+        <v>0.001522286539721381</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001481471415533835</v>
+        <v>0.001481471415533836</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001390685468386894</v>
+        <v>0.001390685468386896</v>
       </c>
       <c r="L8" t="n">
         <v>0.001482514749998701</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001202838411857341</v>
+        <v>0.001202838411857342</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00148523117870701</v>
+        <v>0.001485231178707012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001511250021270985</v>
+        <v>0.001511250021270986</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001490884827506924</v>
+        <v>0.001490884827506925</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001554749059808334</v>
+        <v>0.001554749059808335</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001563683361994381</v>
+        <v>0.001563683361994382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001489360036113104</v>
+        <v>0.001489360036113105</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001499644041120778</v>
+        <v>0.001499644041120779</v>
       </c>
       <c r="U8" t="n">
         <v>0.001438342325364303</v>
@@ -2721,22 +2721,22 @@
         <v>0.00155985001346454</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001477415396784512</v>
+        <v>0.001477415396784513</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001515855009338529</v>
+        <v>0.001515855009338528</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001528301089815046</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00155529348884775</v>
+        <v>0.001555293488847753</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001473675836641433</v>
+        <v>0.001473675836641435</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001350949846252426</v>
+        <v>0.001350949846252427</v>
       </c>
     </row>
   </sheetData>
@@ -2902,34 +2902,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001686383581615044</v>
+        <v>0.001686383581615046</v>
       </c>
       <c r="C2" t="n">
         <v>0.00165285761173293</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001710985032535593</v>
+        <v>0.001710985032535596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002804883502781728</v>
+        <v>0.002804883502781732</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001664720438746063</v>
+        <v>0.001664720438746064</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001668504811128075</v>
+        <v>0.001668504811128076</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001650188139669159</v>
+        <v>0.00165018813966916</v>
       </c>
       <c r="I2" t="n">
         <v>0.001705774883219168</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001704654269026074</v>
+        <v>0.001704654269026076</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001725198820491481</v>
+        <v>0.001725198820491483</v>
       </c>
       <c r="L2" t="n">
         <v>0.001696145962378272</v>
@@ -2941,46 +2941,46 @@
         <v>0.001681348120207691</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001677881202718553</v>
+        <v>0.001677881202718552</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00170224782011845</v>
+        <v>0.001702247820118451</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001661917123302007</v>
+        <v>0.001661917123302008</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001642593137398073</v>
+        <v>0.001642593137398074</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001700265161557845</v>
+        <v>0.001700265161557846</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001690968386749971</v>
+        <v>0.001690968386749972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001704358069812827</v>
+        <v>0.001704358069812828</v>
       </c>
       <c r="V2" t="n">
         <v>0.00164780216755259</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001702702575933536</v>
+        <v>0.001702702575933537</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001659353031721712</v>
+        <v>0.001659353031721714</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001722196628479401</v>
+        <v>0.001722196628479402</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001668196964506815</v>
+        <v>0.001668196964506816</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001718217297536885</v>
+        <v>0.001718217297536886</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001688546820320223</v>
+        <v>0.001688546820320224</v>
       </c>
     </row>
     <row r="3">
@@ -2999,7 +2999,7 @@
         <v>0.00166259316117559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002825162958014672</v>
+        <v>0.002825162958014671</v>
       </c>
       <c r="F3" t="n">
         <v>0.001666846992328118</v>
@@ -3038,7 +3038,7 @@
         <v>0.00166259316117559</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001653867290399557</v>
+        <v>0.001653867290399558</v>
       </c>
       <c r="S3" t="n">
         <v>0.00166259316117559</v>
@@ -3062,13 +3062,13 @@
         <v>0.00166259316117559</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001663219347256823</v>
+        <v>0.001663219347256824</v>
       </c>
       <c r="AA3" t="n">
         <v>0.00166259316117559</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001598510425611063</v>
+        <v>0.001598510425611064</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01492069002194661</v>
+        <v>0.01492069002194664</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005359767682092634</v>
+        <v>0.005359767682092639</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02290238905416561</v>
+        <v>0.02290238905416563</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009152476137441997</v>
+        <v>0.009152476137441978</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009704143097035748</v>
+        <v>0.009704143097035756</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01885431686957471</v>
+        <v>0.01885431686957472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007268812861431081</v>
+        <v>0.007268812861431087</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02187792850144628</v>
+        <v>0.02187792850144625</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02067513882585327</v>
+        <v>0.02067513882585328</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02336243899515476</v>
+        <v>0.02336243899515474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01813778983824241</v>
+        <v>0.0181377898382424</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0599478022372173</v>
+        <v>0.05994780223721725</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01487071796321564</v>
+        <v>0.01487071796321565</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01231603995243194</v>
+        <v>0.01231603995243196</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01855540986966183</v>
+        <v>0.01855540986966188</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00968153022350046</v>
+        <v>0.009681530223500474</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007241766924217084</v>
+        <v>0.007241766924217087</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01822850056615162</v>
+        <v>0.01822850056615164</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0178164461963592</v>
+        <v>0.01781644619635925</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01965497692626591</v>
+        <v>0.01965497692626589</v>
       </c>
       <c r="V4" t="n">
-        <v>0.009159726107377591</v>
+        <v>0.009159726107377654</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02002890378482522</v>
+        <v>0.0200289037848252</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02166593925136794</v>
+        <v>0.02166593925136796</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02475646599084027</v>
+        <v>0.02475646599084036</v>
       </c>
       <c r="Z4" t="n">
         <v>0.01001631672220247</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02397697761876394</v>
+        <v>0.02397697761876395</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03439834095353846</v>
+        <v>0.03439834095353851</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001513210106414161</v>
+        <v>0.001513210106414165</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00186488702114005</v>
+        <v>0.001864887021140052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001630394483840291</v>
+        <v>0.001630394483840293</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002421386843074286</v>
+        <v>0.002421386843074295</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002263569075699435</v>
+        <v>0.002263569075699437</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00226541272911935</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002265412729119621</v>
+        <v>0.002265412729119626</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01487071796321564</v>
+        <v>0.001682329855736658</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001842566092110055</v>
+        <v>0.00184256609211006</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001803288318730685</v>
+        <v>0.001803288318730688</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001365385122894412</v>
+        <v>0.001365385122894419</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001897777971350244</v>
+        <v>0.001897777971350247</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00204740393208216</v>
+        <v>0.002047403932082163</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002265560558377805</v>
+        <v>0.002265560558377809</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001434325987847627</v>
+        <v>0.001434325987847628</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003012464392804125</v>
+        <v>0.003012464392804133</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00149923755652458</v>
+        <v>0.001499237556524584</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002265412729119349</v>
+        <v>0.002265412729119354</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003051151266594482</v>
+        <v>0.003051151266594486</v>
       </c>
     </row>
     <row r="6">
@@ -3257,82 +3257,82 @@
         <v>0.002030170640785504</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002391978800054389</v>
+        <v>0.00239197880005439</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001416213425006254</v>
+        <v>0.001416213425006256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002500537568343615</v>
+        <v>0.002500537568343616</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002498694154874134</v>
+        <v>0.002498694154874135</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002500537808294048</v>
+        <v>0.002500537808294052</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01487071796321564</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="O6" t="n">
         <v>0.002656416552246194</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002690317556809716</v>
+        <v>0.002690317556809718</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002500537568343615</v>
+        <v>0.002500537568343616</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003031455507129742</v>
+        <v>0.003031455507129745</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002500537808294048</v>
+        <v>0.002500537808294052</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002216948137685327</v>
+        <v>0.002216948137685331</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002500537808294047</v>
+        <v>0.002500537808294051</v>
       </c>
     </row>
     <row r="7">
@@ -3342,28 +3342,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00130434128412008</v>
+        <v>0.001304341284120082</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001561792148533784</v>
+        <v>0.001561792148533786</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001165764250063156</v>
+        <v>0.001165764250063157</v>
       </c>
       <c r="E7" t="n">
         <v>0.002620934019283467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001464777730138263</v>
+        <v>0.001464777730138264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001164457625938842</v>
+        <v>0.001164457625938843</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001522836621754555</v>
+        <v>0.001522836621754554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001197156750787045</v>
+        <v>0.001197156750787044</v>
       </c>
       <c r="J7" t="n">
         <v>0.001186603111450541</v>
@@ -3372,55 +3372,55 @@
         <v>0.001096299079651146</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001248879210072414</v>
+        <v>0.001248879210072415</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003649209161461059</v>
+        <v>0.0003649209161461075</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001337993694897666</v>
+        <v>0.001337993694897667</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001354587781627129</v>
+        <v>0.00135458778162713</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00120906572196053</v>
+        <v>0.001209065721960531</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001452644226399676</v>
+        <v>0.001452644226399677</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001511503954087317</v>
+        <v>0.001511503954087318</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001223120053453853</v>
+        <v>0.001223120053453854</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001283253737218773</v>
+        <v>0.001283253737218774</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001199868541819945</v>
+        <v>0.001199868541819946</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001423819547247261</v>
+        <v>0.001423819547247259</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001210873381286027</v>
+        <v>0.001210873381286028</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001133814947268204</v>
+        <v>0.001133814947268203</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00109673607134392</v>
+        <v>0.001096736071343922</v>
       </c>
       <c r="Z7" t="n">
         <v>0.001416840937098733</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0011197479217563</v>
+        <v>0.001119747921756301</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0008902562943248586</v>
+        <v>0.0008902562943248577</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001523377835873796</v>
+        <v>0.001523377835873797</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001603005428524819</v>
+        <v>0.00160300542852482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001484926294679641</v>
+        <v>0.001484926294679642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002711958684820016</v>
+        <v>0.00271195868482002</v>
       </c>
       <c r="F8" t="n">
         <v>0.00157277828049315</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001459277158144583</v>
+        <v>0.001459277158144584</v>
       </c>
       <c r="H8" t="n">
         <v>0.001586598468854922</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001493999833234546</v>
+        <v>0.001493999833234547</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001488948979402903</v>
+        <v>0.001488948979402905</v>
       </c>
       <c r="K8" t="n">
         <v>0.00146648764544925</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001507904796198191</v>
+        <v>0.001507904796198192</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001258104576225567</v>
+        <v>0.001258104576225568</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001533654328614112</v>
+        <v>0.001533654328614114</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001537737773469096</v>
+        <v>0.001537737773469098</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001495891389969407</v>
+        <v>0.001495891389969406</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001566389688911407</v>
+        <v>0.001566389688911408</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001577817365690968</v>
+        <v>0.00157781736569097</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001500303497026759</v>
+        <v>0.001500303497026758</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001518367739966604</v>
+        <v>0.001518367739966606</v>
       </c>
       <c r="U8" t="n">
         <v>0.001493816893390144</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001546428535485011</v>
+        <v>0.00154642853548501</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001497168636538261</v>
+        <v>0.001497168636538263</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00144267408909558</v>
+        <v>0.001442674089095582</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00146472984932644</v>
+        <v>0.001464729849326442</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001556094002723477</v>
+        <v>0.001556094002723478</v>
       </c>
       <c r="AA8" t="n">
         <v>0.001471220983655977</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001366288933513002</v>
+        <v>0.001366288933513004</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001613275268237646</v>
+        <v>0.001613275268237649</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001586162130721841</v>
+        <v>0.001586162130721838</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0016178347352864</v>
+        <v>0.001617834735286396</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002786871857401602</v>
+        <v>0.002786871857401606</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001606531651434363</v>
+        <v>0.001606531651434357</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001570983926971044</v>
+        <v>0.00157098392697104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001584553848500333</v>
+        <v>0.001584553848500332</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001636744177823758</v>
+        <v>0.001636744177823757</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001635245445093709</v>
+        <v>0.001635245445093708</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001677770281643543</v>
+        <v>0.001677770281643544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001623543192046159</v>
+        <v>0.001623543192046162</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001746537763866824</v>
+        <v>0.001746537763866823</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00159793102971845</v>
+        <v>0.001597931029718445</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001611425869494977</v>
+        <v>0.00161142586949497</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001628883137990905</v>
+        <v>0.001628883137990902</v>
       </c>
       <c r="Q2" t="n">
         <v>0.00159666377966816</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001581719580799085</v>
+        <v>0.001581719580799079</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001630840406394291</v>
+        <v>0.001630840406394284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001629904176135971</v>
+        <v>0.001629904176135966</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001639884342073668</v>
+        <v>0.001639884342073662</v>
       </c>
       <c r="V2" t="n">
         <v>0.001560266918765933</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001609816679771553</v>
+        <v>0.001609816679771549</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001627697081233593</v>
+        <v>0.001627697081233584</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001702183186442089</v>
+        <v>0.001702183186442088</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001597829997165617</v>
+        <v>0.001597829997165619</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001660943835929398</v>
+        <v>0.001660943835929393</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001614149697685508</v>
+        <v>0.001614149697685507</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001605660372551818</v>
+        <v>0.001605660372551816</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002817801306578569</v>
+        <v>0.002817801306578564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001602576810841434</v>
+        <v>0.001602576810841432</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001531225414572723</v>
+        <v>0.001531225414572721</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001596029305245819</v>
+        <v>0.001596029305245817</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001599877021609475</v>
+        <v>0.001599877021609473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001580110486013996</v>
+        <v>0.001580110486013994</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="V3" t="n">
         <v>0.001541644729017672</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001572833175767847</v>
+        <v>0.001572833175767844</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001597547305974033</v>
+        <v>0.001597547305974031</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001596931173287124</v>
+        <v>0.001596931173287122</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001532848437722598</v>
+        <v>0.001532848437722596</v>
       </c>
     </row>
     <row r="4">
@@ -3853,82 +3853,82 @@
         <v>0.01253281389055628</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004826329083043757</v>
+        <v>0.004826329083043751</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01484145099470531</v>
+        <v>0.01484145099470535</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006162870962364905</v>
+        <v>0.006162870962364889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01095233847728475</v>
+        <v>0.01095233847728476</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01647857681149208</v>
+        <v>0.01647857681149203</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006995302304591711</v>
+        <v>0.0069953023045917</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02033996331108248</v>
+        <v>0.0203399633110825</v>
       </c>
       <c r="J4" t="n">
         <v>0.01875075689881836</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02723398600435751</v>
+        <v>0.02723398600435756</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01556847696915864</v>
+        <v>0.01556847696915867</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04783934054510484</v>
+        <v>0.04783934054510488</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01003449052063715</v>
+        <v>0.01003449052063713</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01191541268932167</v>
+        <v>0.01191541268932166</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01596569797349927</v>
+        <v>0.01596569797349925</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009307007996869909</v>
+        <v>0.0093070079968699</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01025965602554542</v>
+        <v>0.01025965602554541</v>
       </c>
       <c r="S4" t="n">
         <v>0.01686083180553689</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01877477395862029</v>
+        <v>0.01877477395862031</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01902737542924606</v>
+        <v>0.01902737542924604</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01255309570812235</v>
+        <v>0.01255309570812236</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01287006387770747</v>
+        <v>0.01287006387770748</v>
       </c>
       <c r="X4" t="n">
         <v>0.02275316875891004</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0366685830507791</v>
+        <v>0.03666858305077907</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008334539639982015</v>
+        <v>0.008334539639982021</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02597973667164129</v>
+        <v>0.02597973667164134</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03120735441406608</v>
+        <v>0.03120735441406607</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001516425636522825</v>
+        <v>0.00151642563652282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001865208131819812</v>
+        <v>0.001865208131819806</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001632645547063309</v>
+        <v>0.001632645547063305</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00241712777282928</v>
+        <v>0.002417127772829277</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002260746084709023</v>
+        <v>0.002260746084709015</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00226243737835349</v>
+        <v>0.002262437378353484</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002262437378353894</v>
+        <v>0.002262437378353886</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01003449052063715</v>
+        <v>0.001684153473360832</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001843070911552986</v>
+        <v>0.001843070911552977</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001804116407474296</v>
+        <v>0.001804116407474293</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001369817302394335</v>
+        <v>0.001369817302394318</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00189789273794088</v>
+        <v>0.001897892737940876</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002047155341732844</v>
+        <v>0.002047155341732845</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002262583990928498</v>
+        <v>0.002262583990928495</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001438190760815182</v>
+        <v>0.00143819076081518</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003003450655680488</v>
+        <v>0.003003450655680499</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00150256808542371</v>
+        <v>0.001502568085423711</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002262437378353489</v>
+        <v>0.002262437378353483</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003041709023084069</v>
+        <v>0.003041709023084077</v>
       </c>
     </row>
     <row r="6">
@@ -4029,82 +4029,82 @@
         <v>0.001924077532960501</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00226056006201397</v>
+        <v>0.002260560062013963</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001353095725602833</v>
+        <v>0.001353095725602832</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002361519998845446</v>
+        <v>0.00236151999884546</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002359828890810563</v>
+        <v>0.002359828890810561</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01003449052063715</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002506487859260475</v>
+        <v>0.002506487859260461</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002538015881668806</v>
+        <v>0.002538015881668801</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002361519998845446</v>
+        <v>0.00236151999884546</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002855403153903608</v>
+        <v>0.002855403153903623</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002097781090818719</v>
+        <v>0.00209778109081872</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002361520184455027</v>
+        <v>0.002361520184455029</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001289566831961717</v>
+        <v>0.001289566831961714</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001508467038649929</v>
+        <v>0.001508467038649927</v>
       </c>
       <c r="D7" t="n">
         <v>0.001267602411812967</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002677680855942307</v>
+        <v>0.002677680855942304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001370815138494576</v>
+        <v>0.001370815138494575</v>
       </c>
       <c r="G7" t="n">
         <v>0.001118479826609258</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001463456235609744</v>
+        <v>0.001463456235609746</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001157664556734332</v>
+        <v>0.001157664556734326</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001156886349627284</v>
+        <v>0.001156886349627282</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000934299385601896</v>
+        <v>0.0009342993856018943</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001230796697579611</v>
+        <v>0.00123079669757961</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0005178330739903346</v>
+        <v>0.0005178330739903321</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001383286745959639</v>
+        <v>0.00138328674595963</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001300245914763013</v>
+        <v>0.001300245914763008</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001195920144360789</v>
+        <v>0.001195920144360788</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001391085579128622</v>
+        <v>0.001391085579128623</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001373111263626132</v>
+        <v>0.001373111263626129</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001186342009211306</v>
+        <v>0.001186342009211311</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001197159614175778</v>
+        <v>0.001197159614175781</v>
       </c>
       <c r="U7" t="n">
         <v>0.00113372796439491</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001225639547510614</v>
+        <v>0.001225639547510615</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001312421979345588</v>
+        <v>0.001312421979345587</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001056247558225074</v>
+        <v>0.001056247558225069</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0007686177625695612</v>
+        <v>0.0007686177625695639</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001385654749941624</v>
+        <v>0.001385654749941621</v>
       </c>
       <c r="AA7" t="n">
         <v>0.001011147738404511</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0008822339685991389</v>
+        <v>0.0008822339685991359</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001473423513422558</v>
+        <v>0.001473423513422551</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001541938854059701</v>
+        <v>0.001541938854059702</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001467989099307168</v>
+        <v>0.001467989099307165</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002723116605824721</v>
+        <v>0.002723116605824723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001501079351935913</v>
+        <v>0.001501079351935911</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001383183369105524</v>
+        <v>0.001383183369105519</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00152382232649774</v>
+        <v>0.001523822326497736</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001436876467432588</v>
+        <v>0.001436876467432584</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001435434000821712</v>
+        <v>0.001435434000821709</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001374930336190024</v>
+        <v>0.00137493033619002</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001456950838797902</v>
+        <v>0.001456950838797903</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001255544689805188</v>
+        <v>0.001255544689805185</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001500722134440038</v>
+        <v>0.001500722134440045</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00147643313138668</v>
+        <v>0.001476433131386679</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001446421841883098</v>
+        <v>0.001446421841883095</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001503003378335053</v>
+        <v>0.001503003378335057</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001487534274945223</v>
+        <v>0.001487534274945219</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001444021028269763</v>
+        <v>0.001444021028269762</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001448006842743942</v>
+        <v>0.001448006842743935</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001429125405886666</v>
+        <v>0.001429125405886661</v>
       </c>
       <c r="V8" t="n">
         <v>0.00141648355413146</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001480364089851147</v>
+        <v>0.001480364089851143</v>
       </c>
       <c r="X8" t="n">
         <v>0.001392648978990939</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001325297944887383</v>
+        <v>0.00132529794488738</v>
       </c>
       <c r="Z8" t="n">
         <v>0.001501418208909361</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001394410506276759</v>
+        <v>0.001394410506276761</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001318118040849043</v>
+        <v>0.001318118040849041</v>
       </c>
     </row>
   </sheetData>
@@ -4452,31 +4452,31 @@
         <v>0.001592191543812855</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001623500682238986</v>
+        <v>0.001623500682238987</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002765316895740088</v>
+        <v>0.002765316895740089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001597749500892745</v>
+        <v>0.001597749500892747</v>
       </c>
       <c r="G2" t="n">
         <v>0.001576934648769378</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001610206009586901</v>
+        <v>0.0016102060095869</v>
       </c>
       <c r="I2" t="n">
         <v>0.001612689464974099</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001612369197669</v>
+        <v>0.001612369197669001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001645933568156953</v>
+        <v>0.001645933568156952</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001626390121619435</v>
+        <v>0.001626390121619436</v>
       </c>
       <c r="M2" t="n">
         <v>0.00166657190934393</v>
@@ -4485,19 +4485,19 @@
         <v>0.001631754374484173</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001600324102159396</v>
+        <v>0.001600324102159397</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001616952010930463</v>
+        <v>0.001616952010930464</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001612175236673818</v>
+        <v>0.001612175236673817</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001607641174281306</v>
+        <v>0.001607641174281305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001612081698159634</v>
+        <v>0.001612081698159635</v>
       </c>
       <c r="T2" t="n">
         <v>0.001604307964125438</v>
@@ -4509,7 +4509,7 @@
         <v>0.001583591254332715</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001633009123665005</v>
+        <v>0.001633009123665007</v>
       </c>
       <c r="X2" t="n">
         <v>0.001619508873757398</v>
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001623289006247803</v>
+        <v>0.001623289006247802</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002797585593630964</v>
+        <v>0.002797585593630969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001617958578834041</v>
+        <v>0.00161795857883404</v>
       </c>
       <c r="G3" t="n">
         <v>0.001582721861936474</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001613656664210015</v>
+        <v>0.001613656664210014</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001616564553439818</v>
+        <v>0.001616564553439817</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001615248124852696</v>
+        <v>0.001615248124852695</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="V3" t="n">
         <v>0.001603315714378673</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001610540804102086</v>
+        <v>0.001610540804102085</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001615316913618373</v>
+        <v>0.001615316913618372</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001614944507815514</v>
+        <v>0.001614944507815513</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001550861772250988</v>
+        <v>0.001550861772250987</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005114636548637963</v>
+        <v>0.005114636548637965</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00224289969078551</v>
+        <v>0.002242899690785507</v>
       </c>
       <c r="D4" t="n">
         <v>0.01312654017355685</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006503457550072243</v>
+        <v>0.006503457550072239</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005153526663096353</v>
+        <v>0.00515352666309635</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007204158631227374</v>
+        <v>0.007204158631227373</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009829840480801206</v>
+        <v>0.009829840480801214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01023429802182443</v>
+        <v>0.01023429802182442</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009443150055338863</v>
+        <v>0.009443150055338865</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0173892236765182</v>
+        <v>0.01738922367651821</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01207815122657668</v>
+        <v>0.01207815122657669</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0232644481265252</v>
+        <v>0.02326444812652521</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01478255942103761</v>
+        <v>0.0147825594210376</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005859841063303995</v>
+        <v>0.005859841063304009</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01026407805856432</v>
+        <v>0.0102640780585643</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00943688623099709</v>
+        <v>0.009436886230997078</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008906578872142905</v>
+        <v>0.008906578872142894</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008187665823803507</v>
+        <v>0.008187665823803508</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007559955550481316</v>
+        <v>0.007559955550481312</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01278462668623851</v>
+        <v>0.01278462668623852</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004692118863054494</v>
+        <v>0.00469211886305449</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01532703619279302</v>
+        <v>0.01532703619279304</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01296824201209165</v>
+        <v>0.01296824201209166</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005886721841097164</v>
+        <v>0.005886721841097139</v>
       </c>
       <c r="Z4" t="n">
         <v>0.007961161084279732</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01431893788930405</v>
+        <v>0.01431893788930403</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01210672195433107</v>
+        <v>0.01210672195433106</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001466802026870912</v>
+        <v>0.001466802026870914</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001813076169853357</v>
+        <v>0.001813076169853355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001582186114269469</v>
+        <v>0.001582186114269473</v>
       </c>
       <c r="G5" t="n">
         <v>0.00236102654943147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002205674734914835</v>
+        <v>0.002205674734914834</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002207448647737396</v>
+        <v>0.002207448647737402</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01478255942103761</v>
+        <v>0.00163332360905971</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001791098154683572</v>
+        <v>0.001791098154683573</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001752423801188849</v>
+        <v>0.001752423801188852</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001321248061460918</v>
+        <v>0.001321248061460921</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001845481619949717</v>
+        <v>0.001845481619949719</v>
       </c>
       <c r="V5" t="n">
         <v>0.00199305846339668</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002207594205923452</v>
+        <v>0.002207594205923456</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001389129795891853</v>
+        <v>0.001389129795891854</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002943057314766105</v>
+        <v>0.002943057314766109</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001453044135646539</v>
+        <v>0.001453044135646537</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00220744864773737</v>
+        <v>0.002207448647737375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002981115975007903</v>
+        <v>0.002981115975007901</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001999229181062164</v>
+        <v>0.001999229181062163</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002360458576816659</v>
+        <v>0.002360458576816661</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001386254077009014</v>
+        <v>0.001386254077009016</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002468843689944666</v>
+        <v>0.002468843689944668</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002467069665274985</v>
+        <v>0.002467069665274989</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01478255942103761</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002624473323283529</v>
+        <v>0.002624473323283536</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002658320098377426</v>
+        <v>0.002658320098377432</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002468843689944666</v>
+        <v>0.002468843689944668</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002999323423773576</v>
+        <v>0.002999323423773579</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002185707900840085</v>
+        <v>0.002185707900840091</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002468843578097531</v>
+        <v>0.002468843578097533</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00150778341777437</v>
+        <v>0.001507783417774369</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00158967648849201</v>
+        <v>0.001589676488492009</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001353310997329031</v>
+        <v>0.001353310997329032</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002664294398657063</v>
+        <v>0.002664294398657069</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0015237614890678</v>
+        <v>0.001523761489067798</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001418929428442395</v>
+        <v>0.001418929428442394</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001432427758828829</v>
+        <v>0.001432427758828831</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001417010204516542</v>
+        <v>0.001417010204516543</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001408096174400455</v>
+        <v>0.001408096174400456</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001231655889870743</v>
+        <v>0.001231655889870744</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001333798676948482</v>
+        <v>0.001333798676948481</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001102972155765655</v>
+        <v>0.001102972155765654</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001303651189132861</v>
+        <v>0.00130365118913286</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001486951466710991</v>
+        <v>0.001486951466710992</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001387719339650086</v>
+        <v>0.001387719339650088</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001419149465239961</v>
+        <v>0.00141914946523996</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001448797917022397</v>
+        <v>0.001448797917022401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001417755553871376</v>
+        <v>0.001417755553871375</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001465828021346024</v>
+        <v>0.001465828021346023</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001335297303881366</v>
+        <v>0.001335297303881368</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001506424236091523</v>
+        <v>0.001506424236091522</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001295203403273987</v>
+        <v>0.001295203403273986</v>
       </c>
       <c r="X7" t="n">
         <v>0.00134846504561481</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001499629657052083</v>
+        <v>0.001499629657052085</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001435609245923333</v>
+        <v>0.001435609245923331</v>
       </c>
       <c r="AA7" t="n">
         <v>0.001316672421680182</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001316814558574217</v>
+        <v>0.001316814558574215</v>
       </c>
     </row>
     <row r="8">
@@ -4974,82 +4974,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001548087308842272</v>
+        <v>0.001548087308842273</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001576897741117231</v>
+        <v>0.001576897741117232</v>
       </c>
       <c r="D8" t="n">
         <v>0.001504456601191114</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002704668977253123</v>
+        <v>0.002704668977253125</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001554889524860792</v>
+        <v>0.001554889524860793</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001502408569554058</v>
+        <v>0.001502408569554057</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001527160307151592</v>
+        <v>0.001527160307151593</v>
       </c>
       <c r="I8" t="n">
         <v>0.001522628726193871</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001518838519723242</v>
+        <v>0.001518838519723241</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001470798899601893</v>
+        <v>0.001470798899601895</v>
       </c>
       <c r="L8" t="n">
         <v>0.001498467872616334</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001433622857602166</v>
+        <v>0.001433622857602165</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00149011492245062</v>
+        <v>0.001490114922450619</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001542086860567218</v>
+        <v>0.00154208686056722</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001513563835291547</v>
+        <v>0.001513563835291548</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001523087868340162</v>
+        <v>0.001523087868340164</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001531905799273182</v>
+        <v>0.001531905799273181</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001522360095711143</v>
+        <v>0.001522360095711142</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001536459487575774</v>
+        <v>0.001536459487575771</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001498848996157627</v>
+        <v>0.001498848996157628</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001539505322937242</v>
+        <v>0.001539505322937241</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001487525902144171</v>
+        <v>0.001487525902144172</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001500263568459802</v>
+        <v>0.001500263568459801</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001545935317904354</v>
+        <v>0.001545935317904355</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001527646700070556</v>
+        <v>0.001527646700070555</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001493697963246072</v>
+        <v>0.00149369796324607</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001453747597880632</v>
@@ -5218,22 +5218,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001581902814239537</v>
+        <v>0.001581902814239536</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001592092938919151</v>
+        <v>0.001592092938919149</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001587045087761149</v>
+        <v>0.001587045087761148</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002753982996441043</v>
+        <v>0.002753982996441042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001594611304562346</v>
+        <v>0.001594611304562345</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001555517313837422</v>
+        <v>0.001555517313837421</v>
       </c>
       <c r="H2" t="n">
         <v>0.001590259408424433</v>
@@ -5242,46 +5242,46 @@
         <v>0.001590717642991543</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001591778259155005</v>
+        <v>0.001591778259155004</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001588180411722523</v>
+        <v>0.001588180411722522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001590028709566624</v>
+        <v>0.001590028709566623</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001582436385723909</v>
+        <v>0.001582436385723908</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001595753829462528</v>
+        <v>0.001595753829462527</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001597054360976301</v>
+        <v>0.0015970543609763</v>
       </c>
       <c r="P2" t="n">
         <v>0.001591876273652847</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001582078414222041</v>
+        <v>0.00158207841422204</v>
       </c>
       <c r="R2" t="n">
         <v>0.001592846816642182</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001591946307015349</v>
+        <v>0.00159194630701535</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001583280580693227</v>
+        <v>0.001583280580693225</v>
       </c>
       <c r="U2" t="n">
         <v>0.001580814254642115</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001581460556568648</v>
+        <v>0.00158146055656865</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001612633628692655</v>
+        <v>0.001612633628692654</v>
       </c>
       <c r="X2" t="n">
         <v>0.001605831630709877</v>
@@ -5290,10 +5290,10 @@
         <v>0.001596031297929146</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001598382574704008</v>
+        <v>0.001598382574704006</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001606129855488863</v>
+        <v>0.001606129855488862</v>
       </c>
       <c r="AB2" t="n">
         <v>0.001518607532170864</v>
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001616327422260717</v>
+        <v>0.001616327422260716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00279026223805178</v>
+        <v>0.002790262238051778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001611817795622393</v>
+        <v>0.001611817795622392</v>
       </c>
       <c r="G3" t="n">
         <v>0.001569266204106636</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="J3" t="n">
         <v>0.001606865781413451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00160986188964217</v>
+        <v>0.001609861889642169</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="R3" t="n">
         <v>0.001598838093693832</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001595838447658399</v>
+        <v>0.00159583844765839</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00155499987148945</v>
+        <v>0.001554999871489449</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001608190150551099</v>
+        <v>0.001608190150551098</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001607563964469865</v>
+        <v>0.001607563964469864</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001543481228905339</v>
+        <v>0.001543481228905338</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003015561209681003</v>
+        <v>0.003015561209681006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003749477289012973</v>
+        <v>0.003749477289012968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004481644382045385</v>
+        <v>0.00448164438204538</v>
       </c>
       <c r="E4" t="n">
         <v>0.005010734596976118</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005463314148234538</v>
+        <v>0.005463314148234534</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004769117725434422</v>
+        <v>0.004769117725434431</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005648855491658074</v>
+        <v>0.005648855491658073</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00554719715738956</v>
+        <v>0.00554719715738955</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005457156930983579</v>
+        <v>0.005457156930983576</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004129144430939525</v>
+        <v>0.004129144430939521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004594869585344518</v>
+        <v>0.004594869585344506</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003330824082295199</v>
+        <v>0.003330824082295193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006508376546270468</v>
+        <v>0.006508376546270457</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00631795549244652</v>
+        <v>0.006317955492446529</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005305472030196536</v>
+        <v>0.005305472030196541</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003070456325275989</v>
+        <v>0.003070456325275986</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008292695713393321</v>
+        <v>0.008292695713393307</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005007826115901692</v>
+        <v>0.005007826115901691</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003572025229982539</v>
+        <v>0.003572025229982534</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002794241644577977</v>
+        <v>0.002794241644577974</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005446237911630371</v>
+        <v>0.005446237911630382</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01040849010760335</v>
+        <v>0.01040849010760334</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02051502943230481</v>
+        <v>0.02051502943230483</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006760268682439265</v>
+        <v>0.006760268682439266</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006452558493934018</v>
+        <v>0.006452558493934004</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009293574919917965</v>
+        <v>0.009293574919917981</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00211600792582814</v>
+        <v>0.002116007925828137</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001357847474120227</v>
+        <v>0.001357847474120223</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001670834095409274</v>
+        <v>0.001670834095409268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001462139626443826</v>
+        <v>0.001462139626443823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002166109706985387</v>
+        <v>0.002166109706985378</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00202571938724295</v>
+        <v>0.002025719387242938</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002027295332507311</v>
+        <v>0.002027295332507302</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006508376546270468</v>
+        <v>0.001508361246048053</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001650968838793635</v>
+        <v>0.001650968838793626</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001616012271933631</v>
+        <v>0.001616012271933625</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001226285690567059</v>
+        <v>0.001226285690567057</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001700134941087475</v>
+        <v>0.00170013494108747</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001833702324879873</v>
+        <v>0.001833702324879865</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002027426898109064</v>
+        <v>0.002027426898109057</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001287641916950191</v>
+        <v>0.001287641916950186</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002692207584777792</v>
+        <v>0.002692207584777781</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00134541213646179</v>
+        <v>0.001345412136461785</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002027295332507389</v>
+        <v>0.00202729533250738</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002726589598835401</v>
+        <v>0.00272658959883539</v>
       </c>
     </row>
     <row r="6">
@@ -5573,82 +5573,82 @@
         <v>0.001736995670822968</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002041781187801341</v>
+        <v>0.002041781187801337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001219800956938792</v>
+        <v>0.001219800956938791</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002133230591215773</v>
+        <v>0.002133230591215771</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002131654336552796</v>
+        <v>0.002131654336552785</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="N6" t="n">
-        <v>0.006508376546270468</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002264542325011328</v>
+        <v>0.002264542325011329</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002293100374179618</v>
+        <v>0.002293100374179611</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002133230591215773</v>
+        <v>0.002133230591215771</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002580308268362658</v>
+        <v>0.002580308268362643</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001894336168802881</v>
+        <v>0.001894336168802878</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00213323028181723</v>
+        <v>0.002133230281817232</v>
       </c>
     </row>
     <row r="7">
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001546433962742753</v>
+        <v>0.001546433962742752</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001543281356084394</v>
+        <v>0.001543281356084393</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00151726226574383</v>
+        <v>0.001517262265743829</v>
       </c>
       <c r="E7" t="n">
         <v>0.002681723330690936</v>
@@ -5679,25 +5679,25 @@
         <v>0.00149917374782114</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001495960396099117</v>
+        <v>0.001495960396099116</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001483566008886668</v>
+        <v>0.00148356600888667</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001525089619369523</v>
+        <v>0.001525089619369522</v>
       </c>
       <c r="L7" t="n">
         <v>0.00149878172124109</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001544500011916518</v>
+        <v>0.001544500011916517</v>
       </c>
       <c r="N7" t="n">
         <v>0.001465650601711862</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001456129498117372</v>
+        <v>0.001456129498117373</v>
       </c>
       <c r="P7" t="n">
         <v>0.001486860836305383</v>
@@ -5712,31 +5712,31 @@
         <v>0.001487058232770742</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001539356648720509</v>
+        <v>0.00153935664872051</v>
       </c>
       <c r="U7" t="n">
         <v>0.001553201392556295</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001468347108325216</v>
+        <v>0.001468347108325206</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00136555035913844</v>
+        <v>0.001365550359138438</v>
       </c>
       <c r="X7" t="n">
         <v>0.001072828433443073</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001463770287024314</v>
+        <v>0.001463770287024313</v>
       </c>
       <c r="Z7" t="n">
         <v>0.001452596610686909</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001404101436106556</v>
+        <v>0.001404101436106555</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001511042417008642</v>
+        <v>0.001511042417008641</v>
       </c>
     </row>
     <row r="8">
@@ -5746,19 +5746,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001554088468643945</v>
+        <v>0.001554088468643944</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001558856746024922</v>
+        <v>0.001558856746024921</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001545957527066363</v>
+        <v>0.001545957527066362</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002704597447698887</v>
+        <v>0.002704597447698886</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001543968099524986</v>
+        <v>0.001543968099524985</v>
       </c>
       <c r="G8" t="n">
         <v>0.001504419904905212</v>
@@ -5767,7 +5767,7 @@
         <v>0.001540941514430139</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001539937663723388</v>
+        <v>0.001539937663723387</v>
       </c>
       <c r="J8" t="n">
         <v>0.001535676469722258</v>
@@ -5782,31 +5782,31 @@
         <v>0.001553742086339242</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001531182797156587</v>
+        <v>0.001531182797156585</v>
       </c>
       <c r="O8" t="n">
         <v>0.001528151196192905</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001536955965679961</v>
+        <v>0.001536955965679963</v>
       </c>
       <c r="Q8" t="n">
         <v>0.001554156205744293</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001515351964874153</v>
+        <v>0.001515351964874152</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001537115815063267</v>
+        <v>0.001537115815063268</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001552246034663451</v>
+        <v>0.001552246034663452</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001556079111178202</v>
+        <v>0.001556079111178201</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001523451590881258</v>
+        <v>0.00152345159088126</v>
       </c>
       <c r="W8" t="n">
         <v>0.001502516667015257</v>
@@ -5818,13 +5818,13 @@
         <v>0.00153060471644816</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001527587018218609</v>
+        <v>0.001527587018218608</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001513553756686952</v>
+        <v>0.001513553756686951</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001503847769381507</v>
+        <v>0.001503847769381506</v>
       </c>
     </row>
   </sheetData>
@@ -5990,61 +5990,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001521306766697391</v>
+        <v>0.00152130676669739</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001526458837025366</v>
+        <v>0.001526458837025364</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001522119322959586</v>
+        <v>0.001522119322959584</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002760196902538331</v>
+        <v>0.002760196902538327</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001527598693773095</v>
+        <v>0.001527598693773093</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001459295184860839</v>
+        <v>0.001459295184860837</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001518407330227948</v>
+        <v>0.001518407330227946</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001518696285626074</v>
+        <v>0.001518696285626072</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001523735543859434</v>
+        <v>0.001523735543859433</v>
       </c>
       <c r="K2" t="n">
         <v>0.00151980338103833</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001525668639278507</v>
+        <v>0.001525668639278506</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001516014465974665</v>
+        <v>0.001516014465974664</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001522867875461612</v>
+        <v>0.001522867875461609</v>
       </c>
       <c r="O2" t="n">
         <v>0.001547435680319057</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001531311108607665</v>
+        <v>0.001531311108607664</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00151498446686057</v>
+        <v>0.001514984466860569</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001521110863868738</v>
+        <v>0.001521110863868737</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001523294292337579</v>
+        <v>0.001523294292337578</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001515748555499459</v>
+        <v>0.001515748555499458</v>
       </c>
       <c r="U2" t="n">
         <v>0.001516101773787585</v>
@@ -6053,22 +6053,22 @@
         <v>0.001470373296051088</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001538579433361133</v>
+        <v>0.001538579433361132</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001584963774244111</v>
+        <v>0.001584963774244109</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001528637272413322</v>
+        <v>0.00152863727241332</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001526632706435688</v>
+        <v>0.001526632706435687</v>
       </c>
       <c r="AA2" t="n">
         <v>0.001542995766268653</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001456568824688024</v>
+        <v>0.001456568824688023</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>0.00154095941086753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002791250319155295</v>
+        <v>0.002791250319155294</v>
       </c>
       <c r="F3" t="n">
         <v>0.00154660504842184</v>
@@ -6102,10 +6102,10 @@
         <v>0.00154095941086753</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001540581500289902</v>
+        <v>0.001540581500289901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001543905259189881</v>
+        <v>0.00154390525918988</v>
       </c>
       <c r="L3" t="n">
         <v>0.00154095941086753</v>
@@ -6144,19 +6144,19 @@
         <v>0.00154095941086753</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001516861413348253</v>
+        <v>0.001516861413348252</v>
       </c>
       <c r="Y3" t="n">
         <v>0.00154095941086753</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001541575543554439</v>
+        <v>0.001541575543554438</v>
       </c>
       <c r="AA3" t="n">
         <v>0.00154095941086753</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001476876675303005</v>
+        <v>0.001476876675303004</v>
       </c>
     </row>
     <row r="4">
@@ -6166,85 +6166,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0041399401788036</v>
+        <v>0.004139940178803598</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003737148057046068</v>
+        <v>0.003737148057046072</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004669980873640746</v>
+        <v>0.004669980873640743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006024495363000515</v>
+        <v>0.006024495363000508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00485172581750071</v>
+        <v>0.004851725817500714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003648811129282405</v>
+        <v>0.003648811129282413</v>
       </c>
       <c r="H4" t="n">
         <v>0.003927653842976187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003898064395968177</v>
+        <v>0.003898064395968173</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004889878722574733</v>
+        <v>0.004889878722574738</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003370073649189049</v>
+        <v>0.003370073649189047</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004995562811878133</v>
+        <v>0.004995562811878134</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003178101448906851</v>
+        <v>0.003178101448906852</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004789984538979586</v>
+        <v>0.004789984538979582</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009871864235761175</v>
+        <v>0.009871864235761165</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006320229098151884</v>
+        <v>0.006320229098151878</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00277897794111323</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008681327210563271</v>
+        <v>0.00868132721056326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004522744147273754</v>
+        <v>0.004522744147273751</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003101687573624835</v>
+        <v>0.003101687573624833</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002969834823864521</v>
+        <v>0.002969834823864518</v>
       </c>
       <c r="V4" t="n">
-        <v>0.005945482676833283</v>
+        <v>0.005945482676833291</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008508091440559012</v>
+        <v>0.00850809144055902</v>
       </c>
       <c r="X4" t="n">
         <v>0.0246292263806746</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006341903206356122</v>
+        <v>0.006341903206356131</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00500037443681386</v>
+        <v>0.005000374436813856</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009927352614872096</v>
+        <v>0.0099273526148721</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003049897314202064</v>
+        <v>0.003049897314202061</v>
       </c>
     </row>
     <row r="5">
@@ -6257,82 +6257,82 @@
         <v>0.001354328233331726</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001665679513401943</v>
+        <v>0.00166567951340194</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001458075463784433</v>
+        <v>0.001458075463784432</v>
       </c>
       <c r="G5" t="n">
         <v>0.002158367331870108</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002018702152334981</v>
+        <v>0.002018702152334982</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002020278256343112</v>
+        <v>0.002020278256343111</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004789984538979587</v>
+        <v>0.001504055577476414</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001645918051875462</v>
+        <v>0.00164591805187546</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001611144131526465</v>
+        <v>0.00161114413152646</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001223453854262689</v>
+        <v>0.001223453854262691</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001694848320273838</v>
+        <v>0.001694848320273837</v>
       </c>
       <c r="V5" t="n">
         <v>0.001827649944207034</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002020409134525083</v>
+        <v>0.002020409134525081</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001284489497086462</v>
+        <v>0.00128448949708646</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002681752393654745</v>
+        <v>0.002681752393654742</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00134195786976073</v>
+        <v>0.001341957869760729</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002020278256343207</v>
+        <v>0.002020278256343206</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002715918741141829</v>
+        <v>0.002715918741141827</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001634158471144223</v>
+        <v>0.001634158471144224</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001916645276448834</v>
+        <v>0.001916645276448829</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001154802746193539</v>
+        <v>0.001154802746193537</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002001404060506824</v>
+        <v>0.002001404060506822</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00199982768634967</v>
+        <v>0.001999827686349667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004789984538979586</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002123108767957268</v>
+        <v>0.002123108767957265</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002149577453724296</v>
+        <v>0.002149577453724289</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002001404060506824</v>
+        <v>0.002001404060506822</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002415011803363914</v>
+        <v>0.002415011803363912</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001779987626873246</v>
+        <v>0.001779987626873245</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002001403790357897</v>
+        <v>0.002001403790357892</v>
       </c>
     </row>
     <row r="7">
@@ -6430,43 +6430,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001450541219407468</v>
+        <v>0.001450541219407467</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001477133187911732</v>
+        <v>0.001477133187911734</v>
       </c>
       <c r="D7" t="n">
         <v>0.001447182107260461</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00265198932062344</v>
+        <v>0.002651989320623438</v>
       </c>
       <c r="F7" t="n">
         <v>0.001451421194446485</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001396587507335388</v>
+        <v>0.001396587507335387</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001469414519756211</v>
+        <v>0.00146941451975621</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001467371595226729</v>
+        <v>0.001467371595226728</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001434208518250197</v>
+        <v>0.001434208518250195</v>
       </c>
       <c r="K7" t="n">
         <v>0.001479370098528886</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001425325061883562</v>
+        <v>0.001425325061883561</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00148316355268079</v>
+        <v>0.001483163552680789</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001442380070462693</v>
+        <v>0.001442380070462692</v>
       </c>
       <c r="O7" t="n">
         <v>0.001294827494760286</v>
@@ -6478,37 +6478,37 @@
         <v>0.001488840534456574</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001346934397997348</v>
+        <v>0.001346934397997347</v>
       </c>
       <c r="S7" t="n">
         <v>0.001439034284194482</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001484535255246601</v>
+        <v>0.001484535255246602</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001481823368831933</v>
+        <v>0.001481823368831932</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001342423594100451</v>
+        <v>0.001342423594100452</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001349319614063831</v>
+        <v>0.00134931961406383</v>
       </c>
       <c r="X7" t="n">
-        <v>0.000925410974971873</v>
+        <v>0.000925410974971872</v>
       </c>
       <c r="Y7" t="n">
         <v>0.001408213513284151</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001422954133130191</v>
+        <v>0.00142295413313019</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001323431934723536</v>
+        <v>0.001323431934723534</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001424055889671082</v>
+        <v>0.001424055889671081</v>
       </c>
     </row>
     <row r="8">
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001480166201437383</v>
+        <v>0.001480166201437382</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001493445888694629</v>
+        <v>0.00149344588869463</v>
       </c>
       <c r="D8" t="n">
         <v>0.001479450350967837</v>
@@ -6530,46 +6530,46 @@
         <v>0.002696832704407864</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001484289736881364</v>
+        <v>0.001484289736881362</v>
       </c>
       <c r="G8" t="n">
         <v>0.001423501838274637</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001485854176772256</v>
+        <v>0.001485854176772255</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001485213594999054</v>
+        <v>0.001485213594999055</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001475335498040786</v>
+        <v>0.001475335498040785</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001490439677276223</v>
+        <v>0.001490439677276224</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001473054641985998</v>
+        <v>0.001473054641985997</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001489717166315227</v>
+        <v>0.001489717166315225</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001478013961423692</v>
+        <v>0.001478013961423691</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001435444874114383</v>
+        <v>0.001435444874114384</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001462954459277908</v>
+        <v>0.001462954459277907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00149127021200058</v>
+        <v>0.001491270212000581</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001440482331005399</v>
+        <v>0.0014404823310054</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001476918034885234</v>
+        <v>0.001476918034885233</v>
       </c>
       <c r="T8" t="n">
         <v>0.00149007538487882</v>
@@ -6584,19 +6584,19 @@
         <v>0.001451382715095653</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001315851939942144</v>
+        <v>0.001315851939942142</v>
       </c>
       <c r="Y8" t="n">
         <v>0.001468237465976809</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001472659586668649</v>
+        <v>0.001472659586668648</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001444020071404202</v>
+        <v>0.001444020071404199</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001432535198895644</v>
+        <v>0.001432535198895642</v>
       </c>
     </row>
   </sheetData>
@@ -6762,19 +6762,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001664777832319006</v>
+        <v>0.001664777832319007</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001634797937021253</v>
+        <v>0.001634797937021254</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00167319643092231</v>
+        <v>0.001673196430922312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002789384114572213</v>
+        <v>0.002789384114572215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001647285806156658</v>
+        <v>0.001647285806156657</v>
       </c>
       <c r="G2" t="n">
         <v>0.001664345282203535</v>
@@ -6786,61 +6786,61 @@
         <v>0.001679570844119698</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001688668636606285</v>
+        <v>0.001688668636606284</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001716895205408374</v>
+        <v>0.001716895205408375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001692233978421182</v>
+        <v>0.001692233978421184</v>
       </c>
       <c r="M2" t="n">
         <v>0.001864827787758998</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001714374237111346</v>
+        <v>0.001714374237111347</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001662990300160151</v>
+        <v>0.001662990300160152</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001683268273973406</v>
+        <v>0.001683268273973407</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001654696367800187</v>
+        <v>0.001654696367800191</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001657186607130682</v>
+        <v>0.001657186607130684</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001672646514442528</v>
+        <v>0.001672646514442527</v>
       </c>
       <c r="T2" t="n">
         <v>0.001674437228688235</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001702210465543262</v>
+        <v>0.001702210465543263</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001624057918236298</v>
+        <v>0.001624057918236301</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001669948941722104</v>
+        <v>0.001669948941722106</v>
       </c>
       <c r="X2" t="n">
         <v>0.001688439052114125</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001668041037823598</v>
+        <v>0.0016680410378236</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001656700758973561</v>
+        <v>0.001656700758973562</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001696166738839468</v>
+        <v>0.00169616673883947</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001669698718254091</v>
+        <v>0.001669698718254092</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001659260814968755</v>
+        <v>0.001659260814968757</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002817794484634852</v>
+        <v>0.002817794484634856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001653930387554993</v>
+        <v>0.001653930387554996</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001618693670657427</v>
+        <v>0.001618693670657429</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001648493019758962</v>
+        <v>0.001648493019758963</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00165253636216077</v>
+        <v>0.001652536362160772</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001651219933573648</v>
+        <v>0.00165121993357365</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001633970108065508</v>
+        <v>0.001633970108065509</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001646512612823039</v>
+        <v>0.001646512612823041</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001651288722339325</v>
+        <v>0.001651288722339327</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001650916316536466</v>
+        <v>0.001650916316536469</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00158683358097194</v>
+        <v>0.001586833580971943</v>
       </c>
     </row>
     <row r="4">
@@ -6938,79 +6938,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01316687481774099</v>
+        <v>0.01316687481774114</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00416696499851402</v>
+        <v>0.004166964998514025</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01733065204064181</v>
+        <v>0.01733065204064182</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007581373341692526</v>
+        <v>0.007581373341692555</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009101374184663233</v>
+        <v>0.009101374184663228</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02015399670386038</v>
+        <v>0.0201539967038604</v>
       </c>
       <c r="H4" t="n">
         <v>0.01115973273791365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01913557135634236</v>
+        <v>0.01913557135634235</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02034848188008178</v>
+        <v>0.02034848188008181</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0262697754555031</v>
+        <v>0.02626977545550311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02088756038555848</v>
+        <v>0.02088756038555883</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06626245403688621</v>
+        <v>0.06626245403688634</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02822703414332062</v>
+        <v>0.02822703414332061</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01243356186876324</v>
+        <v>0.01243356186876323</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01821508948558201</v>
+        <v>0.01821508948558202</v>
       </c>
       <c r="Q4" t="n">
         <v>0.01151895861522909</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01297802692495223</v>
+        <v>0.01297802692495222</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01468368141347405</v>
+        <v>0.01468368141347411</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01764191623787877</v>
+        <v>0.01764191623787878</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02365161531751597</v>
+        <v>0.0236516153175161</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007188358023194943</v>
+        <v>0.007188358023194973</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01570346573170407</v>
+        <v>0.01570346573170408</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02239234400928655</v>
+        <v>0.02239234400928678</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01500899800913264</v>
+        <v>0.01500899800913265</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01116168840738217</v>
+        <v>0.01116168840738218</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02277536879887756</v>
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001576580397724533</v>
+        <v>0.001576580397724538</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.00237614599711593</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.00237614599711593</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00195040090117226</v>
+        <v>0.001950400901172267</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001701143373374755</v>
+        <v>0.001701143373374756</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002541941132827602</v>
+        <v>0.002541941132827608</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.002376145997115929</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.00237614599711593</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002374124517947748</v>
+        <v>0.002374124517947752</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.00237614599711593</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.00237614599711593</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002376145997116099</v>
+        <v>0.002376145997116103</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02822703414332062</v>
+        <v>0.001756348893146821</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001926674518867425</v>
+        <v>0.001926674518867427</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001884923592365375</v>
+        <v>0.001884923592365378</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001419447508279476</v>
+        <v>0.001419447508279478</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.002376145997115929</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.002376145997115928</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.00237614599711593</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00198540013758299</v>
+        <v>0.001985400137582995</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002144048115238461</v>
+        <v>0.002144048115238462</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00237630313455182</v>
+        <v>0.002376303134551821</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00149272928415509</v>
+        <v>0.001492729284155089</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003170300085689903</v>
+        <v>0.00317030008568991</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001561728056226807</v>
+        <v>0.001561728056226809</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002376145997115925</v>
+        <v>0.002376145997115929</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00321135912416373</v>
+        <v>0.003211359124163718</v>
       </c>
     </row>
     <row r="6">
@@ -7117,82 +7117,82 @@
         <v>0.002261469857953623</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002674858151356188</v>
+        <v>0.00267485815135618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00155998560683565</v>
+        <v>0.001559985606835653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002798893286571584</v>
+        <v>0.002798893286571587</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002796872161121968</v>
+        <v>0.002796872161121961</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02822703414332062</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002976994707122594</v>
+        <v>0.002976994707122598</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003015728710384186</v>
+        <v>0.003015728710384189</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002798893286571584</v>
+        <v>0.002798893286571587</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003406042092662683</v>
+        <v>0.003406042092662691</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002474874748670944</v>
+        <v>0.002474874748670946</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002798893640290147</v>
+        <v>0.002798893640290149</v>
       </c>
     </row>
     <row r="7">
@@ -7208,10 +7208,10 @@
         <v>0.001585017201684676</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001307172678741039</v>
+        <v>0.00130717267874104</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002661364897253559</v>
+        <v>0.002661364897253564</v>
       </c>
       <c r="F7" t="n">
         <v>0.001478953347298714</v>
@@ -7220,25 +7220,25 @@
         <v>0.001147304838756495</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001443127743236583</v>
+        <v>0.001443127743236586</v>
       </c>
       <c r="I7" t="n">
         <v>0.001270548697781138</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001196598891693417</v>
+        <v>0.001196598891693418</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001060658913004211</v>
+        <v>0.001060658913004212</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001191433851265649</v>
+        <v>0.001191433851265648</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001902522202284359</v>
+        <v>0.0001902522202284374</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00106349545228894</v>
+        <v>0.001063495452288944</v>
       </c>
       <c r="O7" t="n">
         <v>0.001362189852805884</v>
@@ -7247,40 +7247,40 @@
         <v>0.001241057088861432</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001414934138876538</v>
+        <v>0.001414934138876539</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00140386023698298</v>
+        <v>0.001403860236982979</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001306127471922945</v>
+        <v>0.001306127471922946</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001300127881168387</v>
+        <v>0.001300127881168389</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001131936349380005</v>
+        <v>0.001131936349380003</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0014772251591016</v>
+        <v>0.001477225159101602</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001323727087727794</v>
+        <v>0.001323727087727796</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001189473023961122</v>
+        <v>0.001189473023961121</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001335498518397266</v>
+        <v>0.001335498518397269</v>
       </c>
       <c r="Z7" t="n">
         <v>0.001402595525020604</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001169382474076392</v>
+        <v>0.001169382474076396</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0009207105185101062</v>
+        <v>0.0009207105185101093</v>
       </c>
     </row>
     <row r="8">
@@ -7290,28 +7290,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001528710883365596</v>
+        <v>0.001528710883365595</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001601016856376638</v>
+        <v>0.00160101685637664</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001516791980279411</v>
+        <v>0.001516791980279413</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00271820815380221</v>
+        <v>0.002718208153802212</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001567670695221312</v>
+        <v>0.001567670695221313</v>
       </c>
       <c r="G8" t="n">
         <v>0.001449861861461535</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001555683158825194</v>
+        <v>0.001555683158825197</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001506502365426345</v>
+        <v>0.001506502365426346</v>
       </c>
       <c r="J8" t="n">
         <v>0.001483055368235322</v>
@@ -7326,16 +7326,16 @@
         <v>0.001200220969078563</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001447095871879502</v>
+        <v>0.001447095871879505</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00153161883904609</v>
+        <v>0.001531618839046092</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001496781019237407</v>
+        <v>0.00149678101923741</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001547323724934343</v>
+        <v>0.001547323724934345</v>
       </c>
       <c r="R8" t="n">
         <v>0.001544637156893347</v>
@@ -7344,31 +7344,31 @@
         <v>0.001515766491366523</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001514827372699343</v>
+        <v>0.001514827372699346</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001466072926596049</v>
+        <v>0.00146607292659605</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001552738466941206</v>
+        <v>0.001552738466941207</v>
       </c>
       <c r="W8" t="n">
         <v>0.001521076799923953</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001480484582683204</v>
+        <v>0.001480484582683206</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00152452493449338</v>
+        <v>0.001524524934493379</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001543544561655351</v>
+        <v>0.001543544561655352</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001477067305962831</v>
+        <v>0.001477067305962832</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001366610602025711</v>
+        <v>0.001366610602025712</v>
       </c>
     </row>
   </sheetData>
@@ -7537,13 +7537,13 @@
         <v>0.001594932034292706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001608418866346842</v>
+        <v>0.001608418866346841</v>
       </c>
       <c r="D2" t="n">
         <v>0.00160600909557863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002762070757495282</v>
+        <v>0.002762070757495285</v>
       </c>
       <c r="F2" t="n">
         <v>0.001606557589837907</v>
@@ -7555,7 +7555,7 @@
         <v>0.0016064870673505</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001605585677081673</v>
+        <v>0.001605585677081674</v>
       </c>
       <c r="J2" t="n">
         <v>0.001625586856939405</v>
@@ -7567,43 +7567,43 @@
         <v>0.001633193958038691</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001618817433486407</v>
+        <v>0.001618817433486406</v>
       </c>
       <c r="N2" t="n">
         <v>0.001615036182255771</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00160636641989733</v>
+        <v>0.001606366419897331</v>
       </c>
       <c r="P2" t="n">
         <v>0.001637371723804834</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00161195505362036</v>
+        <v>0.001611955053620361</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001610633230080581</v>
+        <v>0.001610633230080582</v>
       </c>
       <c r="S2" t="n">
         <v>0.001614054339988914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001605561108034619</v>
+        <v>0.001605561108034618</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0016089236141427</v>
+        <v>0.001608923614142698</v>
       </c>
       <c r="V2" t="n">
         <v>0.001590212175963467</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001634793203283393</v>
+        <v>0.001634793203283395</v>
       </c>
       <c r="X2" t="n">
         <v>0.001618885437349186</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001671536645199824</v>
+        <v>0.001671536645199823</v>
       </c>
       <c r="Z2" t="n">
         <v>0.001607734564092613</v>
@@ -7612,7 +7612,7 @@
         <v>0.001618768975983039</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001606598899502329</v>
+        <v>0.001606598899502328</v>
       </c>
     </row>
     <row r="3">
@@ -7631,7 +7631,7 @@
         <v>0.001624152024066125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002800071548010017</v>
+        <v>0.002800071548010016</v>
       </c>
       <c r="F3" t="n">
         <v>0.001628405855218653</v>
@@ -7646,7 +7646,7 @@
         <v>0.001624152024066125</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001622092857067331</v>
+        <v>0.00162209285706733</v>
       </c>
       <c r="K3" t="n">
         <v>0.00162644994923843</v>
@@ -7682,7 +7682,7 @@
         <v>0.001624152024066125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001607460724891385</v>
+        <v>0.001607460724891386</v>
       </c>
       <c r="W3" t="n">
         <v>0.001624152024066125</v>
@@ -7713,82 +7713,82 @@
         <v>0.002225351909686527</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003741020329766891</v>
+        <v>0.003741020329766892</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005230443850715898</v>
+        <v>0.005230443850715903</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004609126910880277</v>
+        <v>0.004609126910880283</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004381753105991551</v>
+        <v>0.004381753105991553</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01619701743303335</v>
+        <v>0.01619701743303332</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005673247964473307</v>
+        <v>0.005673247964473309</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005243752084444356</v>
+        <v>0.005243752084444358</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009760593768340785</v>
+        <v>0.009760593768340797</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007502283420409671</v>
+        <v>0.007502283420409676</v>
       </c>
       <c r="L4" t="n">
-        <v>0.010977511974028</v>
+        <v>0.01097751197402801</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008156321572537409</v>
+        <v>0.008156321572537406</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007533391041597318</v>
+        <v>0.007533391041597328</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004771257027756107</v>
+        <v>0.004771257027756115</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01204851016314379</v>
+        <v>0.01204851016314377</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006262414550280036</v>
+        <v>0.006262414550280035</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008829919882542822</v>
+        <v>0.008829919882542831</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006454944361519756</v>
+        <v>0.006454944361519753</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00517661675973485</v>
+        <v>0.005176616759734836</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005516541330072209</v>
+        <v>0.005516541330072207</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004898834630390935</v>
+        <v>0.004898834630390933</v>
       </c>
       <c r="W4" t="n">
         <v>0.01242010570684598</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02042013047281291</v>
+        <v>0.02042013047281289</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02148327727177585</v>
+        <v>0.02148327727177581</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004922786682256559</v>
+        <v>0.004922786682256556</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008360013748615579</v>
+        <v>0.008360013748615577</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02145587086621472</v>
+        <v>0.02145587086621473</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00140829314915756</v>
+        <v>0.001408293149157562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001735380459568782</v>
+        <v>0.001735380459568784</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001517283876810603</v>
+        <v>0.001517283876810604</v>
       </c>
       <c r="G5" t="n">
         <v>0.002252969253087986</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="J5" t="n">
         <v>0.00210604406029857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002107901006378451</v>
+        <v>0.002107901006378456</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007533391041597318</v>
+        <v>0.001565587875161523</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001714620232395714</v>
+        <v>0.001714620232395717</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001678088800516386</v>
+        <v>0.00167808880051639</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001270804237469453</v>
+        <v>0.001270804237469454</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001765897286635815</v>
+        <v>0.001765897286635816</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001904134290272248</v>
+        <v>0.00190413429027225</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002108038499269526</v>
+        <v>0.00210803849926953</v>
       </c>
       <c r="X5" t="n">
         <v>0.001334924687665459</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002802590865468298</v>
+        <v>0.0028025908654683</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001395297574038133</v>
+        <v>0.001395297574038136</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002107901006378468</v>
+        <v>0.002107901006378472</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002838699913412753</v>
+        <v>0.002838699913412757</v>
       </c>
     </row>
     <row r="6">
@@ -7886,85 +7886,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001883681860253553</v>
+        <v>0.001883681860253554</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002219037893108517</v>
+        <v>0.002219037893108518</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001314611619708029</v>
+        <v>0.001314611619708027</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002319659830266279</v>
+        <v>0.002319659830266281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002317802596246118</v>
+        <v>0.002317802596246124</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002319659542326033</v>
+        <v>0.002319659542326027</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007533391041597318</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002464142358666802</v>
+        <v>0.002464142358666801</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002495564829688884</v>
+        <v>0.002495564829688885</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002319659830266279</v>
+        <v>0.002319659830266281</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002810804801177222</v>
+        <v>0.002810804801177223</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002056803883022438</v>
+        <v>0.002056803883022437</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002319659542326031</v>
+        <v>0.002319659542326026</v>
       </c>
     </row>
     <row r="7">
@@ -7977,25 +7977,25 @@
         <v>0.001583512359582329</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001560734713011724</v>
+        <v>0.001560734713011723</v>
       </c>
       <c r="D7" t="n">
         <v>0.001519261993329689</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002701632646667966</v>
+        <v>0.002701632646667963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001543491741247491</v>
+        <v>0.00154349174124749</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001164845434920399</v>
+        <v>0.001164845434920398</v>
       </c>
       <c r="H7" t="n">
         <v>0.001517192094936035</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001521934836372627</v>
+        <v>0.001521934836372626</v>
       </c>
       <c r="J7" t="n">
         <v>0.001387981472035324</v>
@@ -8004,31 +8004,31 @@
         <v>0.001455207854595757</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00135757225088635</v>
+        <v>0.001357572250886349</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001444921445743648</v>
+        <v>0.001444921445743649</v>
       </c>
       <c r="N7" t="n">
         <v>0.001465715959008167</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001515368309887745</v>
+        <v>0.001515368309887746</v>
       </c>
       <c r="P7" t="n">
         <v>0.001330450424065181</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001484074770471161</v>
+        <v>0.001484074770471163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001437448802220154</v>
+        <v>0.001437448802220155</v>
       </c>
       <c r="S7" t="n">
         <v>0.001470228726941664</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001521951362784054</v>
+        <v>0.001521951362784053</v>
       </c>
       <c r="U7" t="n">
         <v>0.001500931228433925</v>
@@ -8037,22 +8037,22 @@
         <v>0.001496414277123962</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001348579157348011</v>
+        <v>0.001348579157348009</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001109466610929818</v>
+        <v>0.001109466610929816</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00113251629719055</v>
+        <v>0.001132516297190551</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001511504571721068</v>
+        <v>0.001511504571721069</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00144330133658997</v>
+        <v>0.001443301336589971</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001108807960225521</v>
+        <v>0.00110880796022552</v>
       </c>
     </row>
     <row r="8">
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001576440857441655</v>
+        <v>0.001576440857441654</v>
       </c>
       <c r="C8" t="n">
         <v>0.00157557638649579</v>
@@ -8071,22 +8071,22 @@
         <v>0.001558283797328856</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002717280743678482</v>
+        <v>0.002717280743678485</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001567921397375804</v>
+        <v>0.001567921397375805</v>
       </c>
       <c r="G8" t="n">
         <v>0.001432350113597243</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001557819958735243</v>
+        <v>0.001557819958735241</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001559076530934288</v>
+        <v>0.001559076530934289</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001519065430681123</v>
+        <v>0.001519065430681124</v>
       </c>
       <c r="K8" t="n">
         <v>0.001541479454376981</v>
@@ -8098,46 +8098,46 @@
         <v>0.001537266949175717</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001542947267748619</v>
+        <v>0.001542947267748617</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001556869483273039</v>
+        <v>0.001556869483273041</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001503736559832944</v>
+        <v>0.001503736559832943</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001548219456834931</v>
+        <v>0.001548219456834934</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001529652968163597</v>
+        <v>0.001529652968163596</v>
       </c>
       <c r="S8" t="n">
         <v>0.001544018749272842</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001559059481457097</v>
+        <v>0.001559059481457095</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001552857759448671</v>
+        <v>0.001552857759448669</v>
       </c>
       <c r="V8" t="n">
         <v>0.001539685688345257</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001509406670728032</v>
+        <v>0.001509406670728034</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001408618763984991</v>
+        <v>0.001408618763984989</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00144784082272134</v>
+        <v>0.001447840822721338</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001556194697626986</v>
+        <v>0.001556194697626985</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001536481336844444</v>
+        <v>0.001536481336844445</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001401273557052188</v>
